--- a/artfynd/A 22902-2025 artfynd.xlsx
+++ b/artfynd/A 22902-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125724629</v>
+        <v>125708514</v>
       </c>
       <c r="B2" t="n">
-        <v>91238</v>
+        <v>78967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450502</v>
+        <v>451330</v>
       </c>
       <c r="R2" t="n">
-        <v>7054507</v>
+        <v>7055192</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125724628</v>
+        <v>125714988</v>
       </c>
       <c r="B3" t="n">
-        <v>91238</v>
+        <v>57651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451229</v>
+        <v>450413</v>
       </c>
       <c r="R3" t="n">
-        <v>7055028</v>
+        <v>7054149</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -840,11 +850,26 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -853,26 +878,51 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125708514</v>
+        <v>125724597</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,37 +930,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451330</v>
+        <v>450287</v>
       </c>
       <c r="R4" t="n">
-        <v>7055192</v>
+        <v>7054787</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -940,6 +990,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -954,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125714988</v>
+        <v>125724629</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>91238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,44 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450413</v>
+        <v>450502</v>
       </c>
       <c r="R5" t="n">
-        <v>7054149</v>
+        <v>7054507</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,26 +1089,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1072,51 +1102,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125724597</v>
+        <v>125724628</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>91238</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450287</v>
+        <v>451229</v>
       </c>
       <c r="R6" t="n">
-        <v>7054787</v>
+        <v>7055028</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,11 +1189,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125711912</v>
+        <v>125724591</v>
       </c>
       <c r="B7" t="n">
         <v>57651</v>
@@ -1244,29 +1244,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>450518</v>
+        <v>450270</v>
       </c>
       <c r="R7" t="n">
-        <v>7054696</v>
+        <v>7054720</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,24 +1283,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,28 +1301,23 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125724591</v>
+        <v>125724579</v>
       </c>
       <c r="B8" t="n">
         <v>57651</v>
@@ -1377,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>450270</v>
+        <v>450145</v>
       </c>
       <c r="R8" t="n">
-        <v>7054720</v>
+        <v>7054502</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125724579</v>
+        <v>125724610</v>
       </c>
       <c r="B9" t="n">
         <v>57651</v>
@@ -1479,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>450145</v>
+        <v>450597</v>
       </c>
       <c r="R9" t="n">
-        <v>7054502</v>
+        <v>7055031</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125724610</v>
+        <v>125711912</v>
       </c>
       <c r="B10" t="n">
         <v>57651</v>
@@ -1575,19 +1550,29 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450597</v>
+        <v>450518</v>
       </c>
       <c r="R10" t="n">
-        <v>7055031</v>
+        <v>7054696</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1614,14 +1599,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1632,16 +1627,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2314,62 +2314,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125708478</v>
+        <v>125724560</v>
       </c>
       <c r="B17" t="n">
-        <v>98345</v>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451306</v>
+        <v>450673</v>
       </c>
       <c r="R17" t="n">
-        <v>7055204</v>
+        <v>7054359</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2396,24 +2382,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minst 6 plantor inom ca 4 m2 yta.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2424,80 +2400,61 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125714526</v>
+        <v>125724635</v>
       </c>
       <c r="B18" t="n">
-        <v>98345</v>
+        <v>78967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>450368</v>
+        <v>451002</v>
       </c>
       <c r="R18" t="n">
-        <v>7054102</v>
+        <v>7055090</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2527,26 +2484,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2555,31 +2497,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125724635</v>
+        <v>125718101</v>
       </c>
       <c r="B19" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2587,37 +2524,47 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451002</v>
+        <v>451151</v>
       </c>
       <c r="R19" t="n">
-        <v>7055090</v>
+        <v>7054937</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2644,11 +2591,26 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre och rejäla, längs ca 2 meter på en granstam.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2657,23 +2619,48 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125724560</v>
+        <v>125724598</v>
       </c>
       <c r="B20" t="n">
         <v>57651</v>
@@ -2708,10 +2695,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>450673</v>
+        <v>450292</v>
       </c>
       <c r="R20" t="n">
-        <v>7054359</v>
+        <v>7054851</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2775,7 +2762,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125718101</v>
+        <v>125724547</v>
       </c>
       <c r="B21" t="n">
         <v>57651</v>
@@ -2804,29 +2791,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451151</v>
+        <v>451006</v>
       </c>
       <c r="R21" t="n">
-        <v>7054937</v>
+        <v>7054764</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2853,24 +2830,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, äldre och rejäla, längs ca 2 meter på en granstam.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2881,89 +2848,78 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125724598</v>
+        <v>125708478</v>
       </c>
       <c r="B22" t="n">
-        <v>57651</v>
+        <v>98345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>450292</v>
+        <v>451306</v>
       </c>
       <c r="R22" t="n">
-        <v>7054851</v>
+        <v>7055204</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2990,14 +2946,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 6 plantor inom ca 4 m2 yta.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3008,61 +2974,80 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125724547</v>
+        <v>125714526</v>
       </c>
       <c r="B23" t="n">
-        <v>57651</v>
+        <v>98345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451006</v>
+        <v>450368</v>
       </c>
       <c r="R23" t="n">
-        <v>7054764</v>
+        <v>7054102</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3092,14 +3077,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 11 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3110,16 +3105,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3579,48 +3579,62 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125724573</v>
+        <v>125709103</v>
       </c>
       <c r="B28" t="n">
-        <v>57651</v>
+        <v>98345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Slättbrännorna, Slättbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>450391</v>
+        <v>451383</v>
       </c>
       <c r="R28" t="n">
-        <v>7054076</v>
+        <v>7055475</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3654,7 +3668,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Minst 6 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3665,26 +3679,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125724572</v>
+        <v>125717532</v>
       </c>
       <c r="B29" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3692,34 +3711,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>450406</v>
+        <v>450948</v>
       </c>
       <c r="R29" t="n">
-        <v>7054072</v>
+        <v>7054739</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3749,14 +3768,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3767,64 +3796,94 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125717532</v>
+        <v>125715130</v>
       </c>
       <c r="B30" t="n">
-        <v>78967</v>
+        <v>80106</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>450948</v>
+        <v>450363</v>
       </c>
       <c r="R30" t="n">
-        <v>7054739</v>
+        <v>7054211</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3853,7 +3912,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3863,12 +3922,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3882,27 +3941,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3920,53 +3979,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125715130</v>
+        <v>125724573</v>
       </c>
       <c r="B31" t="n">
-        <v>80106</v>
+        <v>57651</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>450363</v>
+        <v>450391</v>
       </c>
       <c r="R31" t="n">
-        <v>7054211</v>
+        <v>7054076</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3993,24 +4047,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4021,48 +4065,23 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125724574</v>
+        <v>125724572</v>
       </c>
       <c r="B32" t="n">
         <v>57651</v>
@@ -4097,10 +4116,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>450390</v>
+        <v>450406</v>
       </c>
       <c r="R32" t="n">
-        <v>7054071</v>
+        <v>7054072</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4164,7 +4183,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125724608</v>
+        <v>125724574</v>
       </c>
       <c r="B33" t="n">
         <v>57651</v>
@@ -4199,10 +4218,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450441</v>
+        <v>450390</v>
       </c>
       <c r="R33" t="n">
-        <v>7054842</v>
+        <v>7054071</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4266,62 +4285,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125709103</v>
+        <v>125724608</v>
       </c>
       <c r="B34" t="n">
-        <v>98345</v>
+        <v>57651</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Slättbrännorna, Slättbrännorna, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451383</v>
+        <v>450441</v>
       </c>
       <c r="R34" t="n">
-        <v>7055475</v>
+        <v>7054842</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4355,7 +4360,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Minst 6 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4366,28 +4371,23 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125716595</v>
+        <v>125724603</v>
       </c>
       <c r="B35" t="n">
         <v>57651</v>
@@ -4416,26 +4416,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>450481</v>
+        <v>450339</v>
       </c>
       <c r="R35" t="n">
-        <v>7054352</v>
+        <v>7054827</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4465,24 +4455,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4493,48 +4473,23 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125724613</v>
+        <v>125716595</v>
       </c>
       <c r="B36" t="n">
         <v>57651</v>
@@ -4563,16 +4518,26 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>450714</v>
+        <v>450481</v>
       </c>
       <c r="R36" t="n">
-        <v>7055072</v>
+        <v>7054352</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4602,14 +4567,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4620,26 +4595,51 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125724627</v>
+        <v>125724613</v>
       </c>
       <c r="B37" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4647,21 +4647,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4671,10 +4671,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>450528</v>
+        <v>450714</v>
       </c>
       <c r="R37" t="n">
-        <v>7054102</v>
+        <v>7055072</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4707,6 +4707,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4733,45 +4738,64 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125724603</v>
+        <v>125711207</v>
       </c>
       <c r="B38" t="n">
-        <v>57651</v>
+        <v>98345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450339</v>
+        <v>450852</v>
       </c>
       <c r="R38" t="n">
-        <v>7054827</v>
+        <v>7054681</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4808,7 +4832,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Minst 17 plantor inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4819,80 +4843,66 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125711207</v>
+        <v>125724627</v>
       </c>
       <c r="B39" t="n">
-        <v>98345</v>
+        <v>80070</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>450852</v>
+        <v>450528</v>
       </c>
       <c r="R39" t="n">
-        <v>7054681</v>
+        <v>7054102</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4927,11 +4937,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Minst 17 plantor inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4940,31 +4945,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125708223</v>
+        <v>125724631</v>
       </c>
       <c r="B40" t="n">
-        <v>78967</v>
+        <v>91238</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4972,37 +4972,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>451292</v>
+        <v>450196</v>
       </c>
       <c r="R40" t="n">
-        <v>7055142</v>
+        <v>7054664</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5029,21 +5029,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5052,48 +5042,23 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125715396</v>
+        <v>125708223</v>
       </c>
       <c r="B41" t="n">
         <v>78967</v>
@@ -5124,17 +5089,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>450394</v>
+        <v>451292</v>
       </c>
       <c r="R41" t="n">
-        <v>7054235</v>
+        <v>7055142</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5161,11 +5126,21 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5174,6 +5149,31 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5190,7 +5190,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125710168</v>
+        <v>125715396</v>
       </c>
       <c r="B42" t="n">
         <v>78967</v>
@@ -5221,17 +5221,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>451182</v>
+        <v>450394</v>
       </c>
       <c r="R42" t="n">
-        <v>7055004</v>
+        <v>7054235</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5261,11 +5261,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5292,10 +5287,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125724594</v>
+        <v>125710168</v>
       </c>
       <c r="B43" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5303,37 +5298,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>450285</v>
+        <v>451182</v>
       </c>
       <c r="R43" t="n">
-        <v>7054794</v>
+        <v>7055004</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5367,7 +5362,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5382,19 +5377,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125724556</v>
+        <v>125724594</v>
       </c>
       <c r="B44" t="n">
         <v>57651</v>
@@ -5429,10 +5424,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>450878</v>
+        <v>450285</v>
       </c>
       <c r="R44" t="n">
-        <v>7054550</v>
+        <v>7054794</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5496,7 +5491,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125724580</v>
+        <v>125724556</v>
       </c>
       <c r="B45" t="n">
         <v>57651</v>
@@ -5531,10 +5526,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>450072</v>
+        <v>450878</v>
       </c>
       <c r="R45" t="n">
-        <v>7054712</v>
+        <v>7054550</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5598,10 +5593,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125724631</v>
+        <v>125724580</v>
       </c>
       <c r="B46" t="n">
-        <v>91238</v>
+        <v>57651</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5609,21 +5604,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5633,10 +5628,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>450196</v>
+        <v>450072</v>
       </c>
       <c r="R46" t="n">
-        <v>7054664</v>
+        <v>7054712</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5669,6 +5664,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -7930,10 +7930,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125714185</v>
+        <v>125724626</v>
       </c>
       <c r="B66" t="n">
-        <v>57069</v>
+        <v>80070</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7941,56 +7941,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>102961</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>450224</v>
+        <v>450584</v>
       </c>
       <c r="R66" t="n">
-        <v>7054100</v>
+        <v>7054245</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8017,19 +7998,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8044,22 +8015,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125724626</v>
+        <v>125717826</v>
       </c>
       <c r="B67" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8067,37 +8038,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>450584</v>
+        <v>451046</v>
       </c>
       <c r="R67" t="n">
-        <v>7054245</v>
+        <v>7054820</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8124,11 +8095,26 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Långväxta bålar i god mängd.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8137,26 +8123,51 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125717826</v>
+        <v>125714185</v>
       </c>
       <c r="B68" t="n">
-        <v>78967</v>
+        <v>57069</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8164,37 +8175,56 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>102961</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>451046</v>
+        <v>450224</v>
       </c>
       <c r="R68" t="n">
-        <v>7054820</v>
+        <v>7054100</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8223,7 +8253,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8233,12 +8263,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Långväxta bålar i god mängd.</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8249,31 +8274,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8411,10 +8411,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125716115</v>
+        <v>125724544</v>
       </c>
       <c r="B70" t="n">
-        <v>78967</v>
+        <v>91220</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8422,37 +8422,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>450545</v>
+        <v>450929</v>
       </c>
       <c r="R70" t="n">
-        <v>7054277</v>
+        <v>7054588</v>
       </c>
       <c r="S70" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8479,19 +8479,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8506,22 +8496,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125724596</v>
+        <v>125716115</v>
       </c>
       <c r="B71" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8529,37 +8519,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>450286</v>
+        <v>450545</v>
       </c>
       <c r="R71" t="n">
-        <v>7054789</v>
+        <v>7054277</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8586,14 +8576,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8608,22 +8603,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125724544</v>
+        <v>125724596</v>
       </c>
       <c r="B72" t="n">
-        <v>91220</v>
+        <v>57651</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8631,21 +8626,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8655,10 +8650,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>450929</v>
+        <v>450286</v>
       </c>
       <c r="R72" t="n">
-        <v>7054588</v>
+        <v>7054789</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8691,6 +8686,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9759,10 +9759,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125709469</v>
+        <v>125724569</v>
       </c>
       <c r="B82" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9770,34 +9770,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>451269</v>
+        <v>450437</v>
       </c>
       <c r="R82" t="n">
-        <v>7055329</v>
+        <v>7054064</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9832,6 +9832,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9844,19 +9849,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125724569</v>
+        <v>125724588</v>
       </c>
       <c r="B83" t="n">
         <v>57651</v>
@@ -9891,10 +9896,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>450437</v>
+        <v>450275</v>
       </c>
       <c r="R83" t="n">
-        <v>7054064</v>
+        <v>7054607</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9931,7 +9936,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9958,7 +9963,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125724588</v>
+        <v>125724568</v>
       </c>
       <c r="B84" t="n">
         <v>57651</v>
@@ -9993,10 +9998,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>450275</v>
+        <v>450530</v>
       </c>
       <c r="R84" t="n">
-        <v>7054607</v>
+        <v>7054095</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10033,7 +10038,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10060,10 +10065,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125724568</v>
+        <v>125709469</v>
       </c>
       <c r="B85" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10071,34 +10076,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>450530</v>
+        <v>451269</v>
       </c>
       <c r="R85" t="n">
-        <v>7054095</v>
+        <v>7055329</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10133,11 +10138,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10150,12 +10150,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10289,62 +10289,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125708960</v>
+        <v>125724605</v>
       </c>
       <c r="B87" t="n">
-        <v>98345</v>
+        <v>57651</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>451445</v>
+        <v>450357</v>
       </c>
       <c r="R87" t="n">
-        <v>7055383</v>
+        <v>7054800</v>
       </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10378,7 +10364,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Minst 29 plantor inom ca 2 m2.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10389,28 +10375,23 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125724605</v>
+        <v>125715345</v>
       </c>
       <c r="B88" t="n">
         <v>57651</v>
@@ -10439,16 +10420,26 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>450357</v>
+        <v>450372</v>
       </c>
       <c r="R88" t="n">
-        <v>7054800</v>
+        <v>7054250</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10478,14 +10469,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en död liggande gran precis öster om vägen.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10496,23 +10497,48 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125715345</v>
+        <v>125724587</v>
       </c>
       <c r="B89" t="n">
         <v>57651</v>
@@ -10541,26 +10567,16 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>450372</v>
+        <v>450279</v>
       </c>
       <c r="R89" t="n">
-        <v>7054250</v>
+        <v>7054606</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10590,24 +10606,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en död liggande gran precis öster om vägen.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10618,48 +10624,23 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125724587</v>
+        <v>125715883</v>
       </c>
       <c r="B90" t="n">
         <v>57651</v>
@@ -10688,19 +10669,29 @@
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>450279</v>
+        <v>450371</v>
       </c>
       <c r="R90" t="n">
-        <v>7054606</v>
+        <v>7054182</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10727,14 +10718,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en något smalare gran.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10745,74 +10746,103 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125715883</v>
+        <v>125708960</v>
       </c>
       <c r="B91" t="n">
-        <v>57651</v>
+        <v>98345</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>450371</v>
+        <v>451445</v>
       </c>
       <c r="R91" t="n">
-        <v>7054182</v>
+        <v>7055383</v>
       </c>
       <c r="S91" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10839,24 +10869,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en något smalare gran.</t>
+          <t>Minst 29 plantor inom ca 2 m2.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10871,26 +10891,6 @@
       <c r="AH91" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11852,7 +11852,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125724566</v>
+        <v>125715238</v>
       </c>
       <c r="B100" t="n">
         <v>57651</v>
@@ -11881,16 +11881,26 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>450600</v>
+        <v>450342</v>
       </c>
       <c r="R100" t="n">
-        <v>7054142</v>
+        <v>7054212</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11920,14 +11930,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran  precis öster om vägen.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11938,23 +11958,48 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125724551</v>
+        <v>125724566</v>
       </c>
       <c r="B101" t="n">
         <v>57651</v>
@@ -11989,10 +12034,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>450486</v>
+        <v>450600</v>
       </c>
       <c r="R101" t="n">
-        <v>7054445</v>
+        <v>7054142</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12056,7 +12101,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125724609</v>
+        <v>125724551</v>
       </c>
       <c r="B102" t="n">
         <v>57651</v>
@@ -12091,10 +12136,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>450581</v>
+        <v>450486</v>
       </c>
       <c r="R102" t="n">
-        <v>7055012</v>
+        <v>7054445</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12158,45 +12203,59 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125724546</v>
+        <v>125712767</v>
       </c>
       <c r="B103" t="n">
-        <v>57651</v>
+        <v>98345</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>451102</v>
+        <v>450391</v>
       </c>
       <c r="R103" t="n">
-        <v>7054896</v>
+        <v>7054281</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12226,14 +12285,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 20 plantor inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12244,23 +12313,28 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125724621</v>
+        <v>125724609</v>
       </c>
       <c r="B104" t="n">
         <v>57651</v>
@@ -12295,10 +12369,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>450933</v>
+        <v>450581</v>
       </c>
       <c r="R104" t="n">
-        <v>7054883</v>
+        <v>7055012</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12335,7 +12409,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12362,7 +12436,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125724618</v>
+        <v>125724546</v>
       </c>
       <c r="B105" t="n">
         <v>57651</v>
@@ -12397,10 +12471,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>450905</v>
+        <v>451102</v>
       </c>
       <c r="R105" t="n">
-        <v>7054898</v>
+        <v>7054896</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12464,7 +12538,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125724577</v>
+        <v>125724621</v>
       </c>
       <c r="B106" t="n">
         <v>57651</v>
@@ -12499,10 +12573,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>450259</v>
+        <v>450933</v>
       </c>
       <c r="R106" t="n">
-        <v>7054380</v>
+        <v>7054883</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12539,7 +12613,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12566,7 +12640,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125715238</v>
+        <v>125724618</v>
       </c>
       <c r="B107" t="n">
         <v>57651</v>
@@ -12595,26 +12669,16 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>450342</v>
+        <v>450905</v>
       </c>
       <c r="R107" t="n">
-        <v>7054212</v>
+        <v>7054898</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12644,24 +12708,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  precis öster om vägen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12672,100 +12726,61 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125712767</v>
+        <v>125724577</v>
       </c>
       <c r="B108" t="n">
-        <v>98345</v>
+        <v>57651</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>450391</v>
+        <v>450259</v>
       </c>
       <c r="R108" t="n">
-        <v>7054281</v>
+        <v>7054380</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12795,24 +12810,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Minst 20 plantor inom ca 2 m2 yta.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12823,21 +12828,16 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -13769,7 +13769,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125712655</v>
+        <v>125724559</v>
       </c>
       <c r="B117" t="n">
         <v>57651</v>
@@ -13798,29 +13798,19 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>450387</v>
+        <v>450487</v>
       </c>
       <c r="R117" t="n">
-        <v>7054295</v>
+        <v>7054409</v>
       </c>
       <c r="S117" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13847,24 +13837,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran intill en stor myrstack.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13875,48 +13855,23 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125715638</v>
+        <v>125724557</v>
       </c>
       <c r="B118" t="n">
         <v>57651</v>
@@ -13945,26 +13900,16 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>450416</v>
+        <v>450772</v>
       </c>
       <c r="R118" t="n">
-        <v>7054156</v>
+        <v>7054621</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13994,24 +13939,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14022,48 +13957,23 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125724559</v>
+        <v>125712655</v>
       </c>
       <c r="B119" t="n">
         <v>57651</v>
@@ -14092,19 +14002,29 @@
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>450487</v>
+        <v>450387</v>
       </c>
       <c r="R119" t="n">
-        <v>7054409</v>
+        <v>7054295</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14131,14 +14051,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gran intill en stor myrstack.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14149,23 +14079,48 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125724557</v>
+        <v>125715638</v>
       </c>
       <c r="B120" t="n">
         <v>57651</v>
@@ -14194,16 +14149,26 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>450772</v>
+        <v>450416</v>
       </c>
       <c r="R120" t="n">
-        <v>7054621</v>
+        <v>7054156</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14233,14 +14198,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14251,16 +14226,41 @@
       </c>
       <c r="AG120" t="b">
         <v>0</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -14593,7 +14593,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125724616</v>
+        <v>125724602</v>
       </c>
       <c r="B124" t="n">
         <v>57651</v>
@@ -14628,10 +14628,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>450858</v>
+        <v>450307</v>
       </c>
       <c r="R124" t="n">
-        <v>7054949</v>
+        <v>7054854</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14695,7 +14695,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125724612</v>
+        <v>125724616</v>
       </c>
       <c r="B125" t="n">
         <v>57651</v>
@@ -14730,10 +14730,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>450636</v>
+        <v>450858</v>
       </c>
       <c r="R125" t="n">
-        <v>7054958</v>
+        <v>7054949</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14770,7 +14770,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14797,7 +14797,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125724548</v>
+        <v>125724612</v>
       </c>
       <c r="B126" t="n">
         <v>57651</v>
@@ -14832,10 +14832,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>450973</v>
+        <v>450636</v>
       </c>
       <c r="R126" t="n">
-        <v>7054710</v>
+        <v>7054958</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14899,7 +14899,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125724617</v>
+        <v>125724548</v>
       </c>
       <c r="B127" t="n">
         <v>57651</v>
@@ -14934,10 +14934,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>450851</v>
+        <v>450973</v>
       </c>
       <c r="R127" t="n">
-        <v>7054937</v>
+        <v>7054710</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15001,7 +15001,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125724623</v>
+        <v>125724617</v>
       </c>
       <c r="B128" t="n">
         <v>57651</v>
@@ -15036,10 +15036,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>451200</v>
+        <v>450851</v>
       </c>
       <c r="R128" t="n">
-        <v>7055401</v>
+        <v>7054937</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15103,7 +15103,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125724602</v>
+        <v>125724623</v>
       </c>
       <c r="B129" t="n">
         <v>57651</v>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>450307</v>
+        <v>451200</v>
       </c>
       <c r="R129" t="n">
-        <v>7054854</v>
+        <v>7055401</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15178,7 +15178,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15307,10 +15307,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125712965</v>
+        <v>125710733</v>
       </c>
       <c r="B131" t="n">
-        <v>56843</v>
+        <v>98345</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15318,47 +15318,42 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>450279</v>
+        <v>451046</v>
       </c>
       <c r="R131" t="n">
-        <v>7054063</v>
+        <v>7054942</v>
       </c>
       <c r="S131" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15385,19 +15380,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>13:00</t>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15411,7 +15401,7 @@
       </c>
       <c r="AH131" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -15531,48 +15521,58 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125724601</v>
+        <v>125712965</v>
       </c>
       <c r="B133" t="n">
-        <v>57651</v>
+        <v>56843</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>450317</v>
+        <v>450279</v>
       </c>
       <c r="R133" t="n">
-        <v>7054857</v>
+        <v>7054063</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15599,14 +15599,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15617,23 +15622,28 @@
       </c>
       <c r="AG133" t="b">
         <v>0</v>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125724611</v>
+        <v>125724601</v>
       </c>
       <c r="B134" t="n">
         <v>57651</v>
@@ -15668,10 +15678,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>450631</v>
+        <v>450317</v>
       </c>
       <c r="R134" t="n">
-        <v>7054989</v>
+        <v>7054857</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15708,7 +15718,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15735,7 +15745,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125724582</v>
+        <v>125724611</v>
       </c>
       <c r="B135" t="n">
         <v>57651</v>
@@ -15770,10 +15780,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>450120</v>
+        <v>450631</v>
       </c>
       <c r="R135" t="n">
-        <v>7054703</v>
+        <v>7054989</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15837,7 +15847,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125724620</v>
+        <v>125724582</v>
       </c>
       <c r="B136" t="n">
         <v>57651</v>
@@ -15872,10 +15882,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>450942</v>
+        <v>450120</v>
       </c>
       <c r="R136" t="n">
-        <v>7054894</v>
+        <v>7054703</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15939,53 +15949,48 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125710733</v>
+        <v>125724620</v>
       </c>
       <c r="B137" t="n">
-        <v>98345</v>
+        <v>57651</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>451046</v>
+        <v>450942</v>
       </c>
       <c r="R137" t="n">
-        <v>7054942</v>
+        <v>7054894</v>
       </c>
       <c r="S137" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16019,7 +16024,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16030,21 +16035,16 @@
       </c>
       <c r="AG137" t="b">
         <v>0</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>

--- a/artfynd/A 22902-2025 artfynd.xlsx
+++ b/artfynd/A 22902-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125708514</v>
+        <v>125711912</v>
       </c>
       <c r="B2" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451330</v>
+        <v>450518</v>
       </c>
       <c r="R2" t="n">
-        <v>7055192</v>
+        <v>7054696</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,11 +753,26 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -756,6 +781,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -772,7 +802,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125714988</v>
+        <v>125724579</v>
       </c>
       <c r="B3" t="n">
         <v>57651</v>
@@ -801,26 +831,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450413</v>
+        <v>450145</v>
       </c>
       <c r="R3" t="n">
-        <v>7054149</v>
+        <v>7054502</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,24 +870,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,48 +888,23 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125724597</v>
+        <v>125714988</v>
       </c>
       <c r="B4" t="n">
         <v>57651</v>
@@ -948,16 +933,26 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450287</v>
+        <v>450413</v>
       </c>
       <c r="R4" t="n">
-        <v>7054787</v>
+        <v>7054149</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,14 +982,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,26 +1010,51 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125724629</v>
+        <v>125724597</v>
       </c>
       <c r="B5" t="n">
-        <v>91238</v>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,21 +1062,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450502</v>
+        <v>450287</v>
       </c>
       <c r="R5" t="n">
-        <v>7054507</v>
+        <v>7054787</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,6 +1122,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125724628</v>
+        <v>125724591</v>
       </c>
       <c r="B6" t="n">
-        <v>91238</v>
+        <v>57651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,21 +1164,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451229</v>
+        <v>450270</v>
       </c>
       <c r="R6" t="n">
-        <v>7055028</v>
+        <v>7054720</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,6 +1224,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125724591</v>
+        <v>125724610</v>
       </c>
       <c r="B7" t="n">
         <v>57651</v>
@@ -1250,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>450270</v>
+        <v>450597</v>
       </c>
       <c r="R7" t="n">
-        <v>7054720</v>
+        <v>7055031</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1330,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125724579</v>
+        <v>125724629</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>91245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>450145</v>
+        <v>450502</v>
       </c>
       <c r="R8" t="n">
-        <v>7054502</v>
+        <v>7054507</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,11 +1428,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125724610</v>
+        <v>125724628</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>91245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1430,21 +1465,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>450597</v>
+        <v>451229</v>
       </c>
       <c r="R9" t="n">
-        <v>7055031</v>
+        <v>7055028</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,11 +1525,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125711912</v>
+        <v>125708514</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,47 +1562,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450518</v>
+        <v>451330</v>
       </c>
       <c r="R10" t="n">
-        <v>7054696</v>
+        <v>7055192</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1599,26 +1619,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1627,11 +1632,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125711059</v>
+        <v>125724585</v>
       </c>
       <c r="B11" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,34 +1659,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450886</v>
+        <v>450232</v>
       </c>
       <c r="R11" t="n">
-        <v>7054749</v>
+        <v>7054602</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,51 +1734,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125712265</v>
+        <v>125724599</v>
       </c>
       <c r="B12" t="n">
-        <v>57811</v>
+        <v>57651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,51 +1761,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Storholmen, Storholmen, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450456</v>
+        <v>450306</v>
       </c>
       <c r="R12" t="n">
-        <v>7054618</v>
+        <v>7054865</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1857,24 +1818,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Locklätet av en talltita observerades i lämplig häckmiljö.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1885,21 +1836,16 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2008,7 +1954,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125724585</v>
+        <v>125724619</v>
       </c>
       <c r="B14" t="n">
         <v>57651</v>
@@ -2043,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450232</v>
+        <v>450958</v>
       </c>
       <c r="R14" t="n">
-        <v>7054602</v>
+        <v>7054933</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2110,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125724599</v>
+        <v>125711059</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,34 +2067,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450306</v>
+        <v>450886</v>
       </c>
       <c r="R15" t="n">
-        <v>7054865</v>
+        <v>7054749</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,7 +2131,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2196,26 +2142,51 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125724619</v>
+        <v>125712265</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>57811</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,37 +2194,51 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storholmen, Storholmen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>450958</v>
+        <v>450456</v>
       </c>
       <c r="R16" t="n">
-        <v>7054933</v>
+        <v>7054618</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2280,14 +2265,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Locklätet av en talltita observerades i lämplig häckmiljö.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2298,23 +2293,28 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125724560</v>
+        <v>125718101</v>
       </c>
       <c r="B17" t="n">
         <v>57651</v>
@@ -2343,19 +2343,29 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>450673</v>
+        <v>451151</v>
       </c>
       <c r="R17" t="n">
-        <v>7054359</v>
+        <v>7054937</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2382,14 +2392,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre och rejäla, längs ca 2 meter på en granstam.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2400,26 +2420,51 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125724635</v>
+        <v>125724598</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,21 +2472,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2451,10 +2496,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451002</v>
+        <v>450292</v>
       </c>
       <c r="R18" t="n">
-        <v>7055090</v>
+        <v>7054851</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2487,6 +2532,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2513,7 +2563,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125718101</v>
+        <v>125724560</v>
       </c>
       <c r="B19" t="n">
         <v>57651</v>
@@ -2542,29 +2592,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451151</v>
+        <v>450673</v>
       </c>
       <c r="R19" t="n">
-        <v>7054937</v>
+        <v>7054359</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2591,24 +2631,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, äldre och rejäla, längs ca 2 meter på en granstam.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,48 +2649,23 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125724598</v>
+        <v>125724547</v>
       </c>
       <c r="B20" t="n">
         <v>57651</v>
@@ -2695,10 +2700,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>450292</v>
+        <v>451006</v>
       </c>
       <c r="R20" t="n">
-        <v>7054851</v>
+        <v>7054764</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2762,10 +2767,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125724547</v>
+        <v>125724635</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2773,21 +2778,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2797,10 +2802,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451006</v>
+        <v>451002</v>
       </c>
       <c r="R21" t="n">
-        <v>7054764</v>
+        <v>7055090</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2833,11 +2838,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2867,7 +2867,7 @@
         <v>125708478</v>
       </c>
       <c r="B22" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>125714526</v>
       </c>
       <c r="B23" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3126,48 +3126,62 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125724565</v>
+        <v>125709103</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>98352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Slättbrännorna, Slättbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>450606</v>
+        <v>451383</v>
       </c>
       <c r="R24" t="n">
-        <v>7054211</v>
+        <v>7055475</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3201,7 +3215,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 6 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3212,23 +3226,28 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125712711</v>
+        <v>125724565</v>
       </c>
       <c r="B25" t="n">
         <v>57651</v>
@@ -3257,29 +3276,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450410</v>
+        <v>450606</v>
       </c>
       <c r="R25" t="n">
-        <v>7054290</v>
+        <v>7054211</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3306,24 +3315,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  nära en stor myrstack.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3334,48 +3333,23 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125724593</v>
+        <v>125712711</v>
       </c>
       <c r="B26" t="n">
         <v>57651</v>
@@ -3404,19 +3378,29 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450274</v>
+        <v>450410</v>
       </c>
       <c r="R26" t="n">
-        <v>7054720</v>
+        <v>7054290</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3443,14 +3427,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran  nära en stor myrstack.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,23 +3455,48 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125724564</v>
+        <v>125724593</v>
       </c>
       <c r="B27" t="n">
         <v>57651</v>
@@ -3512,10 +3531,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>450638</v>
+        <v>450274</v>
       </c>
       <c r="R27" t="n">
-        <v>7054244</v>
+        <v>7054720</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3552,7 +3571,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3579,62 +3598,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125709103</v>
+        <v>125724564</v>
       </c>
       <c r="B28" t="n">
-        <v>98345</v>
+        <v>57651</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Slättbrännorna, Slättbrännorna, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>451383</v>
+        <v>450638</v>
       </c>
       <c r="R28" t="n">
-        <v>7055475</v>
+        <v>7054244</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3668,7 +3673,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 6 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3679,31 +3684,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125717532</v>
+        <v>125724574</v>
       </c>
       <c r="B29" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3711,34 +3711,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>450948</v>
+        <v>450390</v>
       </c>
       <c r="R29" t="n">
-        <v>7054739</v>
+        <v>7054071</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3768,24 +3768,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3796,94 +3786,64 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125715130</v>
+        <v>125724608</v>
       </c>
       <c r="B30" t="n">
-        <v>80106</v>
+        <v>57651</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>450363</v>
+        <v>450441</v>
       </c>
       <c r="R30" t="n">
-        <v>7054211</v>
+        <v>7054842</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3910,24 +3870,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3938,41 +3888,16 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4183,48 +4108,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125724574</v>
+        <v>125715130</v>
       </c>
       <c r="B33" t="n">
-        <v>57651</v>
+        <v>80106</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450390</v>
+        <v>450363</v>
       </c>
       <c r="R33" t="n">
-        <v>7054071</v>
+        <v>7054211</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4251,14 +4181,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4269,26 +4209,51 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125724608</v>
+        <v>125717532</v>
       </c>
       <c r="B34" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4296,34 +4261,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>450441</v>
+        <v>450948</v>
       </c>
       <c r="R34" t="n">
-        <v>7054842</v>
+        <v>7054739</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4353,14 +4318,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4371,23 +4346,48 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125724603</v>
+        <v>125716595</v>
       </c>
       <c r="B35" t="n">
         <v>57651</v>
@@ -4416,16 +4416,26 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>450339</v>
+        <v>450481</v>
       </c>
       <c r="R35" t="n">
-        <v>7054827</v>
+        <v>7054352</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4455,14 +4465,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4473,23 +4493,48 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125716595</v>
+        <v>125724603</v>
       </c>
       <c r="B36" t="n">
         <v>57651</v>
@@ -4518,26 +4563,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>450481</v>
+        <v>450339</v>
       </c>
       <c r="R36" t="n">
-        <v>7054352</v>
+        <v>7054827</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4567,24 +4602,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4595,41 +4620,16 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4738,64 +4738,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125711207</v>
+        <v>125724627</v>
       </c>
       <c r="B38" t="n">
-        <v>98345</v>
+        <v>80070</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450852</v>
+        <v>450528</v>
       </c>
       <c r="R38" t="n">
-        <v>7054681</v>
+        <v>7054102</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4830,11 +4811,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 17 plantor inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4843,66 +4819,80 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125724627</v>
+        <v>125711207</v>
       </c>
       <c r="B39" t="n">
-        <v>80070</v>
+        <v>98352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>450528</v>
+        <v>450852</v>
       </c>
       <c r="R39" t="n">
-        <v>7054102</v>
+        <v>7054681</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4937,6 +4927,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Minst 17 plantor inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4945,26 +4940,31 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125724631</v>
+        <v>125708223</v>
       </c>
       <c r="B40" t="n">
-        <v>91238</v>
+        <v>78967</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4972,37 +4972,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>450196</v>
+        <v>451292</v>
       </c>
       <c r="R40" t="n">
-        <v>7054664</v>
+        <v>7055142</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5029,11 +5029,21 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5042,23 +5052,48 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125708223</v>
+        <v>125715396</v>
       </c>
       <c r="B41" t="n">
         <v>78967</v>
@@ -5089,17 +5124,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>451292</v>
+        <v>450394</v>
       </c>
       <c r="R41" t="n">
-        <v>7055142</v>
+        <v>7054235</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5126,21 +5161,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5149,31 +5174,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5190,7 +5190,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125715396</v>
+        <v>125710168</v>
       </c>
       <c r="B42" t="n">
         <v>78967</v>
@@ -5221,17 +5221,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>450394</v>
+        <v>451182</v>
       </c>
       <c r="R42" t="n">
-        <v>7054235</v>
+        <v>7055004</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5261,6 +5261,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5287,10 +5292,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125710168</v>
+        <v>125724580</v>
       </c>
       <c r="B43" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5298,37 +5303,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>451182</v>
+        <v>450072</v>
       </c>
       <c r="R43" t="n">
-        <v>7055004</v>
+        <v>7054712</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5362,7 +5367,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5377,12 +5382,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5593,10 +5598,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125724580</v>
+        <v>125724631</v>
       </c>
       <c r="B46" t="n">
-        <v>57651</v>
+        <v>91245</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5604,21 +5609,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5628,10 +5633,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>450072</v>
+        <v>450196</v>
       </c>
       <c r="R46" t="n">
-        <v>7054712</v>
+        <v>7054664</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5664,11 +5669,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5695,48 +5695,62 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125710364</v>
+        <v>125709295</v>
       </c>
       <c r="B47" t="n">
-        <v>78967</v>
+        <v>98352</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451107</v>
+        <v>451312</v>
       </c>
       <c r="R47" t="n">
-        <v>7055032</v>
+        <v>7055388</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5770,7 +5784,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Gott om långväxta bålar på en gran.</t>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5784,27 +5798,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5822,10 +5816,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125724555</v>
+        <v>125710364</v>
       </c>
       <c r="B48" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5833,37 +5827,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>450816</v>
+        <v>451107</v>
       </c>
       <c r="R48" t="n">
-        <v>7054432</v>
+        <v>7055032</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5897,7 +5891,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Gott om långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5908,26 +5902,51 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125724553</v>
+        <v>125724630</v>
       </c>
       <c r="B49" t="n">
-        <v>57651</v>
+        <v>91245</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5935,21 +5954,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5959,10 +5978,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>450713</v>
+        <v>450577</v>
       </c>
       <c r="R49" t="n">
-        <v>7054346</v>
+        <v>7054440</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5995,11 +6014,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6026,10 +6040,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125724630</v>
+        <v>125711989</v>
       </c>
       <c r="B50" t="n">
-        <v>91238</v>
+        <v>57651</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6037,37 +6051,47 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>450577</v>
+        <v>450536</v>
       </c>
       <c r="R50" t="n">
-        <v>7054440</v>
+        <v>7054699</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6094,11 +6118,26 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6107,23 +6146,48 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125711989</v>
+        <v>125724615</v>
       </c>
       <c r="B51" t="n">
         <v>57651</v>
@@ -6152,29 +6216,19 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>450536</v>
+        <v>450856</v>
       </c>
       <c r="R51" t="n">
-        <v>7054699</v>
+        <v>7054955</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6201,24 +6255,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6229,48 +6273,23 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125724615</v>
+        <v>125724555</v>
       </c>
       <c r="B52" t="n">
         <v>57651</v>
@@ -6305,10 +6324,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>450856</v>
+        <v>450816</v>
       </c>
       <c r="R52" t="n">
-        <v>7054955</v>
+        <v>7054432</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6519,7 +6538,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125724614</v>
+        <v>125724553</v>
       </c>
       <c r="B54" t="n">
         <v>57651</v>
@@ -6554,10 +6573,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>450762</v>
+        <v>450713</v>
       </c>
       <c r="R54" t="n">
-        <v>7055029</v>
+        <v>7054346</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6594,7 +6613,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6621,62 +6640,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125709295</v>
+        <v>125724614</v>
       </c>
       <c r="B55" t="n">
-        <v>98345</v>
+        <v>57651</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>451312</v>
+        <v>450762</v>
       </c>
       <c r="R55" t="n">
-        <v>7055388</v>
+        <v>7055029</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6710,7 +6715,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6721,28 +6726,23 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125709678</v>
+        <v>125710504</v>
       </c>
       <c r="B56" t="n">
         <v>78967</v>
@@ -6777,13 +6777,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451218</v>
+        <v>451089</v>
       </c>
       <c r="R56" t="n">
-        <v>7055148</v>
+        <v>7054989</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6815,6 +6815,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flertalet granar.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6826,7 +6831,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
@@ -6864,10 +6869,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125710504</v>
+        <v>125724606</v>
       </c>
       <c r="B57" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6875,37 +6880,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451089</v>
+        <v>450436</v>
       </c>
       <c r="R57" t="n">
-        <v>7054989</v>
+        <v>7054836</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6939,7 +6944,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6950,51 +6955,26 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125711291</v>
+        <v>125724554</v>
       </c>
       <c r="B58" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7002,37 +6982,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>450795</v>
+        <v>450796</v>
       </c>
       <c r="R58" t="n">
-        <v>7054803</v>
+        <v>7054404</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7066,7 +7046,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7077,51 +7057,26 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125724606</v>
+        <v>125709678</v>
       </c>
       <c r="B59" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7129,37 +7084,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>450436</v>
+        <v>451218</v>
       </c>
       <c r="R59" t="n">
-        <v>7054836</v>
+        <v>7055148</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7191,11 +7146,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7204,26 +7154,51 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125724554</v>
+        <v>125711291</v>
       </c>
       <c r="B60" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7231,37 +7206,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>450796</v>
+        <v>450795</v>
       </c>
       <c r="R60" t="n">
-        <v>7054404</v>
+        <v>7054803</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7295,7 +7270,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7306,16 +7281,41 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7325,7 +7325,7 @@
         <v>125709578</v>
       </c>
       <c r="B61" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>125716316</v>
       </c>
       <c r="B62" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7569,10 +7569,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125724634</v>
+        <v>125714547</v>
       </c>
       <c r="B63" t="n">
-        <v>91238</v>
+        <v>78967</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7580,37 +7580,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>451148</v>
+        <v>450361</v>
       </c>
       <c r="R63" t="n">
-        <v>7055327</v>
+        <v>7054101</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7637,11 +7637,21 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7650,26 +7660,51 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125714547</v>
+        <v>125711118</v>
       </c>
       <c r="B64" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7677,34 +7712,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>450361</v>
+        <v>450865</v>
       </c>
       <c r="R64" t="n">
-        <v>7054101</v>
+        <v>7054734</v>
       </c>
       <c r="S64" t="n">
         <v>8</v>
@@ -7734,19 +7774,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:12</t>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På nedfallen död gren av sälg.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7760,27 +7795,27 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7798,10 +7833,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125711118</v>
+        <v>125724634</v>
       </c>
       <c r="B65" t="n">
-        <v>80071</v>
+        <v>91245</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7809,42 +7844,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>450865</v>
+        <v>451148</v>
       </c>
       <c r="R65" t="n">
-        <v>7054734</v>
+        <v>7055327</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7876,11 +7906,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På nedfallen död gren av sälg.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7889,41 +7914,16 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8290,62 +8290,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125708839</v>
+        <v>125716115</v>
       </c>
       <c r="B69" t="n">
-        <v>98345</v>
+        <v>78967</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>451394</v>
+        <v>450545</v>
       </c>
       <c r="R69" t="n">
-        <v>7055346</v>
+        <v>7054277</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8372,14 +8358,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor inom ca 2 m2.</t>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8390,11 +8381,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8414,7 +8400,7 @@
         <v>125724544</v>
       </c>
       <c r="B70" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8508,48 +8494,62 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125716115</v>
+        <v>125708839</v>
       </c>
       <c r="B71" t="n">
-        <v>78967</v>
+        <v>98352</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>450545</v>
+        <v>451394</v>
       </c>
       <c r="R71" t="n">
-        <v>7054277</v>
+        <v>7055346</v>
       </c>
       <c r="S71" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8576,19 +8576,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>15:34</t>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor inom ca 2 m2.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8599,6 +8594,11 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8615,7 +8615,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125724596</v>
+        <v>125715668</v>
       </c>
       <c r="B72" t="n">
         <v>57651</v>
@@ -8644,16 +8644,26 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>450286</v>
+        <v>450399</v>
       </c>
       <c r="R72" t="n">
-        <v>7054789</v>
+        <v>7054150</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8683,14 +8693,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8701,23 +8721,48 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125715668</v>
+        <v>125724596</v>
       </c>
       <c r="B73" t="n">
         <v>57651</v>
@@ -8746,26 +8791,16 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>450399</v>
+        <v>450286</v>
       </c>
       <c r="R73" t="n">
-        <v>7054150</v>
+        <v>7054789</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8795,24 +8830,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8823,41 +8848,16 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -9220,10 +9220,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125724584</v>
+        <v>125724545</v>
       </c>
       <c r="B77" t="n">
-        <v>57651</v>
+        <v>91227</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9231,21 +9231,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>450230</v>
+        <v>450771</v>
       </c>
       <c r="R77" t="n">
-        <v>7054621</v>
+        <v>7055042</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9291,11 +9291,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9322,7 +9317,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125724578</v>
+        <v>125724584</v>
       </c>
       <c r="B78" t="n">
         <v>57651</v>
@@ -9357,10 +9352,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>450228</v>
+        <v>450230</v>
       </c>
       <c r="R78" t="n">
-        <v>7054435</v>
+        <v>7054621</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9424,10 +9419,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125724545</v>
+        <v>125724550</v>
       </c>
       <c r="B79" t="n">
-        <v>91220</v>
+        <v>57651</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9435,21 +9430,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9459,10 +9454,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>450771</v>
+        <v>450437</v>
       </c>
       <c r="R79" t="n">
-        <v>7055042</v>
+        <v>7054480</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9495,6 +9490,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9521,7 +9521,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125724550</v>
+        <v>125724578</v>
       </c>
       <c r="B80" t="n">
         <v>57651</v>
@@ -9556,10 +9556,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>450437</v>
+        <v>450228</v>
       </c>
       <c r="R80" t="n">
-        <v>7054480</v>
+        <v>7054435</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9626,7 +9626,7 @@
         <v>125718167</v>
       </c>
       <c r="B81" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9759,10 +9759,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125724569</v>
+        <v>125709469</v>
       </c>
       <c r="B82" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9770,34 +9770,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>450437</v>
+        <v>451269</v>
       </c>
       <c r="R82" t="n">
-        <v>7054064</v>
+        <v>7055329</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9832,11 +9832,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9849,19 +9844,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125724588</v>
+        <v>125724569</v>
       </c>
       <c r="B83" t="n">
         <v>57651</v>
@@ -9896,10 +9891,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>450275</v>
+        <v>450437</v>
       </c>
       <c r="R83" t="n">
-        <v>7054607</v>
+        <v>7054064</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9936,7 +9931,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9963,7 +9958,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125724568</v>
+        <v>125724588</v>
       </c>
       <c r="B84" t="n">
         <v>57651</v>
@@ -9998,10 +9993,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>450530</v>
+        <v>450275</v>
       </c>
       <c r="R84" t="n">
-        <v>7054095</v>
+        <v>7054607</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10038,7 +10033,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10065,10 +10060,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125709469</v>
+        <v>125724568</v>
       </c>
       <c r="B85" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10076,34 +10071,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>451269</v>
+        <v>450530</v>
       </c>
       <c r="R85" t="n">
-        <v>7055329</v>
+        <v>7054095</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10138,6 +10133,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10150,60 +10150,74 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125710745</v>
+        <v>125708960</v>
       </c>
       <c r="B86" t="n">
-        <v>78967</v>
+        <v>98352</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>451035</v>
+        <v>451445</v>
       </c>
       <c r="R86" t="n">
-        <v>7054940</v>
+        <v>7055383</v>
       </c>
       <c r="S86" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10237,7 +10251,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 29 plantor inom ca 2 m2.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10252,26 +10266,6 @@
       <c r="AH86" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10289,10 +10283,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125724605</v>
+        <v>125710745</v>
       </c>
       <c r="B87" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10300,37 +10294,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>450357</v>
+        <v>451035</v>
       </c>
       <c r="R87" t="n">
-        <v>7054800</v>
+        <v>7054940</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10364,7 +10358,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10375,23 +10369,48 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125715345</v>
+        <v>125724605</v>
       </c>
       <c r="B88" t="n">
         <v>57651</v>
@@ -10420,26 +10439,16 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>450372</v>
+        <v>450357</v>
       </c>
       <c r="R88" t="n">
-        <v>7054250</v>
+        <v>7054800</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10469,24 +10478,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en död liggande gran precis öster om vägen.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10497,48 +10496,23 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125724587</v>
+        <v>125715345</v>
       </c>
       <c r="B89" t="n">
         <v>57651</v>
@@ -10567,16 +10541,26 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>450279</v>
+        <v>450372</v>
       </c>
       <c r="R89" t="n">
-        <v>7054606</v>
+        <v>7054250</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10606,14 +10590,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en död liggande gran precis öster om vägen.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10624,23 +10618,48 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125715883</v>
+        <v>125724587</v>
       </c>
       <c r="B90" t="n">
         <v>57651</v>
@@ -10669,29 +10688,19 @@
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>450371</v>
+        <v>450279</v>
       </c>
       <c r="R90" t="n">
-        <v>7054182</v>
+        <v>7054606</v>
       </c>
       <c r="S90" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10718,24 +10727,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en något smalare gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10746,103 +10745,74 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125708960</v>
+        <v>125715883</v>
       </c>
       <c r="B91" t="n">
-        <v>98345</v>
+        <v>57651</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>451445</v>
+        <v>450371</v>
       </c>
       <c r="R91" t="n">
-        <v>7055383</v>
+        <v>7054182</v>
       </c>
       <c r="S91" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10869,14 +10839,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Minst 29 plantor inom ca 2 m2.</t>
+          <t>Ringhack, äldre, på stambasen av en något smalare gran.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10891,6 +10871,26 @@
       <c r="AH91" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10908,10 +10908,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125714169</v>
+        <v>125724622</v>
       </c>
       <c r="B92" t="n">
-        <v>57811</v>
+        <v>57651</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10919,51 +10919,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>450226</v>
+        <v>450935</v>
       </c>
       <c r="R92" t="n">
-        <v>7054095</v>
+        <v>7055227</v>
       </c>
       <c r="S92" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10990,19 +10976,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>13:35</t>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11013,85 +10994,61 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125710515</v>
+        <v>125724543</v>
       </c>
       <c r="B93" t="n">
-        <v>58019</v>
+        <v>91582</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103015</v>
+        <v>2062</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>451089</v>
+        <v>450931</v>
       </c>
       <c r="R93" t="n">
-        <v>7054975</v>
+        <v>7054587</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11121,54 +11078,40 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125708590</v>
+        <v>125710515</v>
       </c>
       <c r="B94" t="n">
-        <v>98345</v>
+        <v>58019</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11176,36 +11119,41 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221952</v>
+        <v>103015</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11214,13 +11162,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>451359</v>
+        <v>451089</v>
       </c>
       <c r="R94" t="n">
-        <v>7055225</v>
+        <v>7054975</v>
       </c>
       <c r="S94" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11249,7 +11197,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11259,12 +11207,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 3 m2.</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11296,48 +11239,62 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125724543</v>
+        <v>125714169</v>
       </c>
       <c r="B95" t="n">
-        <v>91575</v>
+        <v>57811</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2062</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>450931</v>
+        <v>450226</v>
       </c>
       <c r="R95" t="n">
-        <v>7054587</v>
+        <v>7054095</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11364,78 +11321,106 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125724622</v>
+        <v>125708590</v>
       </c>
       <c r="B96" t="n">
-        <v>57651</v>
+        <v>98352</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>450935</v>
+        <v>451359</v>
       </c>
       <c r="R96" t="n">
-        <v>7055227</v>
+        <v>7055225</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11462,14 +11447,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 60 plantor inom ca 3 m2.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11480,16 +11475,21 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -11852,43 +11852,47 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125715238</v>
+        <v>125712767</v>
       </c>
       <c r="B100" t="n">
-        <v>57651</v>
+        <v>98352</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11897,10 +11901,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>450342</v>
+        <v>450391</v>
       </c>
       <c r="R100" t="n">
-        <v>7054212</v>
+        <v>7054281</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11932,7 +11936,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11942,12 +11946,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  precis öster om vägen.</t>
+          <t>Minst 20 plantor inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11962,26 +11966,6 @@
       <c r="AH100" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11999,7 +11983,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125724566</v>
+        <v>125724609</v>
       </c>
       <c r="B101" t="n">
         <v>57651</v>
@@ -12034,10 +12018,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>450600</v>
+        <v>450581</v>
       </c>
       <c r="R101" t="n">
-        <v>7054142</v>
+        <v>7055012</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12101,7 +12085,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125724551</v>
+        <v>125724546</v>
       </c>
       <c r="B102" t="n">
         <v>57651</v>
@@ -12136,10 +12120,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>450486</v>
+        <v>451102</v>
       </c>
       <c r="R102" t="n">
-        <v>7054445</v>
+        <v>7054896</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12203,59 +12187,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125712767</v>
+        <v>125724566</v>
       </c>
       <c r="B103" t="n">
-        <v>98345</v>
+        <v>57651</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>450391</v>
+        <v>450600</v>
       </c>
       <c r="R103" t="n">
-        <v>7054281</v>
+        <v>7054142</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12285,24 +12255,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Minst 20 plantor inom ca 2 m2 yta.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12313,28 +12273,23 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125724609</v>
+        <v>125724551</v>
       </c>
       <c r="B104" t="n">
         <v>57651</v>
@@ -12369,10 +12324,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>450581</v>
+        <v>450486</v>
       </c>
       <c r="R104" t="n">
-        <v>7055012</v>
+        <v>7054445</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12436,7 +12391,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125724546</v>
+        <v>125724621</v>
       </c>
       <c r="B105" t="n">
         <v>57651</v>
@@ -12471,10 +12426,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>451102</v>
+        <v>450933</v>
       </c>
       <c r="R105" t="n">
-        <v>7054896</v>
+        <v>7054883</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12511,7 +12466,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12538,7 +12493,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125724621</v>
+        <v>125715238</v>
       </c>
       <c r="B106" t="n">
         <v>57651</v>
@@ -12567,16 +12522,26 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>450933</v>
+        <v>450342</v>
       </c>
       <c r="R106" t="n">
-        <v>7054883</v>
+        <v>7054212</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12606,14 +12571,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran  precis öster om vägen.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12624,16 +12599,41 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -12844,10 +12844,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125724549</v>
+        <v>125712294</v>
       </c>
       <c r="B109" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12855,37 +12855,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storholmen, Storholmen, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>450547</v>
+        <v>450461</v>
       </c>
       <c r="R109" t="n">
-        <v>7054823</v>
+        <v>7054536</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12912,14 +12912,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12930,23 +12940,48 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125724586</v>
+        <v>125724549</v>
       </c>
       <c r="B110" t="n">
         <v>57651</v>
@@ -12981,10 +13016,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>450292</v>
+        <v>450547</v>
       </c>
       <c r="R110" t="n">
-        <v>7054587</v>
+        <v>7054823</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13021,7 +13056,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13048,7 +13083,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125724558</v>
+        <v>125724586</v>
       </c>
       <c r="B111" t="n">
         <v>57651</v>
@@ -13083,10 +13118,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>450702</v>
+        <v>450292</v>
       </c>
       <c r="R111" t="n">
-        <v>7054428</v>
+        <v>7054587</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13123,7 +13158,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13150,7 +13185,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125724552</v>
+        <v>125724558</v>
       </c>
       <c r="B112" t="n">
         <v>57651</v>
@@ -13185,10 +13220,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>450545</v>
+        <v>450702</v>
       </c>
       <c r="R112" t="n">
-        <v>7054416</v>
+        <v>7054428</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13252,10 +13287,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125712133</v>
+        <v>125724552</v>
       </c>
       <c r="B113" t="n">
-        <v>58129</v>
+        <v>57651</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13263,56 +13298,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>103018</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>450497</v>
+        <v>450545</v>
       </c>
       <c r="R113" t="n">
-        <v>7054617</v>
+        <v>7054416</v>
       </c>
       <c r="S113" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13339,24 +13355,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>En sjungande hane i ett stråk med en del asp.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13367,31 +13373,26 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125712294</v>
+        <v>125712133</v>
       </c>
       <c r="B114" t="n">
-        <v>78967</v>
+        <v>58129</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13399,37 +13400,56 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>103018</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Storholmen, Storholmen, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>450461</v>
+        <v>450497</v>
       </c>
       <c r="R114" t="n">
-        <v>7054536</v>
+        <v>7054617</v>
       </c>
       <c r="S114" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13458,7 +13478,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13468,12 +13488,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>En sjungande hane i ett stråk med en del asp.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13487,27 +13507,7 @@
       </c>
       <c r="AH114" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -13871,7 +13871,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125724557</v>
+        <v>125712655</v>
       </c>
       <c r="B118" t="n">
         <v>57651</v>
@@ -13900,19 +13900,29 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>450772</v>
+        <v>450387</v>
       </c>
       <c r="R118" t="n">
-        <v>7054621</v>
+        <v>7054295</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13939,14 +13949,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gran intill en stor myrstack.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13957,23 +13977,48 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125712655</v>
+        <v>125715638</v>
       </c>
       <c r="B119" t="n">
         <v>57651</v>
@@ -14018,13 +14063,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>450387</v>
+        <v>450416</v>
       </c>
       <c r="R119" t="n">
-        <v>7054295</v>
+        <v>7054156</v>
       </c>
       <c r="S119" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14053,7 +14098,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14063,12 +14108,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran intill en stor myrstack.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14120,7 +14165,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125715638</v>
+        <v>125724557</v>
       </c>
       <c r="B120" t="n">
         <v>57651</v>
@@ -14149,26 +14194,16 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>450416</v>
+        <v>450772</v>
       </c>
       <c r="R120" t="n">
-        <v>7054156</v>
+        <v>7054621</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14198,24 +14233,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14226,41 +14251,16 @@
       </c>
       <c r="AG120" t="b">
         <v>0</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -14270,7 +14270,7 @@
         <v>125724625</v>
       </c>
       <c r="B121" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14364,10 +14364,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125724633</v>
+        <v>125715696</v>
       </c>
       <c r="B122" t="n">
-        <v>91238</v>
+        <v>78967</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14375,37 +14375,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>450636</v>
+        <v>450391</v>
       </c>
       <c r="R122" t="n">
-        <v>7054969</v>
+        <v>7054170</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14432,11 +14432,21 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -14445,26 +14455,51 @@
       </c>
       <c r="AG122" t="b">
         <v>0</v>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125715696</v>
+        <v>125724571</v>
       </c>
       <c r="B123" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14472,37 +14507,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>450391</v>
+        <v>450408</v>
       </c>
       <c r="R123" t="n">
-        <v>7054170</v>
+        <v>7054064</v>
       </c>
       <c r="S123" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14529,19 +14564,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>15:13</t>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14552,48 +14582,23 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125724602</v>
+        <v>125724616</v>
       </c>
       <c r="B124" t="n">
         <v>57651</v>
@@ -14628,10 +14633,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>450307</v>
+        <v>450858</v>
       </c>
       <c r="R124" t="n">
-        <v>7054854</v>
+        <v>7054949</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14695,7 +14700,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125724616</v>
+        <v>125724612</v>
       </c>
       <c r="B125" t="n">
         <v>57651</v>
@@ -14730,10 +14735,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>450858</v>
+        <v>450636</v>
       </c>
       <c r="R125" t="n">
-        <v>7054949</v>
+        <v>7054958</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14770,7 +14775,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14797,7 +14802,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125724612</v>
+        <v>125724602</v>
       </c>
       <c r="B126" t="n">
         <v>57651</v>
@@ -14832,10 +14837,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>450636</v>
+        <v>450307</v>
       </c>
       <c r="R126" t="n">
-        <v>7054958</v>
+        <v>7054854</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14872,7 +14877,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15205,10 +15210,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125724571</v>
+        <v>125724633</v>
       </c>
       <c r="B130" t="n">
-        <v>57651</v>
+        <v>91245</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15216,21 +15221,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15240,10 +15245,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>450408</v>
+        <v>450636</v>
       </c>
       <c r="R130" t="n">
-        <v>7054064</v>
+        <v>7054969</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15276,11 +15281,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15307,53 +15307,48 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125710733</v>
+        <v>125724601</v>
       </c>
       <c r="B131" t="n">
-        <v>98345</v>
+        <v>57651</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>451046</v>
+        <v>450317</v>
       </c>
       <c r="R131" t="n">
-        <v>7054942</v>
+        <v>7054857</v>
       </c>
       <c r="S131" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15387,7 +15382,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15398,21 +15393,16 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -15521,58 +15511,48 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125712965</v>
+        <v>125724611</v>
       </c>
       <c r="B133" t="n">
-        <v>56843</v>
+        <v>57651</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>450279</v>
+        <v>450631</v>
       </c>
       <c r="R133" t="n">
-        <v>7054063</v>
+        <v>7054989</v>
       </c>
       <c r="S133" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15599,19 +15579,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>13:00</t>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15622,28 +15597,23 @@
       </c>
       <c r="AG133" t="b">
         <v>0</v>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125724601</v>
+        <v>125724582</v>
       </c>
       <c r="B134" t="n">
         <v>57651</v>
@@ -15678,10 +15648,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>450317</v>
+        <v>450120</v>
       </c>
       <c r="R134" t="n">
-        <v>7054857</v>
+        <v>7054703</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15718,7 +15688,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15745,7 +15715,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125724611</v>
+        <v>125724620</v>
       </c>
       <c r="B135" t="n">
         <v>57651</v>
@@ -15780,10 +15750,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>450631</v>
+        <v>450942</v>
       </c>
       <c r="R135" t="n">
-        <v>7054989</v>
+        <v>7054894</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15847,48 +15817,58 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125724582</v>
+        <v>125712965</v>
       </c>
       <c r="B136" t="n">
-        <v>57651</v>
+        <v>56843</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>450120</v>
+        <v>450279</v>
       </c>
       <c r="R136" t="n">
-        <v>7054703</v>
+        <v>7054063</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15915,14 +15895,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15933,64 +15918,74 @@
       </c>
       <c r="AG136" t="b">
         <v>0</v>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125724620</v>
+        <v>125710733</v>
       </c>
       <c r="B137" t="n">
-        <v>57651</v>
+        <v>98352</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>450942</v>
+        <v>451046</v>
       </c>
       <c r="R137" t="n">
-        <v>7054894</v>
+        <v>7054942</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16024,7 +16019,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Minst 30 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16035,16 +16030,21 @@
       </c>
       <c r="AG137" t="b">
         <v>0</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>

--- a/artfynd/A 22902-2025 artfynd.xlsx
+++ b/artfynd/A 22902-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125711912</v>
+        <v>125708514</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,47 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450518</v>
+        <v>451330</v>
       </c>
       <c r="R2" t="n">
-        <v>7054696</v>
+        <v>7055192</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,26 +743,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -781,11 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -802,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125724579</v>
+        <v>125711912</v>
       </c>
       <c r="B3" t="n">
         <v>57651</v>
@@ -831,19 +801,29 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450145</v>
+        <v>450518</v>
       </c>
       <c r="R3" t="n">
-        <v>7054502</v>
+        <v>7054696</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,14 +850,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,23 +878,28 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125714988</v>
+        <v>125724579</v>
       </c>
       <c r="B4" t="n">
         <v>57651</v>
@@ -933,26 +928,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450413</v>
+        <v>450145</v>
       </c>
       <c r="R4" t="n">
-        <v>7054149</v>
+        <v>7054502</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,24 +967,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,48 +985,23 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125724597</v>
+        <v>125714988</v>
       </c>
       <c r="B5" t="n">
         <v>57651</v>
@@ -1080,16 +1030,26 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450287</v>
+        <v>450413</v>
       </c>
       <c r="R5" t="n">
-        <v>7054787</v>
+        <v>7054149</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,14 +1079,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,23 +1107,48 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125724591</v>
+        <v>125724597</v>
       </c>
       <c r="B6" t="n">
         <v>57651</v>
@@ -1188,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450270</v>
+        <v>450287</v>
       </c>
       <c r="R6" t="n">
-        <v>7054720</v>
+        <v>7054787</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1223,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125724610</v>
+        <v>125724591</v>
       </c>
       <c r="B7" t="n">
         <v>57651</v>
@@ -1290,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>450597</v>
+        <v>450270</v>
       </c>
       <c r="R7" t="n">
-        <v>7055031</v>
+        <v>7054720</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1325,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125724629</v>
+        <v>125724610</v>
       </c>
       <c r="B8" t="n">
-        <v>91245</v>
+        <v>57651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>450502</v>
+        <v>450597</v>
       </c>
       <c r="R8" t="n">
-        <v>7054507</v>
+        <v>7055031</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,6 +1423,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,7 +1454,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125724628</v>
+        <v>125724629</v>
       </c>
       <c r="B9" t="n">
         <v>91245</v>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451229</v>
+        <v>450502</v>
       </c>
       <c r="R9" t="n">
-        <v>7055028</v>
+        <v>7054507</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125708514</v>
+        <v>125724628</v>
       </c>
       <c r="B10" t="n">
-        <v>78967</v>
+        <v>91245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1562,37 +1562,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451330</v>
+        <v>451229</v>
       </c>
       <c r="R10" t="n">
-        <v>7055192</v>
+        <v>7055028</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1636,12 +1636,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2314,43 +2314,47 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125718101</v>
+        <v>125708478</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>98352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2359,13 +2363,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451151</v>
+        <v>451306</v>
       </c>
       <c r="R17" t="n">
-        <v>7054937</v>
+        <v>7055204</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2394,7 +2398,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2404,12 +2408,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack, äldre och rejäla, längs ca 2 meter på en granstam.</t>
+          <t>Minst 6 plantor inom ca 4 m2 yta.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2423,27 +2427,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2461,45 +2445,59 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125724598</v>
+        <v>125714526</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>98352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>450292</v>
+        <v>450368</v>
       </c>
       <c r="R18" t="n">
-        <v>7054851</v>
+        <v>7054102</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2529,14 +2527,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 11 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,23 +2555,28 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125724560</v>
+        <v>125718101</v>
       </c>
       <c r="B19" t="n">
         <v>57651</v>
@@ -2592,19 +2605,29 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>450673</v>
+        <v>451151</v>
       </c>
       <c r="R19" t="n">
-        <v>7054359</v>
+        <v>7054937</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2631,14 +2654,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre och rejäla, längs ca 2 meter på en granstam.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2649,23 +2682,48 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125724547</v>
+        <v>125724598</v>
       </c>
       <c r="B20" t="n">
         <v>57651</v>
@@ -2700,10 +2758,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451006</v>
+        <v>450292</v>
       </c>
       <c r="R20" t="n">
-        <v>7054764</v>
+        <v>7054851</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2767,10 +2825,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125724635</v>
+        <v>125724560</v>
       </c>
       <c r="B21" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2778,21 +2836,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2802,10 +2860,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451002</v>
+        <v>450673</v>
       </c>
       <c r="R21" t="n">
-        <v>7055090</v>
+        <v>7054359</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2838,6 +2896,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2864,62 +2927,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125708478</v>
+        <v>125724547</v>
       </c>
       <c r="B22" t="n">
-        <v>98352</v>
+        <v>57651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451306</v>
+        <v>451006</v>
       </c>
       <c r="R22" t="n">
-        <v>7055204</v>
+        <v>7054764</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2946,24 +2995,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minst 6 plantor inom ca 4 m2 yta.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2974,80 +3013,61 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125714526</v>
+        <v>125724635</v>
       </c>
       <c r="B23" t="n">
-        <v>98352</v>
+        <v>78967</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>450368</v>
+        <v>451002</v>
       </c>
       <c r="R23" t="n">
-        <v>7054102</v>
+        <v>7055090</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3077,26 +3097,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3105,31 +3110,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125709103</v>
+        <v>125715130</v>
       </c>
       <c r="B24" t="n">
-        <v>98352</v>
+        <v>80106</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3137,51 +3137,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Slättbrännorna, Slättbrännorna, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451383</v>
+        <v>450363</v>
       </c>
       <c r="R24" t="n">
-        <v>7055475</v>
+        <v>7054211</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3208,14 +3199,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Minst 6 plantor inom ca 1 m2 yta.</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3229,7 +3230,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3247,10 +3268,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125724565</v>
+        <v>125717532</v>
       </c>
       <c r="B25" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3258,34 +3279,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450606</v>
+        <v>450948</v>
       </c>
       <c r="R25" t="n">
-        <v>7054211</v>
+        <v>7054739</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3315,14 +3336,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3333,23 +3364,48 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125712711</v>
+        <v>125724565</v>
       </c>
       <c r="B26" t="n">
         <v>57651</v>
@@ -3378,29 +3434,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450410</v>
+        <v>450606</v>
       </c>
       <c r="R26" t="n">
-        <v>7054290</v>
+        <v>7054211</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3427,24 +3473,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  nära en stor myrstack.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3455,48 +3491,23 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125724593</v>
+        <v>125712711</v>
       </c>
       <c r="B27" t="n">
         <v>57651</v>
@@ -3525,19 +3536,29 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>450274</v>
+        <v>450410</v>
       </c>
       <c r="R27" t="n">
-        <v>7054720</v>
+        <v>7054290</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3564,14 +3585,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran  nära en stor myrstack.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3582,23 +3613,48 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125724564</v>
+        <v>125724593</v>
       </c>
       <c r="B28" t="n">
         <v>57651</v>
@@ -3633,10 +3689,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>450638</v>
+        <v>450274</v>
       </c>
       <c r="R28" t="n">
-        <v>7054244</v>
+        <v>7054720</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3673,7 +3729,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3700,7 +3756,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125724574</v>
+        <v>125724564</v>
       </c>
       <c r="B29" t="n">
         <v>57651</v>
@@ -3735,10 +3791,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>450390</v>
+        <v>450638</v>
       </c>
       <c r="R29" t="n">
-        <v>7054071</v>
+        <v>7054244</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3802,7 +3858,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125724608</v>
+        <v>125724574</v>
       </c>
       <c r="B30" t="n">
         <v>57651</v>
@@ -3837,10 +3893,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>450441</v>
+        <v>450390</v>
       </c>
       <c r="R30" t="n">
-        <v>7054842</v>
+        <v>7054071</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3904,7 +3960,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125724573</v>
+        <v>125724608</v>
       </c>
       <c r="B31" t="n">
         <v>57651</v>
@@ -3939,10 +3995,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>450391</v>
+        <v>450441</v>
       </c>
       <c r="R31" t="n">
-        <v>7054076</v>
+        <v>7054842</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3979,7 +4035,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4006,7 +4062,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125724572</v>
+        <v>125724573</v>
       </c>
       <c r="B32" t="n">
         <v>57651</v>
@@ -4041,10 +4097,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>450406</v>
+        <v>450391</v>
       </c>
       <c r="R32" t="n">
-        <v>7054072</v>
+        <v>7054076</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4081,7 +4137,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4108,53 +4164,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125715130</v>
+        <v>125724572</v>
       </c>
       <c r="B33" t="n">
-        <v>80106</v>
+        <v>57651</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450363</v>
+        <v>450406</v>
       </c>
       <c r="R33" t="n">
-        <v>7054211</v>
+        <v>7054072</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4181,24 +4232,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4209,89 +4250,78 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125717532</v>
+        <v>125709103</v>
       </c>
       <c r="B34" t="n">
-        <v>78967</v>
+        <v>98352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Slättbrännorna, Slättbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>450948</v>
+        <v>451383</v>
       </c>
       <c r="R34" t="n">
-        <v>7054739</v>
+        <v>7055475</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4318,24 +4348,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 6 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4350,26 +4370,6 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4738,45 +4738,64 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125724627</v>
+        <v>125711207</v>
       </c>
       <c r="B38" t="n">
-        <v>80070</v>
+        <v>98352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450528</v>
+        <v>450852</v>
       </c>
       <c r="R38" t="n">
-        <v>7054102</v>
+        <v>7054681</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4811,6 +4830,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 17 plantor inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4819,80 +4843,66 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125711207</v>
+        <v>125724627</v>
       </c>
       <c r="B39" t="n">
-        <v>98352</v>
+        <v>80070</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>450852</v>
+        <v>450528</v>
       </c>
       <c r="R39" t="n">
-        <v>7054681</v>
+        <v>7054102</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4927,11 +4937,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Minst 17 plantor inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4940,21 +4945,16 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5695,62 +5695,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125709295</v>
+        <v>125710364</v>
       </c>
       <c r="B47" t="n">
-        <v>98352</v>
+        <v>78967</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451312</v>
+        <v>451107</v>
       </c>
       <c r="R47" t="n">
-        <v>7055388</v>
+        <v>7055032</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5784,7 +5770,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
+          <t>Gott om långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5798,7 +5784,27 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5816,10 +5822,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125710364</v>
+        <v>125724630</v>
       </c>
       <c r="B48" t="n">
-        <v>78967</v>
+        <v>91245</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5827,37 +5833,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>451107</v>
+        <v>450577</v>
       </c>
       <c r="R48" t="n">
-        <v>7055032</v>
+        <v>7054440</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5889,11 +5895,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Gott om långväxta bålar på en gran.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5902,51 +5903,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125724630</v>
+        <v>125711989</v>
       </c>
       <c r="B49" t="n">
-        <v>91245</v>
+        <v>57651</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5954,37 +5930,47 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>450577</v>
+        <v>450536</v>
       </c>
       <c r="R49" t="n">
-        <v>7054440</v>
+        <v>7054699</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6011,11 +5997,26 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6024,23 +6025,48 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125711989</v>
+        <v>125724615</v>
       </c>
       <c r="B50" t="n">
         <v>57651</v>
@@ -6069,29 +6095,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>450536</v>
+        <v>450856</v>
       </c>
       <c r="R50" t="n">
-        <v>7054699</v>
+        <v>7054955</v>
       </c>
       <c r="S50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6118,24 +6134,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6146,48 +6152,23 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125724615</v>
+        <v>125724555</v>
       </c>
       <c r="B51" t="n">
         <v>57651</v>
@@ -6222,10 +6203,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>450856</v>
+        <v>450816</v>
       </c>
       <c r="R51" t="n">
-        <v>7054955</v>
+        <v>7054432</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6289,7 +6270,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125724555</v>
+        <v>125712552</v>
       </c>
       <c r="B52" t="n">
         <v>57651</v>
@@ -6318,19 +6299,29 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>450816</v>
+        <v>450417</v>
       </c>
       <c r="R52" t="n">
-        <v>7054432</v>
+        <v>7054319</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6357,14 +6348,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6375,23 +6376,48 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125712552</v>
+        <v>125724553</v>
       </c>
       <c r="B53" t="n">
         <v>57651</v>
@@ -6420,29 +6446,19 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>450417</v>
+        <v>450713</v>
       </c>
       <c r="R53" t="n">
-        <v>7054319</v>
+        <v>7054346</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6469,24 +6485,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6497,48 +6503,23 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125724553</v>
+        <v>125724614</v>
       </c>
       <c r="B54" t="n">
         <v>57651</v>
@@ -6573,10 +6554,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>450713</v>
+        <v>450762</v>
       </c>
       <c r="R54" t="n">
-        <v>7054346</v>
+        <v>7055029</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6613,7 +6594,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6640,48 +6621,62 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125724614</v>
+        <v>125709295</v>
       </c>
       <c r="B55" t="n">
-        <v>57651</v>
+        <v>98352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>450762</v>
+        <v>451312</v>
       </c>
       <c r="R55" t="n">
-        <v>7055029</v>
+        <v>7055388</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6715,7 +6710,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6726,16 +6721,21 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -8290,10 +8290,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125716115</v>
+        <v>125715668</v>
       </c>
       <c r="B69" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8301,37 +8301,47 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>450545</v>
+        <v>450399</v>
       </c>
       <c r="R69" t="n">
-        <v>7054277</v>
+        <v>7054150</v>
       </c>
       <c r="S69" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8360,7 +8370,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8370,7 +8380,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8381,6 +8396,31 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8397,10 +8437,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125724544</v>
+        <v>125724596</v>
       </c>
       <c r="B70" t="n">
-        <v>91227</v>
+        <v>57651</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8408,21 +8448,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8432,10 +8472,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>450929</v>
+        <v>450286</v>
       </c>
       <c r="R70" t="n">
-        <v>7054588</v>
+        <v>7054789</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8468,6 +8508,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8494,62 +8539,58 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125708839</v>
+        <v>125712863</v>
       </c>
       <c r="B71" t="n">
-        <v>98352</v>
+        <v>57651</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>451394</v>
+        <v>450351</v>
       </c>
       <c r="R71" t="n">
-        <v>7055346</v>
+        <v>7054230</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8576,14 +8617,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Minst 25 plantor inom ca 2 m2.</t>
+          <t>Ringhack, äldre, på en gran nära vägen.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8597,7 +8648,27 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8615,7 +8686,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125715668</v>
+        <v>125724576</v>
       </c>
       <c r="B72" t="n">
         <v>57651</v>
@@ -8644,26 +8715,16 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>450399</v>
+        <v>450258</v>
       </c>
       <c r="R72" t="n">
-        <v>7054150</v>
+        <v>7054372</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8693,24 +8754,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8721,89 +8772,78 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125724596</v>
+        <v>125708839</v>
       </c>
       <c r="B73" t="n">
-        <v>57651</v>
+        <v>98352</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>450286</v>
+        <v>451394</v>
       </c>
       <c r="R73" t="n">
-        <v>7054789</v>
+        <v>7055346</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8837,7 +8877,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Minst 25 plantor inom ca 2 m2.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8848,26 +8888,31 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125712863</v>
+        <v>125716115</v>
       </c>
       <c r="B74" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8875,47 +8920,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>450351</v>
+        <v>450545</v>
       </c>
       <c r="R74" t="n">
-        <v>7054230</v>
+        <v>7054277</v>
       </c>
       <c r="S74" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8944,7 +8979,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8954,12 +8989,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran nära vägen.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8970,31 +9000,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9011,10 +9016,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125724576</v>
+        <v>125724544</v>
       </c>
       <c r="B75" t="n">
-        <v>57651</v>
+        <v>91227</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9022,21 +9027,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9046,10 +9051,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>450258</v>
+        <v>450929</v>
       </c>
       <c r="R75" t="n">
-        <v>7054372</v>
+        <v>7054588</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9082,11 +9087,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9113,10 +9113,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125715929</v>
+        <v>125724545</v>
       </c>
       <c r="B76" t="n">
-        <v>78967</v>
+        <v>91227</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9124,37 +9124,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>450435</v>
+        <v>450771</v>
       </c>
       <c r="R76" t="n">
-        <v>7054165</v>
+        <v>7055042</v>
       </c>
       <c r="S76" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9181,19 +9181,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>15:26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9208,22 +9198,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125724545</v>
+        <v>125715929</v>
       </c>
       <c r="B77" t="n">
-        <v>91227</v>
+        <v>78967</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9231,37 +9221,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>450771</v>
+        <v>450435</v>
       </c>
       <c r="R77" t="n">
-        <v>7055042</v>
+        <v>7054165</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9288,9 +9278,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9305,12 +9305,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9759,10 +9759,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125709469</v>
+        <v>125724569</v>
       </c>
       <c r="B82" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9770,34 +9770,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>451269</v>
+        <v>450437</v>
       </c>
       <c r="R82" t="n">
-        <v>7055329</v>
+        <v>7054064</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9832,6 +9832,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9844,19 +9849,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125724569</v>
+        <v>125724588</v>
       </c>
       <c r="B83" t="n">
         <v>57651</v>
@@ -9891,10 +9896,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>450437</v>
+        <v>450275</v>
       </c>
       <c r="R83" t="n">
-        <v>7054064</v>
+        <v>7054607</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9931,7 +9936,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9958,7 +9963,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125724588</v>
+        <v>125724568</v>
       </c>
       <c r="B84" t="n">
         <v>57651</v>
@@ -9993,10 +9998,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>450275</v>
+        <v>450530</v>
       </c>
       <c r="R84" t="n">
-        <v>7054607</v>
+        <v>7054095</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10033,7 +10038,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10060,10 +10065,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125724568</v>
+        <v>125709469</v>
       </c>
       <c r="B85" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10071,34 +10076,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>450530</v>
+        <v>451269</v>
       </c>
       <c r="R85" t="n">
-        <v>7054095</v>
+        <v>7055329</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10133,11 +10138,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10150,74 +10150,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125708960</v>
+        <v>125710745</v>
       </c>
       <c r="B86" t="n">
-        <v>98352</v>
+        <v>78967</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>451445</v>
+        <v>451035</v>
       </c>
       <c r="R86" t="n">
-        <v>7055383</v>
+        <v>7054940</v>
       </c>
       <c r="S86" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10251,7 +10237,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Minst 29 plantor inom ca 2 m2.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10266,6 +10252,26 @@
       <c r="AH86" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10283,10 +10289,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125710745</v>
+        <v>125724605</v>
       </c>
       <c r="B87" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10294,37 +10300,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>451035</v>
+        <v>450357</v>
       </c>
       <c r="R87" t="n">
-        <v>7054940</v>
+        <v>7054800</v>
       </c>
       <c r="S87" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10358,7 +10364,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10369,48 +10375,23 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125724605</v>
+        <v>125715345</v>
       </c>
       <c r="B88" t="n">
         <v>57651</v>
@@ -10439,16 +10420,26 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>450357</v>
+        <v>450372</v>
       </c>
       <c r="R88" t="n">
-        <v>7054800</v>
+        <v>7054250</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10478,14 +10469,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en död liggande gran precis öster om vägen.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10496,23 +10497,48 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125715345</v>
+        <v>125724587</v>
       </c>
       <c r="B89" t="n">
         <v>57651</v>
@@ -10541,26 +10567,16 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>450372</v>
+        <v>450279</v>
       </c>
       <c r="R89" t="n">
-        <v>7054250</v>
+        <v>7054606</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10590,24 +10606,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en död liggande gran precis öster om vägen.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10618,48 +10624,23 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125724587</v>
+        <v>125715883</v>
       </c>
       <c r="B90" t="n">
         <v>57651</v>
@@ -10688,19 +10669,29 @@
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>450279</v>
+        <v>450371</v>
       </c>
       <c r="R90" t="n">
-        <v>7054606</v>
+        <v>7054182</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10727,14 +10718,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en något smalare gran.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10745,74 +10746,103 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125715883</v>
+        <v>125708960</v>
       </c>
       <c r="B91" t="n">
-        <v>57651</v>
+        <v>98352</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>450371</v>
+        <v>451445</v>
       </c>
       <c r="R91" t="n">
-        <v>7054182</v>
+        <v>7055383</v>
       </c>
       <c r="S91" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10839,24 +10869,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en något smalare gran.</t>
+          <t>Minst 29 plantor inom ca 2 m2.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10871,26 +10891,6 @@
       <c r="AH91" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12844,10 +12844,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125712294</v>
+        <v>125712133</v>
       </c>
       <c r="B109" t="n">
-        <v>78967</v>
+        <v>58129</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12855,37 +12855,56 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>103018</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Storholmen, Storholmen, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>450461</v>
+        <v>450497</v>
       </c>
       <c r="R109" t="n">
-        <v>7054536</v>
+        <v>7054617</v>
       </c>
       <c r="S109" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12914,7 +12933,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12924,12 +12943,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>En sjungande hane i ett stråk med en del asp.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12943,27 +12962,7 @@
       </c>
       <c r="AH109" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12981,10 +12980,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125724549</v>
+        <v>125712294</v>
       </c>
       <c r="B110" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12992,37 +12991,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storholmen, Storholmen, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>450547</v>
+        <v>450461</v>
       </c>
       <c r="R110" t="n">
-        <v>7054823</v>
+        <v>7054536</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13049,14 +13048,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13067,23 +13076,48 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125724586</v>
+        <v>125724549</v>
       </c>
       <c r="B111" t="n">
         <v>57651</v>
@@ -13118,10 +13152,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>450292</v>
+        <v>450547</v>
       </c>
       <c r="R111" t="n">
-        <v>7054587</v>
+        <v>7054823</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13158,7 +13192,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13185,7 +13219,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125724558</v>
+        <v>125724586</v>
       </c>
       <c r="B112" t="n">
         <v>57651</v>
@@ -13220,10 +13254,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>450702</v>
+        <v>450292</v>
       </c>
       <c r="R112" t="n">
-        <v>7054428</v>
+        <v>7054587</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13260,7 +13294,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13287,7 +13321,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125724552</v>
+        <v>125724558</v>
       </c>
       <c r="B113" t="n">
         <v>57651</v>
@@ -13322,10 +13356,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>450545</v>
+        <v>450702</v>
       </c>
       <c r="R113" t="n">
-        <v>7054416</v>
+        <v>7054428</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13389,10 +13423,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125712133</v>
+        <v>125724552</v>
       </c>
       <c r="B114" t="n">
-        <v>58129</v>
+        <v>57651</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13400,56 +13434,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103018</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>450497</v>
+        <v>450545</v>
       </c>
       <c r="R114" t="n">
-        <v>7054617</v>
+        <v>7054416</v>
       </c>
       <c r="S114" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13476,24 +13491,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>En sjungande hane i ett stråk med en del asp.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13504,69 +13509,64 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125709665</v>
+        <v>125724559</v>
       </c>
       <c r="B115" t="n">
-        <v>80098</v>
+        <v>57651</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>451229</v>
+        <v>450487</v>
       </c>
       <c r="R115" t="n">
-        <v>7055183</v>
+        <v>7054409</v>
       </c>
       <c r="S115" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13615,22 +13615,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125712605</v>
+        <v>125712655</v>
       </c>
       <c r="B116" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13638,27 +13638,32 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -13667,13 +13672,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>450406</v>
+        <v>450387</v>
       </c>
       <c r="R116" t="n">
-        <v>7054312</v>
+        <v>7054295</v>
       </c>
       <c r="S116" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13702,7 +13707,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13712,12 +13717,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar med apothecier.</t>
+          <t>Ringhack, äldre, på en gran intill en stor myrstack.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13746,12 +13751,12 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -13769,7 +13774,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125724559</v>
+        <v>125715638</v>
       </c>
       <c r="B117" t="n">
         <v>57651</v>
@@ -13798,16 +13803,26 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>450487</v>
+        <v>450416</v>
       </c>
       <c r="R117" t="n">
-        <v>7054409</v>
+        <v>7054156</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13837,14 +13852,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13855,23 +13880,48 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125712655</v>
+        <v>125724557</v>
       </c>
       <c r="B118" t="n">
         <v>57651</v>
@@ -13900,29 +13950,19 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>450387</v>
+        <v>450772</v>
       </c>
       <c r="R118" t="n">
-        <v>7054295</v>
+        <v>7054621</v>
       </c>
       <c r="S118" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13949,24 +13989,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran intill en stor myrstack.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13977,99 +14007,64 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125715638</v>
+        <v>125709665</v>
       </c>
       <c r="B119" t="n">
-        <v>57651</v>
+        <v>80098</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>450416</v>
+        <v>451229</v>
       </c>
       <c r="R119" t="n">
-        <v>7054156</v>
+        <v>7055183</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14096,24 +14091,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14124,31 +14109,6 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
@@ -14165,10 +14125,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125724557</v>
+        <v>125712605</v>
       </c>
       <c r="B120" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14176,37 +14136,42 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>450772</v>
+        <v>450406</v>
       </c>
       <c r="R120" t="n">
-        <v>7054621</v>
+        <v>7054312</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14233,14 +14198,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14251,16 +14226,41 @@
       </c>
       <c r="AG120" t="b">
         <v>0</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>

--- a/artfynd/A 22902-2025 artfynd.xlsx
+++ b/artfynd/A 22902-2025 artfynd.xlsx
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125724585</v>
+        <v>125711059</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,34 +1659,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450232</v>
+        <v>450886</v>
       </c>
       <c r="R11" t="n">
-        <v>7054602</v>
+        <v>7054749</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,23 +1734,48 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125724599</v>
+        <v>125724585</v>
       </c>
       <c r="B12" t="n">
         <v>57651</v>
@@ -1785,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450306</v>
+        <v>450232</v>
       </c>
       <c r="R12" t="n">
-        <v>7054865</v>
+        <v>7054602</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,7 +1877,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125724592</v>
+        <v>125724599</v>
       </c>
       <c r="B13" t="n">
         <v>57651</v>
@@ -1887,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450278</v>
+        <v>450306</v>
       </c>
       <c r="R13" t="n">
-        <v>7054719</v>
+        <v>7054865</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1952,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,7 +1979,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125724619</v>
+        <v>125724592</v>
       </c>
       <c r="B14" t="n">
         <v>57651</v>
@@ -1989,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450958</v>
+        <v>450278</v>
       </c>
       <c r="R14" t="n">
-        <v>7054933</v>
+        <v>7054719</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2054,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125711059</v>
+        <v>125724619</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2067,34 +2092,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450886</v>
+        <v>450958</v>
       </c>
       <c r="R15" t="n">
-        <v>7054749</v>
+        <v>7054933</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,7 +2156,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2142,41 +2167,16 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2314,47 +2314,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125708478</v>
+        <v>125718101</v>
       </c>
       <c r="B17" t="n">
-        <v>98352</v>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2363,13 +2359,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451306</v>
+        <v>451151</v>
       </c>
       <c r="R17" t="n">
-        <v>7055204</v>
+        <v>7054937</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2398,7 +2394,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2408,12 +2404,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minst 6 plantor inom ca 4 m2 yta.</t>
+          <t>Ringhack, äldre och rejäla, längs ca 2 meter på en granstam.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2427,7 +2423,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2445,59 +2461,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125714526</v>
+        <v>125724598</v>
       </c>
       <c r="B18" t="n">
-        <v>98352</v>
+        <v>57651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>450368</v>
+        <v>450292</v>
       </c>
       <c r="R18" t="n">
-        <v>7054102</v>
+        <v>7054851</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2527,24 +2529,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 11 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2555,28 +2547,23 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125718101</v>
+        <v>125724560</v>
       </c>
       <c r="B19" t="n">
         <v>57651</v>
@@ -2605,29 +2592,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451151</v>
+        <v>450673</v>
       </c>
       <c r="R19" t="n">
-        <v>7054937</v>
+        <v>7054359</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2654,24 +2631,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, äldre och rejäla, längs ca 2 meter på en granstam.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2682,48 +2649,23 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125724598</v>
+        <v>125724547</v>
       </c>
       <c r="B20" t="n">
         <v>57651</v>
@@ -2758,10 +2700,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>450292</v>
+        <v>451006</v>
       </c>
       <c r="R20" t="n">
-        <v>7054851</v>
+        <v>7054764</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2825,10 +2767,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125724560</v>
+        <v>125724635</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2836,21 +2778,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2860,10 +2802,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>450673</v>
+        <v>451002</v>
       </c>
       <c r="R21" t="n">
-        <v>7054359</v>
+        <v>7055090</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2896,11 +2838,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2927,48 +2864,62 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125724547</v>
+        <v>125708478</v>
       </c>
       <c r="B22" t="n">
-        <v>57651</v>
+        <v>98352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451006</v>
+        <v>451306</v>
       </c>
       <c r="R22" t="n">
-        <v>7054764</v>
+        <v>7055204</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2995,14 +2946,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 6 plantor inom ca 4 m2 yta.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3013,61 +2974,80 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125724635</v>
+        <v>125714526</v>
       </c>
       <c r="B23" t="n">
-        <v>78967</v>
+        <v>98352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451002</v>
+        <v>450368</v>
       </c>
       <c r="R23" t="n">
-        <v>7055090</v>
+        <v>7054102</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3097,11 +3077,26 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3110,16 +3105,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -4738,64 +4738,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125711207</v>
+        <v>125724627</v>
       </c>
       <c r="B38" t="n">
-        <v>98352</v>
+        <v>80070</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450852</v>
+        <v>450528</v>
       </c>
       <c r="R38" t="n">
-        <v>7054681</v>
+        <v>7054102</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4830,11 +4811,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 17 plantor inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4843,66 +4819,80 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125724627</v>
+        <v>125711207</v>
       </c>
       <c r="B39" t="n">
-        <v>80070</v>
+        <v>98352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>450528</v>
+        <v>450852</v>
       </c>
       <c r="R39" t="n">
-        <v>7054102</v>
+        <v>7054681</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4937,6 +4927,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Minst 17 plantor inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4945,16 +4940,21 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5822,10 +5822,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125724630</v>
+        <v>125711989</v>
       </c>
       <c r="B48" t="n">
-        <v>91245</v>
+        <v>57651</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5833,37 +5833,47 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>450577</v>
+        <v>450536</v>
       </c>
       <c r="R48" t="n">
-        <v>7054440</v>
+        <v>7054699</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5890,11 +5900,26 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5903,23 +5928,48 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125711989</v>
+        <v>125724615</v>
       </c>
       <c r="B49" t="n">
         <v>57651</v>
@@ -5948,29 +5998,19 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>450536</v>
+        <v>450856</v>
       </c>
       <c r="R49" t="n">
-        <v>7054699</v>
+        <v>7054955</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5997,24 +6037,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6025,48 +6055,23 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125724615</v>
+        <v>125724555</v>
       </c>
       <c r="B50" t="n">
         <v>57651</v>
@@ -6101,10 +6106,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>450856</v>
+        <v>450816</v>
       </c>
       <c r="R50" t="n">
-        <v>7054955</v>
+        <v>7054432</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6168,7 +6173,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125724555</v>
+        <v>125712552</v>
       </c>
       <c r="B51" t="n">
         <v>57651</v>
@@ -6197,19 +6202,29 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>450816</v>
+        <v>450417</v>
       </c>
       <c r="R51" t="n">
-        <v>7054432</v>
+        <v>7054319</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6236,14 +6251,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6254,23 +6279,48 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125712552</v>
+        <v>125724553</v>
       </c>
       <c r="B52" t="n">
         <v>57651</v>
@@ -6299,29 +6349,19 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>450417</v>
+        <v>450713</v>
       </c>
       <c r="R52" t="n">
-        <v>7054319</v>
+        <v>7054346</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6348,24 +6388,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6376,48 +6406,23 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125724553</v>
+        <v>125724614</v>
       </c>
       <c r="B53" t="n">
         <v>57651</v>
@@ -6452,10 +6457,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>450713</v>
+        <v>450762</v>
       </c>
       <c r="R53" t="n">
-        <v>7054346</v>
+        <v>7055029</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6492,7 +6497,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6519,10 +6524,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125724614</v>
+        <v>125724630</v>
       </c>
       <c r="B54" t="n">
-        <v>57651</v>
+        <v>91245</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6530,21 +6535,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6554,10 +6559,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>450762</v>
+        <v>450577</v>
       </c>
       <c r="R54" t="n">
-        <v>7055029</v>
+        <v>7054440</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6590,11 +6595,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6742,7 +6742,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125710504</v>
+        <v>125709678</v>
       </c>
       <c r="B56" t="n">
         <v>78967</v>
@@ -6777,13 +6777,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451089</v>
+        <v>451218</v>
       </c>
       <c r="R56" t="n">
-        <v>7054989</v>
+        <v>7055148</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6815,11 +6815,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flertalet granar.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6831,7 +6826,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
@@ -6869,48 +6864,62 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125724606</v>
+        <v>125709578</v>
       </c>
       <c r="B57" t="n">
-        <v>57651</v>
+        <v>98352</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>450436</v>
+        <v>451288</v>
       </c>
       <c r="R57" t="n">
-        <v>7054836</v>
+        <v>7055288</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6944,7 +6953,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 10 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6955,26 +6964,31 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125724554</v>
+        <v>125710504</v>
       </c>
       <c r="B58" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6982,37 +6996,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>450796</v>
+        <v>451089</v>
       </c>
       <c r="R58" t="n">
-        <v>7054404</v>
+        <v>7054989</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7046,7 +7060,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7057,23 +7071,48 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125709678</v>
+        <v>125711291</v>
       </c>
       <c r="B59" t="n">
         <v>78967</v>
@@ -7108,13 +7147,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451218</v>
+        <v>450795</v>
       </c>
       <c r="R59" t="n">
-        <v>7055148</v>
+        <v>7054803</v>
       </c>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7146,6 +7185,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flertalet granar.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7157,7 +7201,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -7195,10 +7239,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125711291</v>
+        <v>125724606</v>
       </c>
       <c r="B60" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7206,37 +7250,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>450795</v>
+        <v>450436</v>
       </c>
       <c r="R60" t="n">
-        <v>7054803</v>
+        <v>7054836</v>
       </c>
       <c r="S60" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7270,7 +7314,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7281,103 +7325,64 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125709578</v>
+        <v>125724554</v>
       </c>
       <c r="B61" t="n">
-        <v>98352</v>
+        <v>57651</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>451288</v>
+        <v>450796</v>
       </c>
       <c r="R61" t="n">
-        <v>7055288</v>
+        <v>7054404</v>
       </c>
       <c r="S61" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7411,7 +7416,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Minst 10 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7422,21 +7427,16 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7930,10 +7930,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125724626</v>
+        <v>125714185</v>
       </c>
       <c r="B66" t="n">
-        <v>80070</v>
+        <v>57069</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7941,37 +7941,56 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>102961</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>450584</v>
+        <v>450224</v>
       </c>
       <c r="R66" t="n">
-        <v>7054245</v>
+        <v>7054100</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7998,9 +8017,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8015,22 +8044,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125717826</v>
+        <v>125724626</v>
       </c>
       <c r="B67" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8038,37 +8067,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>451046</v>
+        <v>450584</v>
       </c>
       <c r="R67" t="n">
-        <v>7054820</v>
+        <v>7054245</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8095,26 +8124,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Långväxta bålar i god mängd.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8123,51 +8137,26 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125714185</v>
+        <v>125717826</v>
       </c>
       <c r="B68" t="n">
-        <v>57069</v>
+        <v>78967</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8175,56 +8164,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102961</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>450224</v>
+        <v>451046</v>
       </c>
       <c r="R68" t="n">
-        <v>7054100</v>
+        <v>7054820</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8253,7 +8223,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8263,7 +8233,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Långväxta bålar i god mängd.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8274,6 +8249,31 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -9759,10 +9759,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125724569</v>
+        <v>125709469</v>
       </c>
       <c r="B82" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9770,34 +9770,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>450437</v>
+        <v>451269</v>
       </c>
       <c r="R82" t="n">
-        <v>7054064</v>
+        <v>7055329</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9832,11 +9832,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9849,19 +9844,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125724588</v>
+        <v>125724569</v>
       </c>
       <c r="B83" t="n">
         <v>57651</v>
@@ -9896,10 +9891,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>450275</v>
+        <v>450437</v>
       </c>
       <c r="R83" t="n">
-        <v>7054607</v>
+        <v>7054064</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9936,7 +9931,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9963,7 +9958,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125724568</v>
+        <v>125724588</v>
       </c>
       <c r="B84" t="n">
         <v>57651</v>
@@ -9998,10 +9993,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>450530</v>
+        <v>450275</v>
       </c>
       <c r="R84" t="n">
-        <v>7054095</v>
+        <v>7054607</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10038,7 +10033,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10065,10 +10060,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125709469</v>
+        <v>125724568</v>
       </c>
       <c r="B85" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10076,34 +10071,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>451269</v>
+        <v>450530</v>
       </c>
       <c r="R85" t="n">
-        <v>7055329</v>
+        <v>7054095</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10138,6 +10133,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10150,12 +10150,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -14023,10 +14023,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125709665</v>
+        <v>125724625</v>
       </c>
       <c r="B119" t="n">
-        <v>80098</v>
+        <v>98352</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14034,37 +14034,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6461</v>
+        <v>221952</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>451229</v>
+        <v>451414</v>
       </c>
       <c r="R119" t="n">
-        <v>7055183</v>
+        <v>7055348</v>
       </c>
       <c r="S119" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14094,11 +14094,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14113,65 +14108,60 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125712605</v>
+        <v>125709665</v>
       </c>
       <c r="B120" t="n">
-        <v>78967</v>
+        <v>80098</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>450406</v>
+        <v>451229</v>
       </c>
       <c r="R120" t="n">
-        <v>7054312</v>
+        <v>7055183</v>
       </c>
       <c r="S120" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14198,24 +14188,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar med apothecier.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14226,31 +14206,6 @@
       </c>
       <c r="AG120" t="b">
         <v>0</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
@@ -14267,48 +14222,53 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125724625</v>
+        <v>125712605</v>
       </c>
       <c r="B121" t="n">
-        <v>98352</v>
+        <v>78967</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>451414</v>
+        <v>450406</v>
       </c>
       <c r="R121" t="n">
-        <v>7055348</v>
+        <v>7054312</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14335,11 +14295,26 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Långväxta fertila bålar med apothecier.</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -14348,26 +14323,51 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125715696</v>
+        <v>125724633</v>
       </c>
       <c r="B122" t="n">
-        <v>78967</v>
+        <v>91245</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14375,37 +14375,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>450391</v>
+        <v>450636</v>
       </c>
       <c r="R122" t="n">
-        <v>7054170</v>
+        <v>7054969</v>
       </c>
       <c r="S122" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14432,21 +14432,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -14455,51 +14445,26 @@
       </c>
       <c r="AG122" t="b">
         <v>0</v>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125724571</v>
+        <v>125715696</v>
       </c>
       <c r="B123" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14507,37 +14472,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>450408</v>
+        <v>450391</v>
       </c>
       <c r="R123" t="n">
-        <v>7054064</v>
+        <v>7054170</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14564,14 +14529,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14582,23 +14552,48 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125724616</v>
+        <v>125724571</v>
       </c>
       <c r="B124" t="n">
         <v>57651</v>
@@ -14633,10 +14628,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>450858</v>
+        <v>450408</v>
       </c>
       <c r="R124" t="n">
-        <v>7054949</v>
+        <v>7054064</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14673,7 +14668,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14700,7 +14695,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125724612</v>
+        <v>125724616</v>
       </c>
       <c r="B125" t="n">
         <v>57651</v>
@@ -14735,10 +14730,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>450636</v>
+        <v>450858</v>
       </c>
       <c r="R125" t="n">
-        <v>7054958</v>
+        <v>7054949</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14775,7 +14770,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14802,7 +14797,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125724602</v>
+        <v>125724612</v>
       </c>
       <c r="B126" t="n">
         <v>57651</v>
@@ -14837,10 +14832,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>450307</v>
+        <v>450636</v>
       </c>
       <c r="R126" t="n">
-        <v>7054854</v>
+        <v>7054958</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14877,7 +14872,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14904,7 +14899,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125724548</v>
+        <v>125724602</v>
       </c>
       <c r="B127" t="n">
         <v>57651</v>
@@ -14939,10 +14934,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>450973</v>
+        <v>450307</v>
       </c>
       <c r="R127" t="n">
-        <v>7054710</v>
+        <v>7054854</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14979,7 +14974,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15006,7 +15001,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125724617</v>
+        <v>125724548</v>
       </c>
       <c r="B128" t="n">
         <v>57651</v>
@@ -15041,10 +15036,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>450851</v>
+        <v>450973</v>
       </c>
       <c r="R128" t="n">
-        <v>7054937</v>
+        <v>7054710</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15108,7 +15103,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125724623</v>
+        <v>125724617</v>
       </c>
       <c r="B129" t="n">
         <v>57651</v>
@@ -15143,10 +15138,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>451200</v>
+        <v>450851</v>
       </c>
       <c r="R129" t="n">
-        <v>7055401</v>
+        <v>7054937</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15210,10 +15205,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125724633</v>
+        <v>125724623</v>
       </c>
       <c r="B130" t="n">
-        <v>91245</v>
+        <v>57651</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15221,21 +15216,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15245,10 +15240,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>450636</v>
+        <v>451200</v>
       </c>
       <c r="R130" t="n">
-        <v>7054969</v>
+        <v>7055401</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15281,6 +15276,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD130" t="b">

--- a/artfynd/A 22902-2025 artfynd.xlsx
+++ b/artfynd/A 22902-2025 artfynd.xlsx
@@ -4961,10 +4961,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125724631</v>
+        <v>125724580</v>
       </c>
       <c r="B40" t="n">
-        <v>91246</v>
+        <v>57651</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4972,21 +4972,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4996,10 +4996,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>450196</v>
+        <v>450072</v>
       </c>
       <c r="R40" t="n">
-        <v>7054664</v>
+        <v>7054712</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5032,6 +5032,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5058,7 +5063,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125724580</v>
+        <v>125724594</v>
       </c>
       <c r="B41" t="n">
         <v>57651</v>
@@ -5093,10 +5098,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>450072</v>
+        <v>450285</v>
       </c>
       <c r="R41" t="n">
-        <v>7054712</v>
+        <v>7054794</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5160,7 +5165,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125724594</v>
+        <v>125724556</v>
       </c>
       <c r="B42" t="n">
         <v>57651</v>
@@ -5195,10 +5200,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>450285</v>
+        <v>450878</v>
       </c>
       <c r="R42" t="n">
-        <v>7054794</v>
+        <v>7054550</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5262,10 +5267,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125724556</v>
+        <v>125724631</v>
       </c>
       <c r="B43" t="n">
-        <v>57651</v>
+        <v>91246</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5273,21 +5278,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5297,10 +5302,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>450878</v>
+        <v>450196</v>
       </c>
       <c r="R43" t="n">
-        <v>7054550</v>
+        <v>7054664</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5333,11 +5338,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -8290,62 +8290,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125708839</v>
+        <v>125724544</v>
       </c>
       <c r="B69" t="n">
-        <v>98355</v>
+        <v>91228</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>451394</v>
+        <v>450929</v>
       </c>
       <c r="R69" t="n">
-        <v>7055346</v>
+        <v>7054588</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8377,11 +8363,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor inom ca 2 m2.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8390,69 +8371,78 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125724544</v>
+        <v>125708839</v>
       </c>
       <c r="B70" t="n">
-        <v>91228</v>
+        <v>98355</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>450929</v>
+        <v>451394</v>
       </c>
       <c r="R70" t="n">
-        <v>7054588</v>
+        <v>7055346</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8484,6 +8474,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor inom ca 2 m2.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8492,16 +8487,21 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -10162,62 +10162,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125708960</v>
+        <v>125710745</v>
       </c>
       <c r="B86" t="n">
-        <v>98355</v>
+        <v>78968</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>451445</v>
+        <v>451035</v>
       </c>
       <c r="R86" t="n">
-        <v>7055383</v>
+        <v>7054940</v>
       </c>
       <c r="S86" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10251,7 +10237,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Minst 29 plantor inom ca 2 m2.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10266,6 +10252,26 @@
       <c r="AH86" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10781,48 +10787,62 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125710745</v>
+        <v>125708960</v>
       </c>
       <c r="B91" t="n">
-        <v>78968</v>
+        <v>98355</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>451035</v>
+        <v>451445</v>
       </c>
       <c r="R91" t="n">
-        <v>7054940</v>
+        <v>7055383</v>
       </c>
       <c r="S91" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10856,7 +10876,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 29 plantor inom ca 2 m2.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10871,26 +10891,6 @@
       <c r="AH91" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11496,10 +11496,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125715109</v>
+        <v>125724609</v>
       </c>
       <c r="B97" t="n">
-        <v>80072</v>
+        <v>57651</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11507,39 +11507,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>450365</v>
+        <v>450581</v>
       </c>
       <c r="R97" t="n">
-        <v>7054197</v>
+        <v>7055012</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11569,24 +11564,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11597,51 +11582,26 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125709922</v>
+        <v>125724546</v>
       </c>
       <c r="B98" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11649,37 +11609,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>451225</v>
+        <v>451102</v>
       </c>
       <c r="R98" t="n">
-        <v>7055093</v>
+        <v>7054896</v>
       </c>
       <c r="S98" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11713,7 +11673,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11724,31 +11684,26 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125718221</v>
+        <v>125724566</v>
       </c>
       <c r="B99" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11756,37 +11711,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>451172</v>
+        <v>450600</v>
       </c>
       <c r="R99" t="n">
-        <v>7054946</v>
+        <v>7054142</v>
       </c>
       <c r="S99" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11813,19 +11768,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>17:06</t>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11840,19 +11790,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125724609</v>
+        <v>125724551</v>
       </c>
       <c r="B100" t="n">
         <v>57651</v>
@@ -11887,10 +11837,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>450581</v>
+        <v>450486</v>
       </c>
       <c r="R100" t="n">
-        <v>7055012</v>
+        <v>7054445</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11954,7 +11904,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125724546</v>
+        <v>125724621</v>
       </c>
       <c r="B101" t="n">
         <v>57651</v>
@@ -11989,10 +11939,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>451102</v>
+        <v>450933</v>
       </c>
       <c r="R101" t="n">
-        <v>7054896</v>
+        <v>7054883</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12029,7 +11979,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12056,7 +12006,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125724566</v>
+        <v>125715238</v>
       </c>
       <c r="B102" t="n">
         <v>57651</v>
@@ -12085,16 +12035,26 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>450600</v>
+        <v>450342</v>
       </c>
       <c r="R102" t="n">
-        <v>7054142</v>
+        <v>7054212</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12124,14 +12084,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran  precis öster om vägen.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12142,23 +12112,48 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125724551</v>
+        <v>125724618</v>
       </c>
       <c r="B103" t="n">
         <v>57651</v>
@@ -12193,10 +12188,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>450486</v>
+        <v>450905</v>
       </c>
       <c r="R103" t="n">
-        <v>7054445</v>
+        <v>7054898</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12260,7 +12255,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125724621</v>
+        <v>125724577</v>
       </c>
       <c r="B104" t="n">
         <v>57651</v>
@@ -12295,10 +12290,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>450933</v>
+        <v>450259</v>
       </c>
       <c r="R104" t="n">
-        <v>7054883</v>
+        <v>7054380</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12335,7 +12330,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12362,10 +12357,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125715238</v>
+        <v>125715109</v>
       </c>
       <c r="B105" t="n">
-        <v>57651</v>
+        <v>80072</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12373,32 +12368,27 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -12407,10 +12397,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>450342</v>
+        <v>450365</v>
       </c>
       <c r="R105" t="n">
-        <v>7054212</v>
+        <v>7054197</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12442,7 +12432,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12452,12 +12442,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  precis öster om vägen.</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12476,22 +12466,22 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12509,10 +12499,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125724618</v>
+        <v>125709922</v>
       </c>
       <c r="B106" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12520,37 +12510,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>450905</v>
+        <v>451225</v>
       </c>
       <c r="R106" t="n">
-        <v>7054898</v>
+        <v>7055093</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12584,7 +12574,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12595,26 +12585,31 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125724577</v>
+        <v>125718221</v>
       </c>
       <c r="B107" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12622,37 +12617,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>450259</v>
+        <v>451172</v>
       </c>
       <c r="R107" t="n">
-        <v>7054380</v>
+        <v>7054946</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12679,14 +12674,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12701,12 +12701,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -12844,10 +12844,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125724549</v>
+        <v>125712294</v>
       </c>
       <c r="B109" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12855,37 +12855,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storholmen, Storholmen, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>450547</v>
+        <v>450461</v>
       </c>
       <c r="R109" t="n">
-        <v>7054823</v>
+        <v>7054536</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12912,14 +12912,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12930,23 +12940,48 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125724586</v>
+        <v>125724549</v>
       </c>
       <c r="B110" t="n">
         <v>57651</v>
@@ -12981,10 +13016,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>450292</v>
+        <v>450547</v>
       </c>
       <c r="R110" t="n">
-        <v>7054587</v>
+        <v>7054823</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13021,7 +13056,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13048,7 +13083,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125724558</v>
+        <v>125724586</v>
       </c>
       <c r="B111" t="n">
         <v>57651</v>
@@ -13083,10 +13118,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>450702</v>
+        <v>450292</v>
       </c>
       <c r="R111" t="n">
-        <v>7054428</v>
+        <v>7054587</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13123,7 +13158,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13150,7 +13185,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125724552</v>
+        <v>125724558</v>
       </c>
       <c r="B112" t="n">
         <v>57651</v>
@@ -13185,10 +13220,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>450545</v>
+        <v>450702</v>
       </c>
       <c r="R112" t="n">
-        <v>7054416</v>
+        <v>7054428</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13252,10 +13287,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125712294</v>
+        <v>125724552</v>
       </c>
       <c r="B113" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13263,37 +13298,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Storholmen, Storholmen, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>450461</v>
+        <v>450545</v>
       </c>
       <c r="R113" t="n">
-        <v>7054536</v>
+        <v>7054416</v>
       </c>
       <c r="S113" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13320,24 +13355,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13348,41 +13373,16 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -13525,48 +13525,53 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125709665</v>
+        <v>125712605</v>
       </c>
       <c r="B115" t="n">
-        <v>80099</v>
+        <v>78968</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>451229</v>
+        <v>450406</v>
       </c>
       <c r="R115" t="n">
-        <v>7055183</v>
+        <v>7054312</v>
       </c>
       <c r="S115" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13593,14 +13598,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13611,6 +13626,31 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
@@ -13627,53 +13667,48 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125712605</v>
+        <v>125724625</v>
       </c>
       <c r="B116" t="n">
-        <v>78968</v>
+        <v>98355</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>450406</v>
+        <v>451414</v>
       </c>
       <c r="R116" t="n">
-        <v>7054312</v>
+        <v>7055348</v>
       </c>
       <c r="S116" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13700,26 +13735,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Långväxta fertila bålar med apothecier.</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
@@ -13728,41 +13748,16 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -13871,58 +13866,48 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125712655</v>
+        <v>125709665</v>
       </c>
       <c r="B118" t="n">
-        <v>57651</v>
+        <v>80099</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>450387</v>
+        <v>451229</v>
       </c>
       <c r="R118" t="n">
-        <v>7054295</v>
+        <v>7055183</v>
       </c>
       <c r="S118" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13949,24 +13934,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran intill en stor myrstack.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13977,31 +13952,6 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
@@ -14018,7 +13968,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125715638</v>
+        <v>125712655</v>
       </c>
       <c r="B119" t="n">
         <v>57651</v>
@@ -14063,13 +14013,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>450416</v>
+        <v>450387</v>
       </c>
       <c r="R119" t="n">
-        <v>7054156</v>
+        <v>7054295</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14098,7 +14048,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14108,12 +14058,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack, äldre, på en gran intill en stor myrstack.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14165,7 +14115,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125724557</v>
+        <v>125715638</v>
       </c>
       <c r="B120" t="n">
         <v>57651</v>
@@ -14194,16 +14144,26 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>450772</v>
+        <v>450416</v>
       </c>
       <c r="R120" t="n">
-        <v>7054621</v>
+        <v>7054156</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14233,14 +14193,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14251,48 +14221,73 @@
       </c>
       <c r="AG120" t="b">
         <v>0</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125724625</v>
+        <v>125724557</v>
       </c>
       <c r="B121" t="n">
-        <v>98355</v>
+        <v>57651</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14302,10 +14297,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>451414</v>
+        <v>450772</v>
       </c>
       <c r="R121" t="n">
-        <v>7055348</v>
+        <v>7054621</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14338,6 +14333,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD121" t="b">

--- a/artfynd/A 22902-2025 artfynd.xlsx
+++ b/artfynd/A 22902-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125724629</v>
+        <v>125711912</v>
       </c>
       <c r="B2" t="n">
-        <v>91246</v>
+        <v>57651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450502</v>
+        <v>450518</v>
       </c>
       <c r="R2" t="n">
-        <v>7054507</v>
+        <v>7054696</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,11 +753,26 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -756,26 +781,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125724628</v>
+        <v>125724579</v>
       </c>
       <c r="B3" t="n">
-        <v>91246</v>
+        <v>57651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451229</v>
+        <v>450145</v>
       </c>
       <c r="R3" t="n">
-        <v>7055028</v>
+        <v>7054502</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +873,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125708514</v>
+        <v>125714988</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,37 +915,47 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451330</v>
+        <v>450413</v>
       </c>
       <c r="R4" t="n">
-        <v>7055192</v>
+        <v>7054149</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -937,11 +982,26 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -950,6 +1010,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -966,7 +1051,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125711912</v>
+        <v>125724597</v>
       </c>
       <c r="B5" t="n">
         <v>57651</v>
@@ -995,29 +1080,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450518</v>
+        <v>450287</v>
       </c>
       <c r="R5" t="n">
-        <v>7054696</v>
+        <v>7054787</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1044,24 +1119,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1072,28 +1137,23 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125724579</v>
+        <v>125724591</v>
       </c>
       <c r="B6" t="n">
         <v>57651</v>
@@ -1128,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450145</v>
+        <v>450270</v>
       </c>
       <c r="R6" t="n">
-        <v>7054502</v>
+        <v>7054720</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1228,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125714988</v>
+        <v>125724610</v>
       </c>
       <c r="B7" t="n">
         <v>57651</v>
@@ -1224,26 +1284,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>450413</v>
+        <v>450597</v>
       </c>
       <c r="R7" t="n">
-        <v>7054149</v>
+        <v>7055031</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,24 +1323,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,51 +1341,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125724597</v>
+        <v>125708514</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,37 +1368,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>450287</v>
+        <v>451330</v>
       </c>
       <c r="R8" t="n">
-        <v>7054787</v>
+        <v>7055192</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,11 +1428,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,22 +1442,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125724591</v>
+        <v>125724629</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>91250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,21 +1465,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>450270</v>
+        <v>450502</v>
       </c>
       <c r="R9" t="n">
-        <v>7054720</v>
+        <v>7054507</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,11 +1525,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125724610</v>
+        <v>125724628</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>91250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,21 +1562,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450597</v>
+        <v>451229</v>
       </c>
       <c r="R10" t="n">
-        <v>7055031</v>
+        <v>7055028</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,11 +1622,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125711059</v>
+        <v>125712265</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>57811</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,37 +1659,51 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Storholmen, Storholmen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450886</v>
+        <v>450456</v>
       </c>
       <c r="R11" t="n">
-        <v>7054749</v>
+        <v>7054618</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1716,14 +1730,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Locklätet av en talltita observerades i lämplig häckmiljö.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1738,26 +1762,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2183,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125712265</v>
+        <v>125711059</v>
       </c>
       <c r="B16" t="n">
-        <v>57811</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,51 +2198,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storholmen, Storholmen, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>450456</v>
+        <v>450886</v>
       </c>
       <c r="R16" t="n">
-        <v>7054618</v>
+        <v>7054749</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2265,24 +2255,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Locklätet av en talltita observerades i lämplig häckmiljö.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2297,6 +2277,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2314,10 +2314,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125724635</v>
+        <v>125718101</v>
       </c>
       <c r="B17" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,37 +2325,47 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451002</v>
+        <v>451151</v>
       </c>
       <c r="R17" t="n">
-        <v>7055090</v>
+        <v>7054937</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2382,11 +2392,26 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre och rejäla, längs ca 2 meter på en granstam.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2395,78 +2420,89 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125708478</v>
+        <v>125724598</v>
       </c>
       <c r="B18" t="n">
-        <v>98355</v>
+        <v>57651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451306</v>
+        <v>450292</v>
       </c>
       <c r="R18" t="n">
-        <v>7055204</v>
+        <v>7054851</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2493,24 +2529,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 6 plantor inom ca 4 m2 yta.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2521,80 +2547,61 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125714526</v>
+        <v>125724560</v>
       </c>
       <c r="B19" t="n">
-        <v>98355</v>
+        <v>57651</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>450368</v>
+        <v>450673</v>
       </c>
       <c r="R19" t="n">
-        <v>7054102</v>
+        <v>7054359</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2624,24 +2631,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Minst 11 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2652,28 +2649,23 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125718101</v>
+        <v>125724547</v>
       </c>
       <c r="B20" t="n">
         <v>57651</v>
@@ -2702,29 +2694,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451151</v>
+        <v>451006</v>
       </c>
       <c r="R20" t="n">
-        <v>7054937</v>
+        <v>7054764</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2751,24 +2733,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack, äldre och rejäla, längs ca 2 meter på en granstam.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2779,86 +2751,75 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125724598</v>
+        <v>125714526</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>98359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>450292</v>
+        <v>450368</v>
       </c>
       <c r="R21" t="n">
-        <v>7054851</v>
+        <v>7054102</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2888,14 +2849,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 11 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2906,64 +2877,83 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125724560</v>
+        <v>125708478</v>
       </c>
       <c r="B22" t="n">
-        <v>57651</v>
+        <v>98359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>450673</v>
+        <v>451306</v>
       </c>
       <c r="R22" t="n">
-        <v>7054359</v>
+        <v>7055204</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2990,14 +2980,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 6 plantor inom ca 4 m2 yta.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3008,26 +3008,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125724547</v>
+        <v>125724635</v>
       </c>
       <c r="B23" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3035,21 +3040,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3059,10 +3064,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451006</v>
+        <v>451002</v>
       </c>
       <c r="R23" t="n">
-        <v>7054764</v>
+        <v>7055090</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3095,11 +3100,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3129,7 +3129,7 @@
         <v>125715130</v>
       </c>
       <c r="B24" t="n">
-        <v>80107</v>
+        <v>80111</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3268,48 +3268,62 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125717532</v>
+        <v>125709103</v>
       </c>
       <c r="B25" t="n">
-        <v>78968</v>
+        <v>98359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Slättbrännorna, Slättbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450948</v>
+        <v>451383</v>
       </c>
       <c r="R25" t="n">
-        <v>7054739</v>
+        <v>7055475</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3336,24 +3350,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 6 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3368,26 +3372,6 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3405,10 +3389,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125724565</v>
+        <v>125717532</v>
       </c>
       <c r="B26" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3416,34 +3400,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450606</v>
+        <v>450948</v>
       </c>
       <c r="R26" t="n">
-        <v>7054211</v>
+        <v>7054739</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3473,14 +3457,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3491,23 +3485,48 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125712711</v>
+        <v>125724565</v>
       </c>
       <c r="B27" t="n">
         <v>57651</v>
@@ -3536,29 +3555,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>450410</v>
+        <v>450606</v>
       </c>
       <c r="R27" t="n">
-        <v>7054290</v>
+        <v>7054211</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3585,24 +3594,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  nära en stor myrstack.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3613,48 +3612,23 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125724593</v>
+        <v>125712711</v>
       </c>
       <c r="B28" t="n">
         <v>57651</v>
@@ -3683,19 +3657,29 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>450274</v>
+        <v>450410</v>
       </c>
       <c r="R28" t="n">
-        <v>7054720</v>
+        <v>7054290</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3722,14 +3706,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran  nära en stor myrstack.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3740,23 +3734,48 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125724564</v>
+        <v>125724593</v>
       </c>
       <c r="B29" t="n">
         <v>57651</v>
@@ -3791,10 +3810,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>450638</v>
+        <v>450274</v>
       </c>
       <c r="R29" t="n">
-        <v>7054244</v>
+        <v>7054720</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3831,7 +3850,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3858,7 +3877,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125724574</v>
+        <v>125724564</v>
       </c>
       <c r="B30" t="n">
         <v>57651</v>
@@ -3893,10 +3912,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>450390</v>
+        <v>450638</v>
       </c>
       <c r="R30" t="n">
-        <v>7054071</v>
+        <v>7054244</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3960,7 +3979,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125724608</v>
+        <v>125724574</v>
       </c>
       <c r="B31" t="n">
         <v>57651</v>
@@ -3995,10 +4014,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>450441</v>
+        <v>450390</v>
       </c>
       <c r="R31" t="n">
-        <v>7054842</v>
+        <v>7054071</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4062,7 +4081,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125724573</v>
+        <v>125724608</v>
       </c>
       <c r="B32" t="n">
         <v>57651</v>
@@ -4097,10 +4116,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>450391</v>
+        <v>450441</v>
       </c>
       <c r="R32" t="n">
-        <v>7054076</v>
+        <v>7054842</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4137,7 +4156,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4164,7 +4183,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125724572</v>
+        <v>125724573</v>
       </c>
       <c r="B33" t="n">
         <v>57651</v>
@@ -4199,10 +4218,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450406</v>
+        <v>450391</v>
       </c>
       <c r="R33" t="n">
-        <v>7054072</v>
+        <v>7054076</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4239,7 +4258,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4266,62 +4285,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125709103</v>
+        <v>125724572</v>
       </c>
       <c r="B34" t="n">
-        <v>98355</v>
+        <v>57651</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Slättbrännorna, Slättbrännorna, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451383</v>
+        <v>450406</v>
       </c>
       <c r="R34" t="n">
-        <v>7055475</v>
+        <v>7054072</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4355,7 +4360,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Minst 6 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4366,59 +4371,63 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125716595</v>
+        <v>125711207</v>
       </c>
       <c r="B35" t="n">
-        <v>57651</v>
+        <v>98359</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4428,14 +4437,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>450481</v>
+        <v>450852</v>
       </c>
       <c r="R35" t="n">
-        <v>7054352</v>
+        <v>7054681</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4465,24 +4474,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
+          <t>Minst 17 plantor inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4497,26 +4496,6 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4534,7 +4513,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125724603</v>
+        <v>125716595</v>
       </c>
       <c r="B36" t="n">
         <v>57651</v>
@@ -4563,16 +4542,26 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>450339</v>
+        <v>450481</v>
       </c>
       <c r="R36" t="n">
-        <v>7054827</v>
+        <v>7054352</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4602,14 +4591,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4620,23 +4619,48 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125724613</v>
+        <v>125724603</v>
       </c>
       <c r="B37" t="n">
         <v>57651</v>
@@ -4671,10 +4695,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>450714</v>
+        <v>450339</v>
       </c>
       <c r="R37" t="n">
-        <v>7055072</v>
+        <v>7054827</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4711,7 +4735,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4738,10 +4762,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125724627</v>
+        <v>125724613</v>
       </c>
       <c r="B38" t="n">
-        <v>80071</v>
+        <v>57651</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4749,21 +4773,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4773,10 +4797,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450528</v>
+        <v>450714</v>
       </c>
       <c r="R38" t="n">
-        <v>7054102</v>
+        <v>7055072</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4809,6 +4833,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4835,64 +4864,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125711207</v>
+        <v>125724627</v>
       </c>
       <c r="B39" t="n">
-        <v>98355</v>
+        <v>80075</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>450852</v>
+        <v>450528</v>
       </c>
       <c r="R39" t="n">
-        <v>7054681</v>
+        <v>7054102</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4927,11 +4937,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Minst 17 plantor inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4940,31 +4945,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125724580</v>
+        <v>125708223</v>
       </c>
       <c r="B40" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4972,37 +4972,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>450072</v>
+        <v>451292</v>
       </c>
       <c r="R40" t="n">
-        <v>7054712</v>
+        <v>7055142</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5029,14 +5029,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5047,26 +5052,51 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125724594</v>
+        <v>125715396</v>
       </c>
       <c r="B41" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5074,37 +5104,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>450285</v>
+        <v>450394</v>
       </c>
       <c r="R41" t="n">
-        <v>7054794</v>
+        <v>7054235</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5134,11 +5164,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5153,22 +5178,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125724556</v>
+        <v>125710168</v>
       </c>
       <c r="B42" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5176,37 +5201,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>450878</v>
+        <v>451182</v>
       </c>
       <c r="R42" t="n">
-        <v>7054550</v>
+        <v>7055004</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5240,7 +5265,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5255,12 +5280,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5270,7 +5295,7 @@
         <v>125724631</v>
       </c>
       <c r="B43" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5364,10 +5389,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125708223</v>
+        <v>125724580</v>
       </c>
       <c r="B44" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5375,37 +5400,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>451292</v>
+        <v>450072</v>
       </c>
       <c r="R44" t="n">
-        <v>7055142</v>
+        <v>7054712</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5432,19 +5457,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>09:34</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5455,51 +5475,26 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125715396</v>
+        <v>125724594</v>
       </c>
       <c r="B45" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5507,37 +5502,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>450394</v>
+        <v>450285</v>
       </c>
       <c r="R45" t="n">
-        <v>7054235</v>
+        <v>7054794</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5567,6 +5562,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5581,22 +5581,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125710168</v>
+        <v>125724556</v>
       </c>
       <c r="B46" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5604,37 +5604,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>451182</v>
+        <v>450878</v>
       </c>
       <c r="R46" t="n">
-        <v>7055004</v>
+        <v>7054550</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5683,12 +5683,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5698,7 +5698,7 @@
         <v>125709295</v>
       </c>
       <c r="B47" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5816,10 +5816,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125724630</v>
+        <v>125710364</v>
       </c>
       <c r="B48" t="n">
-        <v>91246</v>
+        <v>78972</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5827,37 +5827,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>450577</v>
+        <v>451107</v>
       </c>
       <c r="R48" t="n">
-        <v>7054440</v>
+        <v>7055032</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5889,6 +5889,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Gott om långväxta bålar på en gran.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5897,26 +5902,51 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125710364</v>
+        <v>125724630</v>
       </c>
       <c r="B49" t="n">
-        <v>78968</v>
+        <v>91250</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5924,37 +5954,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>451107</v>
+        <v>450577</v>
       </c>
       <c r="R49" t="n">
-        <v>7055032</v>
+        <v>7054440</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5986,11 +6016,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Gott om långväxta bålar på en gran.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5999,41 +6024,16 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6745,7 +6745,7 @@
         <v>125709578</v>
       </c>
       <c r="B56" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6863,10 +6863,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125724606</v>
+        <v>125709678</v>
       </c>
       <c r="B57" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6874,37 +6874,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>450436</v>
+        <v>451218</v>
       </c>
       <c r="R57" t="n">
-        <v>7054836</v>
+        <v>7055148</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6936,11 +6936,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6949,26 +6944,51 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125724554</v>
+        <v>125710504</v>
       </c>
       <c r="B58" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6976,37 +6996,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>450796</v>
+        <v>451089</v>
       </c>
       <c r="R58" t="n">
-        <v>7054404</v>
+        <v>7054989</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7040,7 +7060,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7051,26 +7071,51 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125709678</v>
+        <v>125711291</v>
       </c>
       <c r="B59" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7102,13 +7147,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451218</v>
+        <v>450795</v>
       </c>
       <c r="R59" t="n">
-        <v>7055148</v>
+        <v>7054803</v>
       </c>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7140,6 +7185,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flertalet granar.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7151,7 +7201,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -7189,10 +7239,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125710504</v>
+        <v>125724606</v>
       </c>
       <c r="B60" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7200,37 +7250,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>451089</v>
+        <v>450436</v>
       </c>
       <c r="R60" t="n">
-        <v>7054989</v>
+        <v>7054836</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7264,7 +7314,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7275,51 +7325,26 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125711291</v>
+        <v>125724554</v>
       </c>
       <c r="B61" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7327,37 +7352,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>450795</v>
+        <v>450796</v>
       </c>
       <c r="R61" t="n">
-        <v>7054803</v>
+        <v>7054404</v>
       </c>
       <c r="S61" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7391,7 +7416,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7402,41 +7427,16 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7446,7 +7446,7 @@
         <v>125716316</v>
       </c>
       <c r="B62" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>125711118</v>
       </c>
       <c r="B63" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7701,10 +7701,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125724634</v>
+        <v>125714547</v>
       </c>
       <c r="B64" t="n">
-        <v>91246</v>
+        <v>78972</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7712,37 +7712,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>451148</v>
+        <v>450361</v>
       </c>
       <c r="R64" t="n">
-        <v>7055327</v>
+        <v>7054101</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7769,11 +7769,21 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7782,26 +7792,51 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125714547</v>
+        <v>125724634</v>
       </c>
       <c r="B65" t="n">
-        <v>78968</v>
+        <v>91250</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7809,37 +7844,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>450361</v>
+        <v>451148</v>
       </c>
       <c r="R65" t="n">
-        <v>7054101</v>
+        <v>7055327</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7866,21 +7901,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7889,51 +7914,26 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125724626</v>
+        <v>125717826</v>
       </c>
       <c r="B66" t="n">
-        <v>80071</v>
+        <v>78972</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7941,37 +7941,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>450584</v>
+        <v>451046</v>
       </c>
       <c r="R66" t="n">
-        <v>7054245</v>
+        <v>7054820</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7998,11 +7998,26 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Långväxta bålar i god mängd.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8011,26 +8026,51 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125717826</v>
+        <v>125714185</v>
       </c>
       <c r="B67" t="n">
-        <v>78968</v>
+        <v>57069</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8038,37 +8078,56 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>102961</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>451046</v>
+        <v>450224</v>
       </c>
       <c r="R67" t="n">
-        <v>7054820</v>
+        <v>7054100</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8097,7 +8156,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8107,12 +8166,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Långväxta bålar i god mängd.</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8123,31 +8177,6 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8164,10 +8193,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125714185</v>
+        <v>125724626</v>
       </c>
       <c r="B68" t="n">
-        <v>57069</v>
+        <v>80075</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8175,56 +8204,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102961</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>450224</v>
+        <v>450584</v>
       </c>
       <c r="R68" t="n">
-        <v>7054100</v>
+        <v>7054245</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8251,19 +8261,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8278,22 +8278,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125724544</v>
+        <v>125716115</v>
       </c>
       <c r="B69" t="n">
-        <v>91228</v>
+        <v>78972</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8301,37 +8301,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>450929</v>
+        <v>450545</v>
       </c>
       <c r="R69" t="n">
-        <v>7054588</v>
+        <v>7054277</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8358,9 +8358,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8375,74 +8385,70 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125708839</v>
+        <v>125715668</v>
       </c>
       <c r="B70" t="n">
-        <v>98355</v>
+        <v>57651</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>451394</v>
+        <v>450399</v>
       </c>
       <c r="R70" t="n">
-        <v>7055346</v>
+        <v>7054150</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8469,14 +8475,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Minst 25 plantor inom ca 2 m2.</t>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8490,7 +8506,27 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8508,10 +8544,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125716115</v>
+        <v>125724596</v>
       </c>
       <c r="B71" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8519,37 +8555,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>450545</v>
+        <v>450286</v>
       </c>
       <c r="R71" t="n">
-        <v>7054277</v>
+        <v>7054789</v>
       </c>
       <c r="S71" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8576,19 +8612,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>15:34</t>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8603,19 +8634,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125715668</v>
+        <v>125712863</v>
       </c>
       <c r="B72" t="n">
         <v>57651</v>
@@ -8660,13 +8691,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>450399</v>
+        <v>450351</v>
       </c>
       <c r="R72" t="n">
-        <v>7054150</v>
+        <v>7054230</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8695,7 +8726,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8705,12 +8736,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+          <t>Ringhack, äldre, på en gran nära vägen.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8762,7 +8793,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125724596</v>
+        <v>125724576</v>
       </c>
       <c r="B73" t="n">
         <v>57651</v>
@@ -8797,10 +8828,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>450286</v>
+        <v>450258</v>
       </c>
       <c r="R73" t="n">
-        <v>7054789</v>
+        <v>7054372</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8837,7 +8868,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8864,58 +8895,62 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125712863</v>
+        <v>125708839</v>
       </c>
       <c r="B74" t="n">
-        <v>57651</v>
+        <v>98359</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>450351</v>
+        <v>451394</v>
       </c>
       <c r="R74" t="n">
-        <v>7054230</v>
+        <v>7055346</v>
       </c>
       <c r="S74" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8942,24 +8977,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran nära vägen.</t>
+          <t>Minst 25 plantor inom ca 2 m2.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8973,27 +8998,7 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9011,10 +9016,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125724576</v>
+        <v>125724544</v>
       </c>
       <c r="B75" t="n">
-        <v>57651</v>
+        <v>91232</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9022,21 +9027,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9046,10 +9051,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>450258</v>
+        <v>450929</v>
       </c>
       <c r="R75" t="n">
-        <v>7054372</v>
+        <v>7054588</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9082,11 +9087,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9113,10 +9113,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125715929</v>
+        <v>125724545</v>
       </c>
       <c r="B76" t="n">
-        <v>78968</v>
+        <v>91232</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9124,37 +9124,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>450435</v>
+        <v>450771</v>
       </c>
       <c r="R76" t="n">
-        <v>7054165</v>
+        <v>7055042</v>
       </c>
       <c r="S76" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9181,19 +9181,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>15:26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9208,79 +9198,60 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125718167</v>
+        <v>125715929</v>
       </c>
       <c r="B77" t="n">
-        <v>98355</v>
+        <v>78972</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>451146</v>
+        <v>450435</v>
       </c>
       <c r="R77" t="n">
-        <v>7054932</v>
+        <v>7054165</v>
       </c>
       <c r="S77" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9309,7 +9280,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9319,12 +9290,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>17:03</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Minst 14 plantor inom ca 1 m2.</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9335,11 +9301,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9356,48 +9317,67 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125724545</v>
+        <v>125718167</v>
       </c>
       <c r="B78" t="n">
-        <v>91228</v>
+        <v>98359</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>450771</v>
+        <v>451146</v>
       </c>
       <c r="R78" t="n">
-        <v>7055042</v>
+        <v>7054932</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9424,11 +9404,26 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Minst 14 plantor inom ca 1 m2.</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9437,16 +9432,21 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9759,10 +9759,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125709469</v>
+        <v>125724568</v>
       </c>
       <c r="B82" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9770,34 +9770,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>451269</v>
+        <v>450530</v>
       </c>
       <c r="R82" t="n">
-        <v>7055329</v>
+        <v>7054095</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9832,6 +9832,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9844,22 +9849,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125724569</v>
+        <v>125709469</v>
       </c>
       <c r="B83" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9867,34 +9872,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>450437</v>
+        <v>451269</v>
       </c>
       <c r="R83" t="n">
-        <v>7054064</v>
+        <v>7055329</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9929,11 +9934,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9946,19 +9946,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125724588</v>
+        <v>125724569</v>
       </c>
       <c r="B84" t="n">
         <v>57651</v>
@@ -9993,10 +9993,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>450275</v>
+        <v>450437</v>
       </c>
       <c r="R84" t="n">
-        <v>7054607</v>
+        <v>7054064</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10060,7 +10060,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125724568</v>
+        <v>125724588</v>
       </c>
       <c r="B85" t="n">
         <v>57651</v>
@@ -10095,10 +10095,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>450530</v>
+        <v>450275</v>
       </c>
       <c r="R85" t="n">
-        <v>7054095</v>
+        <v>7054607</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10165,7 +10165,7 @@
         <v>125710745</v>
       </c>
       <c r="B86" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>125708960</v>
       </c>
       <c r="B91" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>125724543</v>
       </c>
       <c r="B92" t="n">
-        <v>91586</v>
+        <v>91590</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11108,62 +11108,62 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125714169</v>
+        <v>125708590</v>
       </c>
       <c r="B94" t="n">
-        <v>57811</v>
+        <v>98359</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>450226</v>
+        <v>451359</v>
       </c>
       <c r="R94" t="n">
-        <v>7054095</v>
+        <v>7055225</v>
       </c>
       <c r="S94" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11202,7 +11202,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 3 m2.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11216,7 +11221,7 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11234,10 +11239,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125708590</v>
+        <v>125710515</v>
       </c>
       <c r="B95" t="n">
-        <v>98355</v>
+        <v>58020</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11245,36 +11250,41 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221952</v>
+        <v>103015</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -11283,13 +11293,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>451359</v>
+        <v>451089</v>
       </c>
       <c r="R95" t="n">
-        <v>7055225</v>
+        <v>7054975</v>
       </c>
       <c r="S95" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11318,7 +11328,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11328,12 +11338,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 3 m2.</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11365,32 +11370,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125710515</v>
+        <v>125714169</v>
       </c>
       <c r="B96" t="n">
-        <v>58020</v>
+        <v>57811</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -11398,14 +11403,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>451089</v>
+        <v>450226</v>
       </c>
       <c r="R96" t="n">
-        <v>7054975</v>
+        <v>7054095</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11496,45 +11496,59 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125724609</v>
+        <v>125712767</v>
       </c>
       <c r="B97" t="n">
-        <v>57651</v>
+        <v>98359</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>450581</v>
+        <v>450391</v>
       </c>
       <c r="R97" t="n">
-        <v>7055012</v>
+        <v>7054281</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11564,14 +11578,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 20 plantor inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11582,26 +11606,31 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125724546</v>
+        <v>125718221</v>
       </c>
       <c r="B98" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11609,37 +11638,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>451102</v>
+        <v>451172</v>
       </c>
       <c r="R98" t="n">
-        <v>7054896</v>
+        <v>7054946</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11666,14 +11695,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11688,22 +11722,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125724566</v>
+        <v>125709922</v>
       </c>
       <c r="B99" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11711,37 +11745,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>450600</v>
+        <v>451225</v>
       </c>
       <c r="R99" t="n">
-        <v>7054142</v>
+        <v>7055093</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11775,7 +11809,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11786,26 +11820,31 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125724551</v>
+        <v>125715109</v>
       </c>
       <c r="B100" t="n">
-        <v>57651</v>
+        <v>80076</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11813,34 +11852,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>450486</v>
+        <v>450365</v>
       </c>
       <c r="R100" t="n">
-        <v>7054445</v>
+        <v>7054197</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11870,14 +11914,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11888,23 +11942,48 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125724621</v>
+        <v>125724609</v>
       </c>
       <c r="B101" t="n">
         <v>57651</v>
@@ -11939,10 +12018,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>450933</v>
+        <v>450581</v>
       </c>
       <c r="R101" t="n">
-        <v>7054883</v>
+        <v>7055012</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11979,7 +12058,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12006,7 +12085,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125715238</v>
+        <v>125724546</v>
       </c>
       <c r="B102" t="n">
         <v>57651</v>
@@ -12035,26 +12114,16 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>450342</v>
+        <v>451102</v>
       </c>
       <c r="R102" t="n">
-        <v>7054212</v>
+        <v>7054896</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12084,24 +12153,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  precis öster om vägen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12112,48 +12171,23 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125724618</v>
+        <v>125724566</v>
       </c>
       <c r="B103" t="n">
         <v>57651</v>
@@ -12188,10 +12222,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>450905</v>
+        <v>450600</v>
       </c>
       <c r="R103" t="n">
-        <v>7054898</v>
+        <v>7054142</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12255,7 +12289,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125724577</v>
+        <v>125724551</v>
       </c>
       <c r="B104" t="n">
         <v>57651</v>
@@ -12290,10 +12324,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>450259</v>
+        <v>450486</v>
       </c>
       <c r="R104" t="n">
-        <v>7054380</v>
+        <v>7054445</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12357,10 +12391,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125715109</v>
+        <v>125724621</v>
       </c>
       <c r="B105" t="n">
-        <v>80072</v>
+        <v>57651</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12368,39 +12402,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>450365</v>
+        <v>450933</v>
       </c>
       <c r="R105" t="n">
-        <v>7054197</v>
+        <v>7054883</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12430,24 +12459,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12458,51 +12477,26 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125709922</v>
+        <v>125715238</v>
       </c>
       <c r="B106" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12510,37 +12504,47 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>451225</v>
+        <v>450342</v>
       </c>
       <c r="R106" t="n">
-        <v>7055093</v>
+        <v>7054212</v>
       </c>
       <c r="S106" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12567,14 +12571,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack, äldre, på stambasen av en gran  precis öster om vägen.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12589,6 +12603,26 @@
       <c r="AH106" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -12606,10 +12640,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125718221</v>
+        <v>125724618</v>
       </c>
       <c r="B107" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12617,37 +12651,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>451172</v>
+        <v>450905</v>
       </c>
       <c r="R107" t="n">
-        <v>7054946</v>
+        <v>7054898</v>
       </c>
       <c r="S107" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12674,19 +12708,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>17:06</t>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12701,71 +12730,57 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125712767</v>
+        <v>125724577</v>
       </c>
       <c r="B108" t="n">
-        <v>98355</v>
+        <v>57651</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>450391</v>
+        <v>450259</v>
       </c>
       <c r="R108" t="n">
-        <v>7054281</v>
+        <v>7054380</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12795,24 +12810,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Minst 20 plantor inom ca 2 m2 yta.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12823,31 +12828,26 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125712294</v>
+        <v>125712133</v>
       </c>
       <c r="B109" t="n">
-        <v>78968</v>
+        <v>58130</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12855,37 +12855,56 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>103018</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Storholmen, Storholmen, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>450461</v>
+        <v>450497</v>
       </c>
       <c r="R109" t="n">
-        <v>7054536</v>
+        <v>7054617</v>
       </c>
       <c r="S109" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12914,7 +12933,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12924,12 +12943,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>En sjungande hane i ett stråk med en del asp.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12943,27 +12962,7 @@
       </c>
       <c r="AH109" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12981,10 +12980,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125724549</v>
+        <v>125712294</v>
       </c>
       <c r="B110" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12992,37 +12991,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storholmen, Storholmen, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>450547</v>
+        <v>450461</v>
       </c>
       <c r="R110" t="n">
-        <v>7054823</v>
+        <v>7054536</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13049,14 +13048,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13067,23 +13076,48 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125724586</v>
+        <v>125724549</v>
       </c>
       <c r="B111" t="n">
         <v>57651</v>
@@ -13118,10 +13152,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>450292</v>
+        <v>450547</v>
       </c>
       <c r="R111" t="n">
-        <v>7054587</v>
+        <v>7054823</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13158,7 +13192,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13185,7 +13219,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125724558</v>
+        <v>125724586</v>
       </c>
       <c r="B112" t="n">
         <v>57651</v>
@@ -13220,10 +13254,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>450702</v>
+        <v>450292</v>
       </c>
       <c r="R112" t="n">
-        <v>7054428</v>
+        <v>7054587</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13260,7 +13294,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13287,7 +13321,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125724552</v>
+        <v>125724558</v>
       </c>
       <c r="B113" t="n">
         <v>57651</v>
@@ -13322,10 +13356,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>450545</v>
+        <v>450702</v>
       </c>
       <c r="R113" t="n">
-        <v>7054416</v>
+        <v>7054428</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13389,10 +13423,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125712133</v>
+        <v>125724552</v>
       </c>
       <c r="B114" t="n">
-        <v>58130</v>
+        <v>57651</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13400,56 +13434,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103018</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>450497</v>
+        <v>450545</v>
       </c>
       <c r="R114" t="n">
-        <v>7054617</v>
+        <v>7054416</v>
       </c>
       <c r="S114" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13476,24 +13491,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>En sjungande hane i ett stråk med en del asp.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13504,74 +13509,64 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125712605</v>
+        <v>125724625</v>
       </c>
       <c r="B115" t="n">
-        <v>78968</v>
+        <v>98359</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>450406</v>
+        <v>451414</v>
       </c>
       <c r="R115" t="n">
-        <v>7054312</v>
+        <v>7055348</v>
       </c>
       <c r="S115" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13598,26 +13593,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Långväxta fertila bålar med apothecier.</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
@@ -13626,51 +13606,26 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
-      </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125724625</v>
+        <v>125709665</v>
       </c>
       <c r="B116" t="n">
-        <v>98355</v>
+        <v>80103</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13678,37 +13633,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>451414</v>
+        <v>451229</v>
       </c>
       <c r="R116" t="n">
-        <v>7055348</v>
+        <v>7055183</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13738,6 +13693,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13752,22 +13712,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125724559</v>
+        <v>125712605</v>
       </c>
       <c r="B117" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13775,37 +13735,42 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>450487</v>
+        <v>450406</v>
       </c>
       <c r="R117" t="n">
-        <v>7054409</v>
+        <v>7054312</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13832,14 +13797,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13850,64 +13825,89 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125709665</v>
+        <v>125724559</v>
       </c>
       <c r="B118" t="n">
-        <v>80099</v>
+        <v>57651</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>451229</v>
+        <v>450487</v>
       </c>
       <c r="R118" t="n">
-        <v>7055183</v>
+        <v>7054409</v>
       </c>
       <c r="S118" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13956,12 +13956,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -14367,7 +14367,7 @@
         <v>125724633</v>
       </c>
       <c r="B122" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>125715696</v>
       </c>
       <c r="B123" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>125710733</v>
       </c>
       <c r="B137" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16639,10 +16639,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126056423</v>
+        <v>126056436</v>
       </c>
       <c r="B142" t="n">
-        <v>57651</v>
+        <v>91250</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16650,21 +16650,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16674,10 +16674,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>450419</v>
+        <v>450342</v>
       </c>
       <c r="R142" t="n">
-        <v>7054568</v>
+        <v>7054358</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16710,11 +16710,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16741,10 +16736,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126056436</v>
+        <v>126056424</v>
       </c>
       <c r="B143" t="n">
-        <v>91246</v>
+        <v>57651</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16752,21 +16747,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16776,10 +16771,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>450342</v>
+        <v>450341</v>
       </c>
       <c r="R143" t="n">
-        <v>7054358</v>
+        <v>7054692</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16812,6 +16807,11 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16838,7 +16838,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126056424</v>
+        <v>126056423</v>
       </c>
       <c r="B144" t="n">
         <v>57651</v>
@@ -16873,10 +16873,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>450341</v>
+        <v>450419</v>
       </c>
       <c r="R144" t="n">
-        <v>7054692</v>
+        <v>7054568</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16913,7 +16913,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17144,7 +17144,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126056426</v>
+        <v>126056430</v>
       </c>
       <c r="B147" t="n">
         <v>57651</v>
@@ -17179,10 +17179,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>450282</v>
+        <v>450288</v>
       </c>
       <c r="R147" t="n">
-        <v>7054477</v>
+        <v>7054354</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17246,7 +17246,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126056430</v>
+        <v>126056426</v>
       </c>
       <c r="B148" t="n">
         <v>57651</v>
@@ -17281,10 +17281,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>450288</v>
+        <v>450282</v>
       </c>
       <c r="R148" t="n">
-        <v>7054354</v>
+        <v>7054477</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17321,7 +17321,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17351,7 +17351,7 @@
         <v>126056432</v>
       </c>
       <c r="B149" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>126056434</v>
       </c>
       <c r="B150" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>126056435</v>
       </c>
       <c r="B152" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>126056433</v>
       </c>
       <c r="B156" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>126056431</v>
       </c>
       <c r="B160" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 22902-2025 artfynd.xlsx
+++ b/artfynd/A 22902-2025 artfynd.xlsx
@@ -3126,53 +3126,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125715130</v>
+        <v>125717532</v>
       </c>
       <c r="B24" t="n">
-        <v>80111</v>
+        <v>78972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>450363</v>
+        <v>450948</v>
       </c>
       <c r="R24" t="n">
-        <v>7054211</v>
+        <v>7054739</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3201,7 +3196,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3211,12 +3206,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3230,27 +3225,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3268,10 +3263,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125709103</v>
+        <v>125715130</v>
       </c>
       <c r="B25" t="n">
-        <v>98359</v>
+        <v>80111</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3279,51 +3274,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Slättbrännorna, Slättbrännorna, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451383</v>
+        <v>450363</v>
       </c>
       <c r="R25" t="n">
-        <v>7055475</v>
+        <v>7054211</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3350,14 +3336,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Minst 6 plantor inom ca 1 m2 yta.</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3371,7 +3367,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3389,10 +3405,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125717532</v>
+        <v>125724565</v>
       </c>
       <c r="B26" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3400,34 +3416,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450948</v>
+        <v>450606</v>
       </c>
       <c r="R26" t="n">
-        <v>7054739</v>
+        <v>7054211</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3457,24 +3473,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3485,48 +3491,23 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125724565</v>
+        <v>125712711</v>
       </c>
       <c r="B27" t="n">
         <v>57651</v>
@@ -3555,19 +3536,29 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>450606</v>
+        <v>450410</v>
       </c>
       <c r="R27" t="n">
-        <v>7054211</v>
+        <v>7054290</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3594,14 +3585,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran  nära en stor myrstack.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3612,23 +3613,48 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125712711</v>
+        <v>125724593</v>
       </c>
       <c r="B28" t="n">
         <v>57651</v>
@@ -3657,29 +3683,19 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>450410</v>
+        <v>450274</v>
       </c>
       <c r="R28" t="n">
-        <v>7054290</v>
+        <v>7054720</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3706,24 +3722,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  nära en stor myrstack.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3734,48 +3740,23 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125724593</v>
+        <v>125724564</v>
       </c>
       <c r="B29" t="n">
         <v>57651</v>
@@ -3810,10 +3791,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>450274</v>
+        <v>450638</v>
       </c>
       <c r="R29" t="n">
-        <v>7054720</v>
+        <v>7054244</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3850,7 +3831,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3877,7 +3858,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125724564</v>
+        <v>125724574</v>
       </c>
       <c r="B30" t="n">
         <v>57651</v>
@@ -3912,10 +3893,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>450638</v>
+        <v>450390</v>
       </c>
       <c r="R30" t="n">
-        <v>7054244</v>
+        <v>7054071</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3979,7 +3960,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125724574</v>
+        <v>125724608</v>
       </c>
       <c r="B31" t="n">
         <v>57651</v>
@@ -4014,10 +3995,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>450390</v>
+        <v>450441</v>
       </c>
       <c r="R31" t="n">
-        <v>7054071</v>
+        <v>7054842</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4081,7 +4062,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125724608</v>
+        <v>125724573</v>
       </c>
       <c r="B32" t="n">
         <v>57651</v>
@@ -4116,10 +4097,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>450441</v>
+        <v>450391</v>
       </c>
       <c r="R32" t="n">
-        <v>7054842</v>
+        <v>7054076</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4156,7 +4137,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4183,7 +4164,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125724573</v>
+        <v>125724572</v>
       </c>
       <c r="B33" t="n">
         <v>57651</v>
@@ -4218,10 +4199,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450391</v>
+        <v>450406</v>
       </c>
       <c r="R33" t="n">
-        <v>7054076</v>
+        <v>7054072</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4258,7 +4239,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4285,48 +4266,62 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125724572</v>
+        <v>125709103</v>
       </c>
       <c r="B34" t="n">
-        <v>57651</v>
+        <v>98359</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Slättbrännorna, Slättbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>450406</v>
+        <v>451383</v>
       </c>
       <c r="R34" t="n">
-        <v>7054072</v>
+        <v>7055475</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4360,7 +4355,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 6 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4371,16 +4366,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -6742,62 +6742,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125709578</v>
+        <v>125709678</v>
       </c>
       <c r="B56" t="n">
-        <v>98359</v>
+        <v>78972</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451288</v>
+        <v>451218</v>
       </c>
       <c r="R56" t="n">
-        <v>7055288</v>
+        <v>7055148</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6829,11 +6815,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6846,6 +6827,26 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -6863,7 +6864,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125709678</v>
+        <v>125710504</v>
       </c>
       <c r="B57" t="n">
         <v>78972</v>
@@ -6898,13 +6899,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451218</v>
+        <v>451089</v>
       </c>
       <c r="R57" t="n">
-        <v>7055148</v>
+        <v>7054989</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6936,6 +6937,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flertalet granar.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6947,7 +6953,7 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -6985,7 +6991,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125710504</v>
+        <v>125711291</v>
       </c>
       <c r="B58" t="n">
         <v>78972</v>
@@ -7020,13 +7026,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451089</v>
+        <v>450795</v>
       </c>
       <c r="R58" t="n">
-        <v>7054989</v>
+        <v>7054803</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7112,10 +7118,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125711291</v>
+        <v>125724606</v>
       </c>
       <c r="B59" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7123,37 +7129,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>450795</v>
+        <v>450436</v>
       </c>
       <c r="R59" t="n">
-        <v>7054803</v>
+        <v>7054836</v>
       </c>
       <c r="S59" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7187,7 +7193,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7198,48 +7204,23 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125724606</v>
+        <v>125724554</v>
       </c>
       <c r="B60" t="n">
         <v>57651</v>
@@ -7274,10 +7255,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>450436</v>
+        <v>450796</v>
       </c>
       <c r="R60" t="n">
-        <v>7054836</v>
+        <v>7054404</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7314,7 +7295,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7341,48 +7322,62 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125724554</v>
+        <v>125709578</v>
       </c>
       <c r="B61" t="n">
-        <v>57651</v>
+        <v>98359</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>450796</v>
+        <v>451288</v>
       </c>
       <c r="R61" t="n">
-        <v>7054404</v>
+        <v>7055288</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7416,7 +7411,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Minst 10 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7427,78 +7422,74 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125716316</v>
+        <v>125711118</v>
       </c>
       <c r="B62" t="n">
-        <v>98359</v>
+        <v>80076</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>450483</v>
+        <v>450865</v>
       </c>
       <c r="R62" t="n">
-        <v>7054352</v>
+        <v>7054734</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7525,19 +7516,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:44</t>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På nedfallen död gren av sälg.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7551,7 +7537,27 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7569,10 +7575,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125711118</v>
+        <v>125714547</v>
       </c>
       <c r="B63" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7580,39 +7586,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>450865</v>
+        <v>450361</v>
       </c>
       <c r="R63" t="n">
-        <v>7054734</v>
+        <v>7054101</v>
       </c>
       <c r="S63" t="n">
         <v>8</v>
@@ -7642,14 +7643,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>På nedfallen död gren av sälg.</t>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7663,27 +7669,27 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7701,10 +7707,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125714547</v>
+        <v>125724634</v>
       </c>
       <c r="B64" t="n">
-        <v>78972</v>
+        <v>91250</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7712,37 +7718,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>450361</v>
+        <v>451148</v>
       </c>
       <c r="R64" t="n">
-        <v>7054101</v>
+        <v>7055327</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7769,21 +7775,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7792,86 +7788,75 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125724634</v>
+        <v>125716316</v>
       </c>
       <c r="B65" t="n">
-        <v>91250</v>
+        <v>98359</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>451148</v>
+        <v>450483</v>
       </c>
       <c r="R65" t="n">
-        <v>7055327</v>
+        <v>7054352</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7901,11 +7886,21 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7914,16 +7909,21 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8290,48 +8290,62 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125716115</v>
+        <v>125708839</v>
       </c>
       <c r="B69" t="n">
-        <v>78972</v>
+        <v>98359</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>450545</v>
+        <v>451394</v>
       </c>
       <c r="R69" t="n">
-        <v>7054277</v>
+        <v>7055346</v>
       </c>
       <c r="S69" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8358,19 +8372,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>15:34</t>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor inom ca 2 m2.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8381,6 +8390,11 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8397,10 +8411,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125715668</v>
+        <v>125724544</v>
       </c>
       <c r="B70" t="n">
-        <v>57651</v>
+        <v>91232</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8408,44 +8422,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>450399</v>
+        <v>450929</v>
       </c>
       <c r="R70" t="n">
-        <v>7054150</v>
+        <v>7054588</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8475,26 +8479,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8503,51 +8492,26 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125724596</v>
+        <v>125716115</v>
       </c>
       <c r="B71" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8555,37 +8519,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>450286</v>
+        <v>450545</v>
       </c>
       <c r="R71" t="n">
-        <v>7054789</v>
+        <v>7054277</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8612,14 +8576,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8634,19 +8603,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125712863</v>
+        <v>125715668</v>
       </c>
       <c r="B72" t="n">
         <v>57651</v>
@@ -8691,13 +8660,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>450351</v>
+        <v>450399</v>
       </c>
       <c r="R72" t="n">
-        <v>7054230</v>
+        <v>7054150</v>
       </c>
       <c r="S72" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8726,7 +8695,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8736,12 +8705,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran nära vägen.</t>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8793,7 +8762,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125724576</v>
+        <v>125724596</v>
       </c>
       <c r="B73" t="n">
         <v>57651</v>
@@ -8828,10 +8797,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>450258</v>
+        <v>450286</v>
       </c>
       <c r="R73" t="n">
-        <v>7054372</v>
+        <v>7054789</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8868,7 +8837,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8895,62 +8864,58 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125708839</v>
+        <v>125712863</v>
       </c>
       <c r="B74" t="n">
-        <v>98359</v>
+        <v>57651</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>451394</v>
+        <v>450351</v>
       </c>
       <c r="R74" t="n">
-        <v>7055346</v>
+        <v>7054230</v>
       </c>
       <c r="S74" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8977,14 +8942,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Minst 25 plantor inom ca 2 m2.</t>
+          <t>Ringhack, äldre, på en gran nära vägen.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8998,7 +8973,27 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9016,10 +9011,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125724544</v>
+        <v>125724576</v>
       </c>
       <c r="B75" t="n">
-        <v>91232</v>
+        <v>57651</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9027,21 +9022,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9051,10 +9046,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>450929</v>
+        <v>450258</v>
       </c>
       <c r="R75" t="n">
-        <v>7054588</v>
+        <v>7054372</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9087,6 +9082,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9759,7 +9759,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125724568</v>
+        <v>125724569</v>
       </c>
       <c r="B82" t="n">
         <v>57651</v>
@@ -9794,10 +9794,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>450530</v>
+        <v>450437</v>
       </c>
       <c r="R82" t="n">
-        <v>7054095</v>
+        <v>7054064</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9861,10 +9861,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125709469</v>
+        <v>125724588</v>
       </c>
       <c r="B83" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9872,34 +9872,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>451269</v>
+        <v>450275</v>
       </c>
       <c r="R83" t="n">
-        <v>7055329</v>
+        <v>7054607</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9934,6 +9934,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9946,19 +9951,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125724569</v>
+        <v>125724568</v>
       </c>
       <c r="B84" t="n">
         <v>57651</v>
@@ -9993,10 +9998,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>450437</v>
+        <v>450530</v>
       </c>
       <c r="R84" t="n">
-        <v>7054064</v>
+        <v>7054095</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10060,10 +10065,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125724588</v>
+        <v>125709469</v>
       </c>
       <c r="B85" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10071,34 +10076,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>450275</v>
+        <v>451269</v>
       </c>
       <c r="R85" t="n">
-        <v>7054607</v>
+        <v>7055329</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10133,11 +10138,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10150,60 +10150,74 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125710745</v>
+        <v>125708960</v>
       </c>
       <c r="B86" t="n">
-        <v>78972</v>
+        <v>98359</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>451035</v>
+        <v>451445</v>
       </c>
       <c r="R86" t="n">
-        <v>7054940</v>
+        <v>7055383</v>
       </c>
       <c r="S86" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10237,7 +10251,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 29 plantor inom ca 2 m2.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10252,26 +10266,6 @@
       <c r="AH86" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10289,10 +10283,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125724605</v>
+        <v>125710745</v>
       </c>
       <c r="B87" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10300,37 +10294,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>450357</v>
+        <v>451035</v>
       </c>
       <c r="R87" t="n">
-        <v>7054800</v>
+        <v>7054940</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10364,7 +10358,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10375,23 +10369,48 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125715345</v>
+        <v>125724605</v>
       </c>
       <c r="B88" t="n">
         <v>57651</v>
@@ -10420,26 +10439,16 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>450372</v>
+        <v>450357</v>
       </c>
       <c r="R88" t="n">
-        <v>7054250</v>
+        <v>7054800</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10469,24 +10478,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en död liggande gran precis öster om vägen.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10497,48 +10496,23 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125724587</v>
+        <v>125715345</v>
       </c>
       <c r="B89" t="n">
         <v>57651</v>
@@ -10567,16 +10541,26 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>450279</v>
+        <v>450372</v>
       </c>
       <c r="R89" t="n">
-        <v>7054606</v>
+        <v>7054250</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10606,14 +10590,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en död liggande gran precis öster om vägen.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10624,23 +10618,48 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125715883</v>
+        <v>125724587</v>
       </c>
       <c r="B90" t="n">
         <v>57651</v>
@@ -10669,29 +10688,19 @@
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>450371</v>
+        <v>450279</v>
       </c>
       <c r="R90" t="n">
-        <v>7054182</v>
+        <v>7054606</v>
       </c>
       <c r="S90" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10718,24 +10727,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en något smalare gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10746,103 +10745,74 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125708960</v>
+        <v>125715883</v>
       </c>
       <c r="B91" t="n">
-        <v>98359</v>
+        <v>57651</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>451445</v>
+        <v>450371</v>
       </c>
       <c r="R91" t="n">
-        <v>7055383</v>
+        <v>7054182</v>
       </c>
       <c r="S91" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10869,14 +10839,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Minst 29 plantor inom ca 2 m2.</t>
+          <t>Ringhack, äldre, på stambasen av en något smalare gran.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10891,6 +10871,26 @@
       <c r="AH91" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10908,32 +10908,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125724543</v>
+        <v>125724622</v>
       </c>
       <c r="B92" t="n">
-        <v>91590</v>
+        <v>57651</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10943,10 +10943,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>450931</v>
+        <v>450935</v>
       </c>
       <c r="R92" t="n">
-        <v>7054587</v>
+        <v>7055227</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10981,13 +10981,17 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -11006,32 +11010,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125724622</v>
+        <v>125724543</v>
       </c>
       <c r="B93" t="n">
-        <v>57651</v>
+        <v>91590</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11041,10 +11045,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>450935</v>
+        <v>450931</v>
       </c>
       <c r="R93" t="n">
-        <v>7055227</v>
+        <v>7054587</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11079,17 +11083,13 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -11108,10 +11108,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125708590</v>
+        <v>125710515</v>
       </c>
       <c r="B94" t="n">
-        <v>98359</v>
+        <v>58020</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11119,36 +11119,41 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221952</v>
+        <v>103015</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11157,13 +11162,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>451359</v>
+        <v>451089</v>
       </c>
       <c r="R94" t="n">
-        <v>7055225</v>
+        <v>7054975</v>
       </c>
       <c r="S94" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11192,7 +11197,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11202,12 +11207,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 3 m2.</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11239,32 +11239,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125710515</v>
+        <v>125714169</v>
       </c>
       <c r="B95" t="n">
-        <v>58020</v>
+        <v>57811</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -11272,14 +11272,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -11289,17 +11284,17 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>451089</v>
+        <v>450226</v>
       </c>
       <c r="R95" t="n">
-        <v>7054975</v>
+        <v>7054095</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11328,7 +11323,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11338,7 +11333,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11352,7 +11347,7 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11370,62 +11365,62 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125714169</v>
+        <v>125708590</v>
       </c>
       <c r="B96" t="n">
-        <v>57811</v>
+        <v>98359</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>450226</v>
+        <v>451359</v>
       </c>
       <c r="R96" t="n">
-        <v>7054095</v>
+        <v>7055225</v>
       </c>
       <c r="S96" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11454,7 +11449,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11464,7 +11459,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 3 m2.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12844,10 +12844,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125712133</v>
+        <v>125712294</v>
       </c>
       <c r="B109" t="n">
-        <v>58130</v>
+        <v>78972</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12855,56 +12855,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103018</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Storholmen, Storholmen, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>450497</v>
+        <v>450461</v>
       </c>
       <c r="R109" t="n">
-        <v>7054617</v>
+        <v>7054536</v>
       </c>
       <c r="S109" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12933,7 +12914,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12943,12 +12924,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>En sjungande hane i ett stråk med en del asp.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12962,7 +12943,27 @@
       </c>
       <c r="AH109" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12980,10 +12981,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125712294</v>
+        <v>125724549</v>
       </c>
       <c r="B110" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12991,37 +12992,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Storholmen, Storholmen, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>450461</v>
+        <v>450547</v>
       </c>
       <c r="R110" t="n">
-        <v>7054536</v>
+        <v>7054823</v>
       </c>
       <c r="S110" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13048,24 +13049,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13076,48 +13067,23 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125724549</v>
+        <v>125724586</v>
       </c>
       <c r="B111" t="n">
         <v>57651</v>
@@ -13152,10 +13118,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>450547</v>
+        <v>450292</v>
       </c>
       <c r="R111" t="n">
-        <v>7054823</v>
+        <v>7054587</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13192,7 +13158,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13219,7 +13185,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125724586</v>
+        <v>125724558</v>
       </c>
       <c r="B112" t="n">
         <v>57651</v>
@@ -13254,10 +13220,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>450292</v>
+        <v>450702</v>
       </c>
       <c r="R112" t="n">
-        <v>7054587</v>
+        <v>7054428</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13294,7 +13260,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13321,7 +13287,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125724558</v>
+        <v>125724552</v>
       </c>
       <c r="B113" t="n">
         <v>57651</v>
@@ -13356,10 +13322,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>450702</v>
+        <v>450545</v>
       </c>
       <c r="R113" t="n">
-        <v>7054428</v>
+        <v>7054416</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13423,10 +13389,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125724552</v>
+        <v>125712133</v>
       </c>
       <c r="B114" t="n">
-        <v>57651</v>
+        <v>58130</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13434,37 +13400,56 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>103018</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>450545</v>
+        <v>450497</v>
       </c>
       <c r="R114" t="n">
-        <v>7054416</v>
+        <v>7054617</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13491,14 +13476,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>En sjungande hane i ett stråk med en del asp.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13509,26 +13504,31 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125724625</v>
+        <v>125709665</v>
       </c>
       <c r="B115" t="n">
-        <v>98359</v>
+        <v>80103</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13536,37 +13536,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>451414</v>
+        <v>451229</v>
       </c>
       <c r="R115" t="n">
-        <v>7055348</v>
+        <v>7055183</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13596,6 +13596,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13610,60 +13615,65 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125709665</v>
+        <v>125712605</v>
       </c>
       <c r="B116" t="n">
-        <v>80103</v>
+        <v>78972</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>451229</v>
+        <v>450406</v>
       </c>
       <c r="R116" t="n">
-        <v>7055183</v>
+        <v>7054312</v>
       </c>
       <c r="S116" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13690,14 +13700,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13708,6 +13728,31 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
@@ -13724,10 +13769,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125712605</v>
+        <v>125724559</v>
       </c>
       <c r="B117" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13735,42 +13780,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>450406</v>
+        <v>450487</v>
       </c>
       <c r="R117" t="n">
-        <v>7054312</v>
+        <v>7054409</v>
       </c>
       <c r="S117" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13797,24 +13837,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar med apothecier.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13825,48 +13855,23 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125724559</v>
+        <v>125712655</v>
       </c>
       <c r="B118" t="n">
         <v>57651</v>
@@ -13895,19 +13900,29 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>450487</v>
+        <v>450387</v>
       </c>
       <c r="R118" t="n">
-        <v>7054409</v>
+        <v>7054295</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13934,14 +13949,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gran intill en stor myrstack.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13952,23 +13977,48 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125712655</v>
+        <v>125715638</v>
       </c>
       <c r="B119" t="n">
         <v>57651</v>
@@ -14013,13 +14063,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>450387</v>
+        <v>450416</v>
       </c>
       <c r="R119" t="n">
-        <v>7054295</v>
+        <v>7054156</v>
       </c>
       <c r="S119" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14048,7 +14098,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14058,12 +14108,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran intill en stor myrstack.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14115,7 +14165,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125715638</v>
+        <v>125724557</v>
       </c>
       <c r="B120" t="n">
         <v>57651</v>
@@ -14144,26 +14194,16 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>450416</v>
+        <v>450772</v>
       </c>
       <c r="R120" t="n">
-        <v>7054156</v>
+        <v>7054621</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14193,24 +14233,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14221,73 +14251,48 @@
       </c>
       <c r="AG120" t="b">
         <v>0</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125724557</v>
+        <v>125724625</v>
       </c>
       <c r="B121" t="n">
-        <v>57651</v>
+        <v>98359</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14297,10 +14302,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>450772</v>
+        <v>451414</v>
       </c>
       <c r="R121" t="n">
-        <v>7054621</v>
+        <v>7055348</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14333,11 +14338,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15307,48 +15307,58 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125724601</v>
+        <v>125712965</v>
       </c>
       <c r="B131" t="n">
-        <v>57651</v>
+        <v>56843</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>450317</v>
+        <v>450279</v>
       </c>
       <c r="R131" t="n">
-        <v>7054857</v>
+        <v>7054063</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15375,14 +15385,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15393,64 +15408,74 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125724561</v>
+        <v>125710733</v>
       </c>
       <c r="B132" t="n">
-        <v>57651</v>
+        <v>98359</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>450605</v>
+        <v>451046</v>
       </c>
       <c r="R132" t="n">
-        <v>7054337</v>
+        <v>7054942</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15484,7 +15509,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 30 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15495,23 +15520,28 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125724611</v>
+        <v>125724601</v>
       </c>
       <c r="B133" t="n">
         <v>57651</v>
@@ -15546,10 +15576,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>450631</v>
+        <v>450317</v>
       </c>
       <c r="R133" t="n">
-        <v>7054989</v>
+        <v>7054857</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15586,7 +15616,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15613,7 +15643,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125724582</v>
+        <v>125724561</v>
       </c>
       <c r="B134" t="n">
         <v>57651</v>
@@ -15648,10 +15678,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>450120</v>
+        <v>450605</v>
       </c>
       <c r="R134" t="n">
-        <v>7054703</v>
+        <v>7054337</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15688,7 +15718,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15715,7 +15745,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125724620</v>
+        <v>125724611</v>
       </c>
       <c r="B135" t="n">
         <v>57651</v>
@@ -15750,10 +15780,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>450942</v>
+        <v>450631</v>
       </c>
       <c r="R135" t="n">
-        <v>7054894</v>
+        <v>7054989</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15817,58 +15847,48 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125712965</v>
+        <v>125724582</v>
       </c>
       <c r="B136" t="n">
-        <v>56843</v>
+        <v>57651</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>450279</v>
+        <v>450120</v>
       </c>
       <c r="R136" t="n">
-        <v>7054063</v>
+        <v>7054703</v>
       </c>
       <c r="S136" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15895,19 +15915,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>13:00</t>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15918,74 +15933,64 @@
       </c>
       <c r="AG136" t="b">
         <v>0</v>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125710733</v>
+        <v>125724620</v>
       </c>
       <c r="B137" t="n">
-        <v>98359</v>
+        <v>57651</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>451046</v>
+        <v>450942</v>
       </c>
       <c r="R137" t="n">
-        <v>7054942</v>
+        <v>7054894</v>
       </c>
       <c r="S137" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16019,7 +16024,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16030,21 +16035,16 @@
       </c>
       <c r="AG137" t="b">
         <v>0</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>

--- a/artfynd/A 22902-2025 artfynd.xlsx
+++ b/artfynd/A 22902-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125724579</v>
+        <v>125714988</v>
       </c>
       <c r="B3" t="n">
         <v>57651</v>
@@ -831,16 +831,26 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450145</v>
+        <v>450413</v>
       </c>
       <c r="R3" t="n">
-        <v>7054502</v>
+        <v>7054149</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,14 +880,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,23 +908,48 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125714988</v>
+        <v>125724597</v>
       </c>
       <c r="B4" t="n">
         <v>57651</v>
@@ -933,26 +978,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450413</v>
+        <v>450287</v>
       </c>
       <c r="R4" t="n">
-        <v>7054149</v>
+        <v>7054787</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,24 +1017,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,51 +1035,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125724597</v>
+        <v>125708514</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1062,37 +1062,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450287</v>
+        <v>451330</v>
       </c>
       <c r="R5" t="n">
-        <v>7054787</v>
+        <v>7055192</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,11 +1122,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,22 +1136,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125724591</v>
+        <v>125724629</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>91250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1188,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450270</v>
+        <v>450502</v>
       </c>
       <c r="R6" t="n">
-        <v>7054720</v>
+        <v>7054507</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,11 +1219,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125724610</v>
+        <v>125724628</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>91250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>450597</v>
+        <v>451229</v>
       </c>
       <c r="R7" t="n">
-        <v>7055031</v>
+        <v>7055028</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1326,11 +1316,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125708514</v>
+        <v>125724579</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,37 +1353,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451330</v>
+        <v>450145</v>
       </c>
       <c r="R8" t="n">
-        <v>7055192</v>
+        <v>7054502</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1428,6 +1413,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,22 +1432,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125724629</v>
+        <v>125724591</v>
       </c>
       <c r="B9" t="n">
-        <v>91250</v>
+        <v>57651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,21 +1455,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1489,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>450502</v>
+        <v>450270</v>
       </c>
       <c r="R9" t="n">
-        <v>7054507</v>
+        <v>7054720</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,6 +1515,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125724628</v>
+        <v>125724610</v>
       </c>
       <c r="B10" t="n">
-        <v>91250</v>
+        <v>57651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1562,21 +1557,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1586,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451229</v>
+        <v>450597</v>
       </c>
       <c r="R10" t="n">
-        <v>7055028</v>
+        <v>7055031</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,6 +1617,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125712265</v>
+        <v>125724585</v>
       </c>
       <c r="B11" t="n">
-        <v>57811</v>
+        <v>57651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,51 +1659,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storholmen, Storholmen, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450456</v>
+        <v>450232</v>
       </c>
       <c r="R11" t="n">
-        <v>7054618</v>
+        <v>7054602</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1730,24 +1716,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Locklätet av en talltita observerades i lämplig häckmiljö.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,28 +1734,23 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125724585</v>
+        <v>125724599</v>
       </c>
       <c r="B12" t="n">
         <v>57651</v>
@@ -1814,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450232</v>
+        <v>450306</v>
       </c>
       <c r="R12" t="n">
-        <v>7054602</v>
+        <v>7054865</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1881,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125724599</v>
+        <v>125724619</v>
       </c>
       <c r="B13" t="n">
         <v>57651</v>
@@ -1916,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450306</v>
+        <v>450958</v>
       </c>
       <c r="R13" t="n">
-        <v>7054865</v>
+        <v>7054933</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125724592</v>
+        <v>125711059</v>
       </c>
       <c r="B14" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,34 +1965,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450278</v>
+        <v>450886</v>
       </c>
       <c r="R14" t="n">
-        <v>7054719</v>
+        <v>7054749</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,23 +2040,48 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125724619</v>
+        <v>125724592</v>
       </c>
       <c r="B15" t="n">
         <v>57651</v>
@@ -2120,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450958</v>
+        <v>450278</v>
       </c>
       <c r="R15" t="n">
-        <v>7054933</v>
+        <v>7054719</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,7 +2156,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125711059</v>
+        <v>125712265</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>57811</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,37 +2194,51 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Storholmen, Storholmen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>450886</v>
+        <v>450456</v>
       </c>
       <c r="R16" t="n">
-        <v>7054749</v>
+        <v>7054618</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2255,14 +2265,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Locklätet av en talltita observerades i lämplig häckmiljö.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2277,26 +2297,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2314,10 +2314,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125718101</v>
+        <v>125724635</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,47 +2325,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451151</v>
+        <v>451002</v>
       </c>
       <c r="R17" t="n">
-        <v>7054937</v>
+        <v>7055090</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2392,26 +2382,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre och rejäla, längs ca 2 meter på en granstam.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2420,48 +2395,23 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125724598</v>
+        <v>125718101</v>
       </c>
       <c r="B18" t="n">
         <v>57651</v>
@@ -2490,19 +2440,29 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>450292</v>
+        <v>451151</v>
       </c>
       <c r="R18" t="n">
-        <v>7054851</v>
+        <v>7054937</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2529,14 +2489,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre och rejäla, längs ca 2 meter på en granstam.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,16 +2517,41 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2767,59 +2762,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125714526</v>
+        <v>125724598</v>
       </c>
       <c r="B21" t="n">
-        <v>98359</v>
+        <v>57651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>450368</v>
+        <v>450292</v>
       </c>
       <c r="R21" t="n">
-        <v>7054102</v>
+        <v>7054851</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2849,24 +2830,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Minst 11 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2877,21 +2848,16 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2901,7 +2867,7 @@
         <v>125708478</v>
       </c>
       <c r="B22" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3029,45 +2995,59 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125724635</v>
+        <v>125714526</v>
       </c>
       <c r="B23" t="n">
-        <v>78972</v>
+        <v>98360</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451002</v>
+        <v>450368</v>
       </c>
       <c r="R23" t="n">
-        <v>7055090</v>
+        <v>7054102</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3097,11 +3077,26 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3110,26 +3105,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125717532</v>
+        <v>125724565</v>
       </c>
       <c r="B24" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3137,34 +3137,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>450948</v>
+        <v>450606</v>
       </c>
       <c r="R24" t="n">
-        <v>7054739</v>
+        <v>7054211</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3194,24 +3194,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3222,79 +3212,59 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125715130</v>
+        <v>125712711</v>
       </c>
       <c r="B25" t="n">
-        <v>80111</v>
+        <v>57651</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3303,10 +3273,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450363</v>
+        <v>450410</v>
       </c>
       <c r="R25" t="n">
-        <v>7054211</v>
+        <v>7054290</v>
       </c>
       <c r="S25" t="n">
         <v>11</v>
@@ -3338,7 +3308,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3348,12 +3318,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Ringhack, äldre, på stambasen av en gran  nära en stor myrstack.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3372,22 +3342,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3405,7 +3375,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125724565</v>
+        <v>125724593</v>
       </c>
       <c r="B26" t="n">
         <v>57651</v>
@@ -3440,10 +3410,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450606</v>
+        <v>450274</v>
       </c>
       <c r="R26" t="n">
-        <v>7054211</v>
+        <v>7054720</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3480,7 +3450,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3507,7 +3477,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125712711</v>
+        <v>125724564</v>
       </c>
       <c r="B27" t="n">
         <v>57651</v>
@@ -3536,29 +3506,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>450410</v>
+        <v>450638</v>
       </c>
       <c r="R27" t="n">
-        <v>7054290</v>
+        <v>7054244</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3585,24 +3545,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  nära en stor myrstack.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3613,48 +3563,23 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125724593</v>
+        <v>125724574</v>
       </c>
       <c r="B28" t="n">
         <v>57651</v>
@@ -3689,10 +3614,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>450274</v>
+        <v>450390</v>
       </c>
       <c r="R28" t="n">
-        <v>7054720</v>
+        <v>7054071</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3729,7 +3654,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3756,7 +3681,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125724564</v>
+        <v>125724608</v>
       </c>
       <c r="B29" t="n">
         <v>57651</v>
@@ -3791,10 +3716,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>450638</v>
+        <v>450441</v>
       </c>
       <c r="R29" t="n">
-        <v>7054244</v>
+        <v>7054842</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3858,7 +3783,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125724574</v>
+        <v>125724573</v>
       </c>
       <c r="B30" t="n">
         <v>57651</v>
@@ -3893,10 +3818,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>450390</v>
+        <v>450391</v>
       </c>
       <c r="R30" t="n">
-        <v>7054071</v>
+        <v>7054076</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3933,7 +3858,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3960,7 +3885,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125724608</v>
+        <v>125724572</v>
       </c>
       <c r="B31" t="n">
         <v>57651</v>
@@ -3995,10 +3920,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>450441</v>
+        <v>450406</v>
       </c>
       <c r="R31" t="n">
-        <v>7054842</v>
+        <v>7054072</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4062,10 +3987,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125724573</v>
+        <v>125717532</v>
       </c>
       <c r="B32" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4073,34 +3998,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>450391</v>
+        <v>450948</v>
       </c>
       <c r="R32" t="n">
-        <v>7054076</v>
+        <v>7054739</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4130,14 +4055,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4148,64 +4083,94 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125724572</v>
+        <v>125715130</v>
       </c>
       <c r="B33" t="n">
-        <v>57651</v>
+        <v>80111</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450406</v>
+        <v>450363</v>
       </c>
       <c r="R33" t="n">
-        <v>7054072</v>
+        <v>7054211</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4232,14 +4197,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4250,16 +4225,41 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4269,7 +4269,7 @@
         <v>125709103</v>
       </c>
       <c r="B34" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>125711207</v>
       </c>
       <c r="B35" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4513,10 +4513,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125716595</v>
+        <v>125724627</v>
       </c>
       <c r="B36" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4524,44 +4524,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>450481</v>
+        <v>450528</v>
       </c>
       <c r="R36" t="n">
-        <v>7054352</v>
+        <v>7054102</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4591,26 +4581,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4619,48 +4594,23 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125724603</v>
+        <v>125716595</v>
       </c>
       <c r="B37" t="n">
         <v>57651</v>
@@ -4689,16 +4639,26 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>450339</v>
+        <v>450481</v>
       </c>
       <c r="R37" t="n">
-        <v>7054827</v>
+        <v>7054352</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4728,14 +4688,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4746,23 +4716,48 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125724613</v>
+        <v>125724603</v>
       </c>
       <c r="B38" t="n">
         <v>57651</v>
@@ -4797,10 +4792,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450714</v>
+        <v>450339</v>
       </c>
       <c r="R38" t="n">
-        <v>7055072</v>
+        <v>7054827</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4837,7 +4832,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4864,10 +4859,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125724627</v>
+        <v>125724613</v>
       </c>
       <c r="B39" t="n">
-        <v>80075</v>
+        <v>57651</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4875,21 +4870,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4899,10 +4894,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>450528</v>
+        <v>450714</v>
       </c>
       <c r="R39" t="n">
-        <v>7054102</v>
+        <v>7055072</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4935,6 +4930,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5491,7 +5491,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125724594</v>
+        <v>125724556</v>
       </c>
       <c r="B45" t="n">
         <v>57651</v>
@@ -5526,10 +5526,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>450285</v>
+        <v>450878</v>
       </c>
       <c r="R45" t="n">
-        <v>7054794</v>
+        <v>7054550</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5593,7 +5593,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125724556</v>
+        <v>125724594</v>
       </c>
       <c r="B46" t="n">
         <v>57651</v>
@@ -5628,10 +5628,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>450878</v>
+        <v>450285</v>
       </c>
       <c r="R46" t="n">
-        <v>7054550</v>
+        <v>7054794</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5695,62 +5695,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125709295</v>
+        <v>125724630</v>
       </c>
       <c r="B47" t="n">
-        <v>98359</v>
+        <v>91250</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451312</v>
+        <v>450577</v>
       </c>
       <c r="R47" t="n">
-        <v>7055388</v>
+        <v>7054440</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5782,11 +5768,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5795,21 +5776,16 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5943,10 +5919,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125724630</v>
+        <v>125711989</v>
       </c>
       <c r="B49" t="n">
-        <v>91250</v>
+        <v>57651</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5954,37 +5930,47 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>450577</v>
+        <v>450536</v>
       </c>
       <c r="R49" t="n">
-        <v>7054440</v>
+        <v>7054699</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6011,11 +5997,26 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6024,23 +6025,48 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125711989</v>
+        <v>125724615</v>
       </c>
       <c r="B50" t="n">
         <v>57651</v>
@@ -6069,29 +6095,19 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>450536</v>
+        <v>450856</v>
       </c>
       <c r="R50" t="n">
-        <v>7054699</v>
+        <v>7054955</v>
       </c>
       <c r="S50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6118,24 +6134,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6146,48 +6152,23 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125724615</v>
+        <v>125724555</v>
       </c>
       <c r="B51" t="n">
         <v>57651</v>
@@ -6222,10 +6203,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>450856</v>
+        <v>450816</v>
       </c>
       <c r="R51" t="n">
-        <v>7054955</v>
+        <v>7054432</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6289,7 +6270,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125724555</v>
+        <v>125712552</v>
       </c>
       <c r="B52" t="n">
         <v>57651</v>
@@ -6318,19 +6299,29 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>450816</v>
+        <v>450417</v>
       </c>
       <c r="R52" t="n">
-        <v>7054432</v>
+        <v>7054319</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6357,14 +6348,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6375,23 +6376,48 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125712552</v>
+        <v>125724553</v>
       </c>
       <c r="B53" t="n">
         <v>57651</v>
@@ -6420,29 +6446,19 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>450417</v>
+        <v>450713</v>
       </c>
       <c r="R53" t="n">
-        <v>7054319</v>
+        <v>7054346</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6469,24 +6485,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6497,48 +6503,23 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125724553</v>
+        <v>125724614</v>
       </c>
       <c r="B54" t="n">
         <v>57651</v>
@@ -6573,10 +6554,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>450713</v>
+        <v>450762</v>
       </c>
       <c r="R54" t="n">
-        <v>7054346</v>
+        <v>7055029</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6613,7 +6594,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6640,48 +6621,62 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125724614</v>
+        <v>125709295</v>
       </c>
       <c r="B55" t="n">
-        <v>57651</v>
+        <v>98360</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>450762</v>
+        <v>451312</v>
       </c>
       <c r="R55" t="n">
-        <v>7055029</v>
+        <v>7055388</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6715,7 +6710,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6726,26 +6721,31 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125709678</v>
+        <v>125724606</v>
       </c>
       <c r="B56" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6753,37 +6753,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451218</v>
+        <v>450436</v>
       </c>
       <c r="R56" t="n">
-        <v>7055148</v>
+        <v>7054836</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6815,6 +6815,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6823,51 +6828,26 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125710504</v>
+        <v>125724554</v>
       </c>
       <c r="B57" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6875,37 +6855,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451089</v>
+        <v>450796</v>
       </c>
       <c r="R57" t="n">
-        <v>7054989</v>
+        <v>7054404</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6939,7 +6919,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6950,48 +6930,23 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125711291</v>
+        <v>125709678</v>
       </c>
       <c r="B58" t="n">
         <v>78972</v>
@@ -7026,13 +6981,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>450795</v>
+        <v>451218</v>
       </c>
       <c r="R58" t="n">
-        <v>7054803</v>
+        <v>7055148</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7064,11 +7019,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flertalet granar.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7080,7 +7030,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
@@ -7118,10 +7068,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125724606</v>
+        <v>125710504</v>
       </c>
       <c r="B59" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7129,37 +7079,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>450436</v>
+        <v>451089</v>
       </c>
       <c r="R59" t="n">
-        <v>7054836</v>
+        <v>7054989</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7193,7 +7143,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7204,26 +7154,51 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125724554</v>
+        <v>125711291</v>
       </c>
       <c r="B60" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7231,37 +7206,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>450796</v>
+        <v>450795</v>
       </c>
       <c r="R60" t="n">
-        <v>7054404</v>
+        <v>7054803</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7295,7 +7270,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7306,16 +7281,41 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7325,7 +7325,7 @@
         <v>125709578</v>
       </c>
       <c r="B61" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7443,10 +7443,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125711118</v>
+        <v>125714547</v>
       </c>
       <c r="B62" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7454,39 +7454,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>450865</v>
+        <v>450361</v>
       </c>
       <c r="R62" t="n">
-        <v>7054734</v>
+        <v>7054101</v>
       </c>
       <c r="S62" t="n">
         <v>8</v>
@@ -7516,14 +7511,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På nedfallen död gren av sälg.</t>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7537,27 +7537,27 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7575,48 +7575,62 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125714547</v>
+        <v>125716316</v>
       </c>
       <c r="B63" t="n">
-        <v>78972</v>
+        <v>98360</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>450361</v>
+        <v>450483</v>
       </c>
       <c r="R63" t="n">
-        <v>7054101</v>
+        <v>7054352</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7645,7 +7659,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7655,7 +7669,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7670,26 +7684,6 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7707,10 +7701,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125724634</v>
+        <v>125711118</v>
       </c>
       <c r="B64" t="n">
-        <v>91250</v>
+        <v>80076</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7718,37 +7712,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>451148</v>
+        <v>450865</v>
       </c>
       <c r="R64" t="n">
-        <v>7055327</v>
+        <v>7054734</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7780,6 +7779,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På nedfallen död gren av sälg.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7788,75 +7792,86 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125716316</v>
+        <v>125724634</v>
       </c>
       <c r="B65" t="n">
-        <v>98359</v>
+        <v>91250</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>450483</v>
+        <v>451148</v>
       </c>
       <c r="R65" t="n">
-        <v>7054352</v>
+        <v>7055327</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7886,21 +7901,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7909,31 +7914,26 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125717826</v>
+        <v>125714185</v>
       </c>
       <c r="B66" t="n">
-        <v>78972</v>
+        <v>57069</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7941,37 +7941,56 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>102961</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>451046</v>
+        <v>450224</v>
       </c>
       <c r="R66" t="n">
-        <v>7054820</v>
+        <v>7054100</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8000,7 +8019,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8010,12 +8029,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Långväxta bålar i god mängd.</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8026,31 +8040,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8067,10 +8056,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125714185</v>
+        <v>125717826</v>
       </c>
       <c r="B67" t="n">
-        <v>57069</v>
+        <v>78972</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8078,56 +8067,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102961</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>450224</v>
+        <v>451046</v>
       </c>
       <c r="R67" t="n">
-        <v>7054100</v>
+        <v>7054820</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8156,7 +8126,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8166,7 +8136,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Långväxta bålar i god mängd.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8177,6 +8152,31 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8293,7 +8293,7 @@
         <v>125708839</v>
       </c>
       <c r="B69" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9113,48 +9113,67 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125724545</v>
+        <v>125718167</v>
       </c>
       <c r="B76" t="n">
-        <v>91232</v>
+        <v>98360</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>450771</v>
+        <v>451146</v>
       </c>
       <c r="R76" t="n">
-        <v>7055042</v>
+        <v>7054932</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9181,11 +9200,26 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Minst 14 plantor inom ca 1 m2.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9194,26 +9228,31 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125715929</v>
+        <v>125724545</v>
       </c>
       <c r="B77" t="n">
-        <v>78972</v>
+        <v>91232</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9221,37 +9260,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>450435</v>
+        <v>450771</v>
       </c>
       <c r="R77" t="n">
-        <v>7054165</v>
+        <v>7055042</v>
       </c>
       <c r="S77" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9278,19 +9317,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>15:26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9305,79 +9334,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125718167</v>
+        <v>125715929</v>
       </c>
       <c r="B78" t="n">
-        <v>98359</v>
+        <v>78972</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>451146</v>
+        <v>450435</v>
       </c>
       <c r="R78" t="n">
-        <v>7054932</v>
+        <v>7054165</v>
       </c>
       <c r="S78" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9406,7 +9416,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9416,12 +9426,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>17:03</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Minst 14 plantor inom ca 1 m2.</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9432,11 +9437,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -10162,62 +10162,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125708960</v>
+        <v>125710745</v>
       </c>
       <c r="B86" t="n">
-        <v>98359</v>
+        <v>78972</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>451445</v>
+        <v>451035</v>
       </c>
       <c r="R86" t="n">
-        <v>7055383</v>
+        <v>7054940</v>
       </c>
       <c r="S86" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10251,7 +10237,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Minst 29 plantor inom ca 2 m2.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10266,6 +10252,26 @@
       <c r="AH86" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10283,10 +10289,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125710745</v>
+        <v>125724605</v>
       </c>
       <c r="B87" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10294,37 +10300,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>451035</v>
+        <v>450357</v>
       </c>
       <c r="R87" t="n">
-        <v>7054940</v>
+        <v>7054800</v>
       </c>
       <c r="S87" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10358,7 +10364,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10369,48 +10375,23 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125724605</v>
+        <v>125715345</v>
       </c>
       <c r="B88" t="n">
         <v>57651</v>
@@ -10439,16 +10420,26 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>450357</v>
+        <v>450372</v>
       </c>
       <c r="R88" t="n">
-        <v>7054800</v>
+        <v>7054250</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10478,14 +10469,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en död liggande gran precis öster om vägen.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10496,23 +10497,48 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125715345</v>
+        <v>125724587</v>
       </c>
       <c r="B89" t="n">
         <v>57651</v>
@@ -10541,26 +10567,16 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>450372</v>
+        <v>450279</v>
       </c>
       <c r="R89" t="n">
-        <v>7054250</v>
+        <v>7054606</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10590,24 +10606,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en död liggande gran precis öster om vägen.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10618,48 +10624,23 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125724587</v>
+        <v>125715883</v>
       </c>
       <c r="B90" t="n">
         <v>57651</v>
@@ -10688,19 +10669,29 @@
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>450279</v>
+        <v>450371</v>
       </c>
       <c r="R90" t="n">
-        <v>7054606</v>
+        <v>7054182</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10727,14 +10718,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en något smalare gran.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10745,74 +10746,103 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125715883</v>
+        <v>125708960</v>
       </c>
       <c r="B91" t="n">
-        <v>57651</v>
+        <v>98360</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>450371</v>
+        <v>451445</v>
       </c>
       <c r="R91" t="n">
-        <v>7054182</v>
+        <v>7055383</v>
       </c>
       <c r="S91" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10839,24 +10869,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en något smalare gran.</t>
+          <t>Minst 29 plantor inom ca 2 m2.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10871,26 +10891,6 @@
       <c r="AH91" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10908,10 +10908,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125724622</v>
+        <v>125714169</v>
       </c>
       <c r="B92" t="n">
-        <v>57651</v>
+        <v>57811</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10919,37 +10919,51 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>450935</v>
+        <v>450226</v>
       </c>
       <c r="R92" t="n">
-        <v>7055227</v>
+        <v>7054095</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10976,14 +10990,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10994,61 +11013,85 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125724543</v>
+        <v>125710515</v>
       </c>
       <c r="B93" t="n">
-        <v>91590</v>
+        <v>58020</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2062</v>
+        <v>103015</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>450931</v>
+        <v>451089</v>
       </c>
       <c r="R93" t="n">
-        <v>7054587</v>
+        <v>7054975</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11078,40 +11121,54 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125710515</v>
+        <v>125708590</v>
       </c>
       <c r="B94" t="n">
-        <v>58020</v>
+        <v>98360</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11119,41 +11176,36 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103015</v>
+        <v>221952</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11162,13 +11214,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>451089</v>
+        <v>451359</v>
       </c>
       <c r="R94" t="n">
-        <v>7054975</v>
+        <v>7055225</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11197,7 +11249,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11207,7 +11259,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 3 m2.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11239,62 +11296,48 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125714169</v>
+        <v>125724543</v>
       </c>
       <c r="B95" t="n">
-        <v>57811</v>
+        <v>91590</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>2062</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>450226</v>
+        <v>450931</v>
       </c>
       <c r="R95" t="n">
-        <v>7054095</v>
+        <v>7054587</v>
       </c>
       <c r="S95" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11321,106 +11364,78 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125708590</v>
+        <v>125724622</v>
       </c>
       <c r="B96" t="n">
-        <v>98359</v>
+        <v>57651</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>451359</v>
+        <v>450935</v>
       </c>
       <c r="R96" t="n">
-        <v>7055225</v>
+        <v>7055227</v>
       </c>
       <c r="S96" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11447,24 +11462,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Minst 60 plantor inom ca 3 m2.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11475,83 +11480,64 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125712767</v>
+        <v>125709922</v>
       </c>
       <c r="B97" t="n">
-        <v>98359</v>
+        <v>78972</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>450391</v>
+        <v>451225</v>
       </c>
       <c r="R97" t="n">
-        <v>7054281</v>
+        <v>7055093</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11578,24 +11564,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Minst 20 plantor inom ca 2 m2 yta.</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11734,10 +11710,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125709922</v>
+        <v>125715109</v>
       </c>
       <c r="B99" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11745,37 +11721,42 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>451225</v>
+        <v>450365</v>
       </c>
       <c r="R99" t="n">
-        <v>7055093</v>
+        <v>7054197</v>
       </c>
       <c r="S99" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11802,14 +11783,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11824,6 +11815,26 @@
       <c r="AH99" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -11841,10 +11852,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125715109</v>
+        <v>125724609</v>
       </c>
       <c r="B100" t="n">
-        <v>80076</v>
+        <v>57651</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11852,39 +11863,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>450365</v>
+        <v>450581</v>
       </c>
       <c r="R100" t="n">
-        <v>7054197</v>
+        <v>7055012</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11914,24 +11920,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11942,48 +11938,23 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125724609</v>
+        <v>125724546</v>
       </c>
       <c r="B101" t="n">
         <v>57651</v>
@@ -12018,10 +11989,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>450581</v>
+        <v>451102</v>
       </c>
       <c r="R101" t="n">
-        <v>7055012</v>
+        <v>7054896</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12085,7 +12056,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125724546</v>
+        <v>125724566</v>
       </c>
       <c r="B102" t="n">
         <v>57651</v>
@@ -12120,10 +12091,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>451102</v>
+        <v>450600</v>
       </c>
       <c r="R102" t="n">
-        <v>7054896</v>
+        <v>7054142</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12187,7 +12158,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125724566</v>
+        <v>125724551</v>
       </c>
       <c r="B103" t="n">
         <v>57651</v>
@@ -12222,10 +12193,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>450600</v>
+        <v>450486</v>
       </c>
       <c r="R103" t="n">
-        <v>7054142</v>
+        <v>7054445</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12289,7 +12260,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125724551</v>
+        <v>125724621</v>
       </c>
       <c r="B104" t="n">
         <v>57651</v>
@@ -12324,10 +12295,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>450486</v>
+        <v>450933</v>
       </c>
       <c r="R104" t="n">
-        <v>7054445</v>
+        <v>7054883</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12364,7 +12335,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12391,7 +12362,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125724621</v>
+        <v>125715238</v>
       </c>
       <c r="B105" t="n">
         <v>57651</v>
@@ -12420,16 +12391,26 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>450933</v>
+        <v>450342</v>
       </c>
       <c r="R105" t="n">
-        <v>7054883</v>
+        <v>7054212</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12459,14 +12440,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran  precis öster om vägen.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12477,23 +12468,48 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125715238</v>
+        <v>125724618</v>
       </c>
       <c r="B106" t="n">
         <v>57651</v>
@@ -12522,26 +12538,16 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>450342</v>
+        <v>450905</v>
       </c>
       <c r="R106" t="n">
-        <v>7054212</v>
+        <v>7054898</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12571,24 +12577,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  precis öster om vägen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12599,48 +12595,23 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125724618</v>
+        <v>125724577</v>
       </c>
       <c r="B107" t="n">
         <v>57651</v>
@@ -12675,10 +12646,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>450905</v>
+        <v>450259</v>
       </c>
       <c r="R107" t="n">
-        <v>7054898</v>
+        <v>7054380</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12742,45 +12713,59 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125724577</v>
+        <v>125712767</v>
       </c>
       <c r="B108" t="n">
-        <v>57651</v>
+        <v>98360</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>450259</v>
+        <v>450391</v>
       </c>
       <c r="R108" t="n">
-        <v>7054380</v>
+        <v>7054281</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12810,14 +12795,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 20 plantor inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12828,16 +12823,21 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -13525,48 +13525,53 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125709665</v>
+        <v>125712605</v>
       </c>
       <c r="B115" t="n">
-        <v>80103</v>
+        <v>78972</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>451229</v>
+        <v>450406</v>
       </c>
       <c r="R115" t="n">
-        <v>7055183</v>
+        <v>7054312</v>
       </c>
       <c r="S115" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13593,14 +13598,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13611,6 +13626,31 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
@@ -13627,53 +13667,48 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125712605</v>
+        <v>125709665</v>
       </c>
       <c r="B116" t="n">
-        <v>78972</v>
+        <v>80103</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>450406</v>
+        <v>451229</v>
       </c>
       <c r="R116" t="n">
-        <v>7054312</v>
+        <v>7055183</v>
       </c>
       <c r="S116" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13700,24 +13735,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar med apothecier.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13728,31 +13753,6 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
@@ -14270,7 +14270,7 @@
         <v>125724625</v>
       </c>
       <c r="B121" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125724602</v>
+        <v>125724623</v>
       </c>
       <c r="B127" t="n">
         <v>57651</v>
@@ -14934,10 +14934,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>450307</v>
+        <v>451200</v>
       </c>
       <c r="R127" t="n">
-        <v>7054854</v>
+        <v>7055401</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14974,7 +14974,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15001,7 +15001,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125724548</v>
+        <v>125724602</v>
       </c>
       <c r="B128" t="n">
         <v>57651</v>
@@ -15036,10 +15036,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>450973</v>
+        <v>450307</v>
       </c>
       <c r="R128" t="n">
-        <v>7054710</v>
+        <v>7054854</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15076,7 +15076,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15103,7 +15103,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125724617</v>
+        <v>125724548</v>
       </c>
       <c r="B129" t="n">
         <v>57651</v>
@@ -15138,10 +15138,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>450851</v>
+        <v>450973</v>
       </c>
       <c r="R129" t="n">
-        <v>7054937</v>
+        <v>7054710</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15205,7 +15205,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125724623</v>
+        <v>125724617</v>
       </c>
       <c r="B130" t="n">
         <v>57651</v>
@@ -15240,10 +15240,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>451200</v>
+        <v>450851</v>
       </c>
       <c r="R130" t="n">
-        <v>7055401</v>
+        <v>7054937</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15307,58 +15307,48 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125712965</v>
+        <v>125724601</v>
       </c>
       <c r="B131" t="n">
-        <v>56843</v>
+        <v>57651</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>450279</v>
+        <v>450317</v>
       </c>
       <c r="R131" t="n">
-        <v>7054063</v>
+        <v>7054857</v>
       </c>
       <c r="S131" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15385,19 +15375,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>13:00</t>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15408,74 +15393,64 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125710733</v>
+        <v>125724561</v>
       </c>
       <c r="B132" t="n">
-        <v>98359</v>
+        <v>57651</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>451046</v>
+        <v>450605</v>
       </c>
       <c r="R132" t="n">
-        <v>7054942</v>
+        <v>7054337</v>
       </c>
       <c r="S132" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15509,7 +15484,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15520,28 +15495,23 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125724601</v>
+        <v>125724611</v>
       </c>
       <c r="B133" t="n">
         <v>57651</v>
@@ -15576,10 +15546,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>450317</v>
+        <v>450631</v>
       </c>
       <c r="R133" t="n">
-        <v>7054857</v>
+        <v>7054989</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15616,7 +15586,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15643,7 +15613,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125724561</v>
+        <v>125724620</v>
       </c>
       <c r="B134" t="n">
         <v>57651</v>
@@ -15678,10 +15648,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>450605</v>
+        <v>450942</v>
       </c>
       <c r="R134" t="n">
-        <v>7054337</v>
+        <v>7054894</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15718,7 +15688,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15745,48 +15715,58 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125724611</v>
+        <v>125712965</v>
       </c>
       <c r="B135" t="n">
-        <v>57651</v>
+        <v>56843</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>450631</v>
+        <v>450279</v>
       </c>
       <c r="R135" t="n">
-        <v>7054989</v>
+        <v>7054063</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15813,14 +15793,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15831,16 +15816,21 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -15949,48 +15939,53 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125724620</v>
+        <v>125710733</v>
       </c>
       <c r="B137" t="n">
-        <v>57651</v>
+        <v>98360</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>450942</v>
+        <v>451046</v>
       </c>
       <c r="R137" t="n">
-        <v>7054894</v>
+        <v>7054942</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16024,7 +16019,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Minst 30 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16035,16 +16030,21 @@
       </c>
       <c r="AG137" t="b">
         <v>0</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -17945,10 +17945,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126056429</v>
+        <v>126056433</v>
       </c>
       <c r="B155" t="n">
-        <v>57651</v>
+        <v>91250</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17956,21 +17956,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17980,10 +17980,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>451134</v>
+        <v>450386</v>
       </c>
       <c r="R155" t="n">
-        <v>7054884</v>
+        <v>7054086</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18016,11 +18016,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18047,10 +18042,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126056433</v>
+        <v>126056429</v>
       </c>
       <c r="B156" t="n">
-        <v>91250</v>
+        <v>57651</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18058,21 +18053,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -18082,10 +18077,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>450386</v>
+        <v>451134</v>
       </c>
       <c r="R156" t="n">
-        <v>7054086</v>
+        <v>7054884</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18118,6 +18113,11 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD156" t="b">

--- a/artfynd/A 22902-2025 artfynd.xlsx
+++ b/artfynd/A 22902-2025 artfynd.xlsx
@@ -4387,47 +4387,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125711207</v>
+        <v>125716595</v>
       </c>
       <c r="B35" t="n">
-        <v>98360</v>
+        <v>57651</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4437,14 +4428,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>450852</v>
+        <v>450481</v>
       </c>
       <c r="R35" t="n">
-        <v>7054681</v>
+        <v>7054352</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4474,14 +4465,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Minst 17 plantor inom ca 2 m2 yta.</t>
+          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4496,6 +4497,26 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4513,10 +4534,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125724627</v>
+        <v>125724603</v>
       </c>
       <c r="B36" t="n">
-        <v>80075</v>
+        <v>57651</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4524,21 +4545,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4548,10 +4569,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>450528</v>
+        <v>450339</v>
       </c>
       <c r="R36" t="n">
-        <v>7054102</v>
+        <v>7054827</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4584,6 +4605,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4610,7 +4636,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125716595</v>
+        <v>125724613</v>
       </c>
       <c r="B37" t="n">
         <v>57651</v>
@@ -4639,26 +4665,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>450481</v>
+        <v>450714</v>
       </c>
       <c r="R37" t="n">
-        <v>7054352</v>
+        <v>7055072</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4688,24 +4704,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4716,51 +4722,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125724603</v>
+        <v>125724627</v>
       </c>
       <c r="B38" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4768,21 +4749,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4792,10 +4773,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450339</v>
+        <v>450528</v>
       </c>
       <c r="R38" t="n">
-        <v>7054827</v>
+        <v>7054102</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4828,11 +4809,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4859,45 +4835,64 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125724613</v>
+        <v>125711207</v>
       </c>
       <c r="B39" t="n">
-        <v>57651</v>
+        <v>98360</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>450714</v>
+        <v>450852</v>
       </c>
       <c r="R39" t="n">
-        <v>7055072</v>
+        <v>7054681</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4934,7 +4929,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Minst 17 plantor inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4945,16 +4940,21 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5792,10 +5792,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125710364</v>
+        <v>125711989</v>
       </c>
       <c r="B48" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5803,37 +5803,47 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>451107</v>
+        <v>450536</v>
       </c>
       <c r="R48" t="n">
-        <v>7055032</v>
+        <v>7054699</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5860,14 +5870,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Gott om långväxta bålar på en gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5881,7 +5901,7 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -5896,12 +5916,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5919,7 +5939,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125711989</v>
+        <v>125724615</v>
       </c>
       <c r="B49" t="n">
         <v>57651</v>
@@ -5948,29 +5968,19 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>450536</v>
+        <v>450856</v>
       </c>
       <c r="R49" t="n">
-        <v>7054699</v>
+        <v>7054955</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5997,24 +6007,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6025,48 +6025,23 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125724615</v>
+        <v>125724555</v>
       </c>
       <c r="B50" t="n">
         <v>57651</v>
@@ -6101,10 +6076,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>450856</v>
+        <v>450816</v>
       </c>
       <c r="R50" t="n">
-        <v>7054955</v>
+        <v>7054432</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6168,7 +6143,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125724555</v>
+        <v>125712552</v>
       </c>
       <c r="B51" t="n">
         <v>57651</v>
@@ -6197,19 +6172,29 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>450816</v>
+        <v>450417</v>
       </c>
       <c r="R51" t="n">
-        <v>7054432</v>
+        <v>7054319</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6236,14 +6221,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6254,23 +6249,48 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125712552</v>
+        <v>125724553</v>
       </c>
       <c r="B52" t="n">
         <v>57651</v>
@@ -6299,29 +6319,19 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>450417</v>
+        <v>450713</v>
       </c>
       <c r="R52" t="n">
-        <v>7054319</v>
+        <v>7054346</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6348,24 +6358,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6376,48 +6376,23 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125724553</v>
+        <v>125724614</v>
       </c>
       <c r="B53" t="n">
         <v>57651</v>
@@ -6452,10 +6427,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>450713</v>
+        <v>450762</v>
       </c>
       <c r="R53" t="n">
-        <v>7054346</v>
+        <v>7055029</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6492,7 +6467,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6519,10 +6494,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125724614</v>
+        <v>125710364</v>
       </c>
       <c r="B54" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6530,37 +6505,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>450762</v>
+        <v>451107</v>
       </c>
       <c r="R54" t="n">
-        <v>7055029</v>
+        <v>7055032</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6594,7 +6569,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Gott om långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6605,16 +6580,41 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -7443,48 +7443,62 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125714547</v>
+        <v>125716316</v>
       </c>
       <c r="B62" t="n">
-        <v>78972</v>
+        <v>98360</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>450361</v>
+        <v>450483</v>
       </c>
       <c r="R62" t="n">
-        <v>7054101</v>
+        <v>7054352</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7513,7 +7527,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7523,7 +7537,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7538,26 +7552,6 @@
       <c r="AH62" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7575,62 +7569,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125716316</v>
+        <v>125714547</v>
       </c>
       <c r="B63" t="n">
-        <v>98360</v>
+        <v>78972</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>450483</v>
+        <v>450361</v>
       </c>
       <c r="R63" t="n">
-        <v>7054352</v>
+        <v>7054101</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7659,7 +7639,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7669,7 +7649,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7684,6 +7664,26 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8411,10 +8411,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125724544</v>
+        <v>125716115</v>
       </c>
       <c r="B70" t="n">
-        <v>91232</v>
+        <v>78972</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8422,37 +8422,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>450929</v>
+        <v>450545</v>
       </c>
       <c r="R70" t="n">
-        <v>7054588</v>
+        <v>7054277</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8479,9 +8479,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8496,22 +8506,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125716115</v>
+        <v>125724544</v>
       </c>
       <c r="B71" t="n">
-        <v>78972</v>
+        <v>91232</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8519,37 +8529,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>450545</v>
+        <v>450929</v>
       </c>
       <c r="R71" t="n">
-        <v>7054277</v>
+        <v>7054588</v>
       </c>
       <c r="S71" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8576,19 +8586,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8603,12 +8603,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -10908,62 +10908,48 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125714169</v>
+        <v>125724543</v>
       </c>
       <c r="B92" t="n">
-        <v>57811</v>
+        <v>91590</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103021</v>
+        <v>2062</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>450226</v>
+        <v>450931</v>
       </c>
       <c r="R92" t="n">
-        <v>7054095</v>
+        <v>7054587</v>
       </c>
       <c r="S92" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10990,71 +10976,57 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125710515</v>
+        <v>125724622</v>
       </c>
       <c r="B93" t="n">
-        <v>58020</v>
+        <v>57651</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -11062,36 +11034,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>451089</v>
+        <v>450935</v>
       </c>
       <c r="R93" t="n">
-        <v>7054975</v>
+        <v>7055227</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11121,19 +11074,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>10:58</t>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11144,83 +11092,78 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125708590</v>
+        <v>125714169</v>
       </c>
       <c r="B94" t="n">
-        <v>98360</v>
+        <v>57811</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>451359</v>
+        <v>450226</v>
       </c>
       <c r="R94" t="n">
-        <v>7055225</v>
+        <v>7054095</v>
       </c>
       <c r="S94" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11249,7 +11192,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11259,12 +11202,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 3 m2.</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11278,7 +11216,7 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11296,45 +11234,64 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125724543</v>
+        <v>125710515</v>
       </c>
       <c r="B95" t="n">
-        <v>91590</v>
+        <v>58020</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2062</v>
+        <v>103015</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>450931</v>
+        <v>451089</v>
       </c>
       <c r="R95" t="n">
-        <v>7054587</v>
+        <v>7054975</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11364,78 +11321,106 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125724622</v>
+        <v>125708590</v>
       </c>
       <c r="B96" t="n">
-        <v>57651</v>
+        <v>98360</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>450935</v>
+        <v>451359</v>
       </c>
       <c r="R96" t="n">
-        <v>7055227</v>
+        <v>7055225</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11462,14 +11447,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 60 plantor inom ca 3 m2.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11480,64 +11475,83 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125709922</v>
+        <v>125712767</v>
       </c>
       <c r="B97" t="n">
-        <v>78972</v>
+        <v>98360</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>451225</v>
+        <v>450391</v>
       </c>
       <c r="R97" t="n">
-        <v>7055093</v>
+        <v>7054281</v>
       </c>
       <c r="S97" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11564,14 +11578,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Minst 20 plantor inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11603,7 +11627,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125718221</v>
+        <v>125709922</v>
       </c>
       <c r="B98" t="n">
         <v>78972</v>
@@ -11638,13 +11662,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>451172</v>
+        <v>451225</v>
       </c>
       <c r="R98" t="n">
-        <v>7054946</v>
+        <v>7055093</v>
       </c>
       <c r="S98" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11671,19 +11695,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>17:06</t>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11694,6 +11713,11 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -11710,10 +11734,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125715109</v>
+        <v>125718221</v>
       </c>
       <c r="B99" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11721,42 +11745,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>450365</v>
+        <v>451172</v>
       </c>
       <c r="R99" t="n">
-        <v>7054197</v>
+        <v>7054946</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11785,7 +11804,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11795,12 +11814,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11811,31 +11825,6 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -11852,10 +11841,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125724609</v>
+        <v>125715109</v>
       </c>
       <c r="B100" t="n">
-        <v>57651</v>
+        <v>80076</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11863,34 +11852,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>450581</v>
+        <v>450365</v>
       </c>
       <c r="R100" t="n">
-        <v>7055012</v>
+        <v>7054197</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11920,14 +11914,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11938,23 +11942,48 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125724546</v>
+        <v>125724609</v>
       </c>
       <c r="B101" t="n">
         <v>57651</v>
@@ -11989,10 +12018,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>451102</v>
+        <v>450581</v>
       </c>
       <c r="R101" t="n">
-        <v>7054896</v>
+        <v>7055012</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12056,7 +12085,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125724566</v>
+        <v>125724546</v>
       </c>
       <c r="B102" t="n">
         <v>57651</v>
@@ -12091,10 +12120,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>450600</v>
+        <v>451102</v>
       </c>
       <c r="R102" t="n">
-        <v>7054142</v>
+        <v>7054896</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12158,7 +12187,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125724551</v>
+        <v>125724566</v>
       </c>
       <c r="B103" t="n">
         <v>57651</v>
@@ -12193,10 +12222,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>450486</v>
+        <v>450600</v>
       </c>
       <c r="R103" t="n">
-        <v>7054445</v>
+        <v>7054142</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12260,7 +12289,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125724621</v>
+        <v>125724551</v>
       </c>
       <c r="B104" t="n">
         <v>57651</v>
@@ -12295,10 +12324,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>450933</v>
+        <v>450486</v>
       </c>
       <c r="R104" t="n">
-        <v>7054883</v>
+        <v>7054445</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12335,7 +12364,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12362,7 +12391,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125715238</v>
+        <v>125724621</v>
       </c>
       <c r="B105" t="n">
         <v>57651</v>
@@ -12391,26 +12420,16 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>450342</v>
+        <v>450933</v>
       </c>
       <c r="R105" t="n">
-        <v>7054212</v>
+        <v>7054883</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12440,24 +12459,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  precis öster om vägen.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12468,48 +12477,23 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125724618</v>
+        <v>125715238</v>
       </c>
       <c r="B106" t="n">
         <v>57651</v>
@@ -12538,16 +12522,26 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>450905</v>
+        <v>450342</v>
       </c>
       <c r="R106" t="n">
-        <v>7054898</v>
+        <v>7054212</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12577,14 +12571,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran  precis öster om vägen.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12595,23 +12599,48 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125724577</v>
+        <v>125724618</v>
       </c>
       <c r="B107" t="n">
         <v>57651</v>
@@ -12646,10 +12675,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>450259</v>
+        <v>450905</v>
       </c>
       <c r="R107" t="n">
-        <v>7054380</v>
+        <v>7054898</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12713,59 +12742,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125712767</v>
+        <v>125724577</v>
       </c>
       <c r="B108" t="n">
-        <v>98360</v>
+        <v>57651</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>450391</v>
+        <v>450259</v>
       </c>
       <c r="R108" t="n">
-        <v>7054281</v>
+        <v>7054380</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12795,24 +12810,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Minst 20 plantor inom ca 2 m2 yta.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12823,21 +12828,16 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -13667,48 +13667,48 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125709665</v>
+        <v>125724559</v>
       </c>
       <c r="B116" t="n">
-        <v>80103</v>
+        <v>57651</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>451229</v>
+        <v>450487</v>
       </c>
       <c r="R116" t="n">
-        <v>7055183</v>
+        <v>7054409</v>
       </c>
       <c r="S116" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13757,19 +13757,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125724559</v>
+        <v>125712655</v>
       </c>
       <c r="B117" t="n">
         <v>57651</v>
@@ -13798,19 +13798,29 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>450487</v>
+        <v>450387</v>
       </c>
       <c r="R117" t="n">
-        <v>7054409</v>
+        <v>7054295</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13837,14 +13847,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gran intill en stor myrstack.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13855,23 +13875,48 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125712655</v>
+        <v>125715638</v>
       </c>
       <c r="B118" t="n">
         <v>57651</v>
@@ -13916,13 +13961,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>450387</v>
+        <v>450416</v>
       </c>
       <c r="R118" t="n">
-        <v>7054295</v>
+        <v>7054156</v>
       </c>
       <c r="S118" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13951,7 +13996,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13961,12 +14006,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran intill en stor myrstack.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14018,7 +14063,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125715638</v>
+        <v>125724557</v>
       </c>
       <c r="B119" t="n">
         <v>57651</v>
@@ -14047,26 +14092,16 @@
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>450416</v>
+        <v>450772</v>
       </c>
       <c r="R119" t="n">
-        <v>7054156</v>
+        <v>7054621</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14096,24 +14131,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14124,89 +14149,64 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125724557</v>
+        <v>125709665</v>
       </c>
       <c r="B120" t="n">
-        <v>57651</v>
+        <v>80103</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>450772</v>
+        <v>451229</v>
       </c>
       <c r="R120" t="n">
-        <v>7054621</v>
+        <v>7055183</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14255,12 +14255,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -15613,7 +15613,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125724620</v>
+        <v>125724582</v>
       </c>
       <c r="B134" t="n">
         <v>57651</v>
@@ -15648,10 +15648,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>450942</v>
+        <v>450120</v>
       </c>
       <c r="R134" t="n">
-        <v>7054894</v>
+        <v>7054703</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15715,58 +15715,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125712965</v>
+        <v>125724620</v>
       </c>
       <c r="B135" t="n">
-        <v>56843</v>
+        <v>57651</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>450279</v>
+        <v>450942</v>
       </c>
       <c r="R135" t="n">
-        <v>7054063</v>
+        <v>7054894</v>
       </c>
       <c r="S135" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15793,19 +15783,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>13:00</t>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15816,69 +15801,74 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125724582</v>
+        <v>125712965</v>
       </c>
       <c r="B136" t="n">
-        <v>57651</v>
+        <v>56843</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>450120</v>
+        <v>450279</v>
       </c>
       <c r="R136" t="n">
-        <v>7054703</v>
+        <v>7054063</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15905,14 +15895,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15923,16 +15918,21 @@
       </c>
       <c r="AG136" t="b">
         <v>0</v>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -17445,10 +17445,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126056434</v>
+        <v>126056428</v>
       </c>
       <c r="B150" t="n">
-        <v>91250</v>
+        <v>57651</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17456,21 +17456,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17480,10 +17480,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>450397</v>
+        <v>450230</v>
       </c>
       <c r="R150" t="n">
-        <v>7054085</v>
+        <v>7054413</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17516,6 +17516,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17542,10 +17547,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126056428</v>
+        <v>126056434</v>
       </c>
       <c r="B151" t="n">
-        <v>57651</v>
+        <v>91250</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17553,21 +17558,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17577,10 +17582,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>450230</v>
+        <v>450397</v>
       </c>
       <c r="R151" t="n">
-        <v>7054413</v>
+        <v>7054085</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17613,11 +17618,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18144,7 +18144,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126056420</v>
+        <v>126056421</v>
       </c>
       <c r="B157" t="n">
         <v>57651</v>
@@ -18179,10 +18179,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>450415</v>
+        <v>450926</v>
       </c>
       <c r="R157" t="n">
-        <v>7054582</v>
+        <v>7054878</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18219,7 +18219,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18246,7 +18246,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126056419</v>
+        <v>126056420</v>
       </c>
       <c r="B158" t="n">
         <v>57651</v>
@@ -18281,10 +18281,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>450642</v>
+        <v>450415</v>
       </c>
       <c r="R158" t="n">
-        <v>7054903</v>
+        <v>7054582</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18321,7 +18321,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18348,7 +18348,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126056421</v>
+        <v>126056419</v>
       </c>
       <c r="B159" t="n">
         <v>57651</v>
@@ -18383,10 +18383,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>450926</v>
+        <v>450642</v>
       </c>
       <c r="R159" t="n">
-        <v>7054878</v>
+        <v>7054903</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>

--- a/artfynd/A 22902-2025 artfynd.xlsx
+++ b/artfynd/A 22902-2025 artfynd.xlsx
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125724585</v>
+        <v>125711059</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,34 +1659,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450232</v>
+        <v>450886</v>
       </c>
       <c r="R11" t="n">
-        <v>7054602</v>
+        <v>7054749</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,23 +1734,48 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125724599</v>
+        <v>125724592</v>
       </c>
       <c r="B12" t="n">
         <v>57651</v>
@@ -1785,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450306</v>
+        <v>450278</v>
       </c>
       <c r="R12" t="n">
-        <v>7054865</v>
+        <v>7054719</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1850,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1877,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125724619</v>
+        <v>125724585</v>
       </c>
       <c r="B13" t="n">
         <v>57651</v>
@@ -1887,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450958</v>
+        <v>450232</v>
       </c>
       <c r="R13" t="n">
-        <v>7054933</v>
+        <v>7054602</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125711059</v>
+        <v>125724599</v>
       </c>
       <c r="B14" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1965,34 +1990,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450886</v>
+        <v>450306</v>
       </c>
       <c r="R14" t="n">
-        <v>7054749</v>
+        <v>7054865</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2054,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2040,48 +2065,23 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125724592</v>
+        <v>125724619</v>
       </c>
       <c r="B15" t="n">
         <v>57651</v>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450278</v>
+        <v>450958</v>
       </c>
       <c r="R15" t="n">
-        <v>7054719</v>
+        <v>7054933</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3126,48 +3126,62 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125724565</v>
+        <v>125709103</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>98360</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Slättbrännorna, Slättbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>450606</v>
+        <v>451383</v>
       </c>
       <c r="R24" t="n">
-        <v>7054211</v>
+        <v>7055475</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3201,7 +3215,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 6 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3212,23 +3226,28 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125712711</v>
+        <v>125724565</v>
       </c>
       <c r="B25" t="n">
         <v>57651</v>
@@ -3257,29 +3276,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450410</v>
+        <v>450606</v>
       </c>
       <c r="R25" t="n">
-        <v>7054290</v>
+        <v>7054211</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3306,24 +3315,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  nära en stor myrstack.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3334,48 +3333,23 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125724593</v>
+        <v>125712711</v>
       </c>
       <c r="B26" t="n">
         <v>57651</v>
@@ -3404,19 +3378,29 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450274</v>
+        <v>450410</v>
       </c>
       <c r="R26" t="n">
-        <v>7054720</v>
+        <v>7054290</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3443,14 +3427,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran  nära en stor myrstack.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3461,23 +3455,48 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125724564</v>
+        <v>125724593</v>
       </c>
       <c r="B27" t="n">
         <v>57651</v>
@@ -3512,10 +3531,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>450638</v>
+        <v>450274</v>
       </c>
       <c r="R27" t="n">
-        <v>7054244</v>
+        <v>7054720</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3552,7 +3571,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3579,7 +3598,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125724574</v>
+        <v>125724564</v>
       </c>
       <c r="B28" t="n">
         <v>57651</v>
@@ -3614,10 +3633,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>450390</v>
+        <v>450638</v>
       </c>
       <c r="R28" t="n">
-        <v>7054071</v>
+        <v>7054244</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3681,7 +3700,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125724608</v>
+        <v>125724574</v>
       </c>
       <c r="B29" t="n">
         <v>57651</v>
@@ -3716,10 +3735,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>450441</v>
+        <v>450390</v>
       </c>
       <c r="R29" t="n">
-        <v>7054842</v>
+        <v>7054071</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3783,7 +3802,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125724573</v>
+        <v>125724608</v>
       </c>
       <c r="B30" t="n">
         <v>57651</v>
@@ -3818,10 +3837,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>450391</v>
+        <v>450441</v>
       </c>
       <c r="R30" t="n">
-        <v>7054076</v>
+        <v>7054842</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3858,7 +3877,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3885,7 +3904,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125724572</v>
+        <v>125724573</v>
       </c>
       <c r="B31" t="n">
         <v>57651</v>
@@ -3920,10 +3939,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>450406</v>
+        <v>450391</v>
       </c>
       <c r="R31" t="n">
-        <v>7054072</v>
+        <v>7054076</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3960,7 +3979,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3987,10 +4006,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125717532</v>
+        <v>125724572</v>
       </c>
       <c r="B32" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3998,34 +4017,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>450948</v>
+        <v>450406</v>
       </c>
       <c r="R32" t="n">
-        <v>7054739</v>
+        <v>7054072</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4055,24 +4074,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4083,94 +4092,64 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125715130</v>
+        <v>125717532</v>
       </c>
       <c r="B33" t="n">
-        <v>80111</v>
+        <v>78972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450363</v>
+        <v>450948</v>
       </c>
       <c r="R33" t="n">
-        <v>7054211</v>
+        <v>7054739</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4199,7 +4178,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4209,12 +4188,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4228,27 +4207,27 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4266,10 +4245,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125709103</v>
+        <v>125715130</v>
       </c>
       <c r="B34" t="n">
-        <v>98360</v>
+        <v>80111</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4277,51 +4256,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Slättbrännorna, Slättbrännorna, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451383</v>
+        <v>450363</v>
       </c>
       <c r="R34" t="n">
-        <v>7055475</v>
+        <v>7054211</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4348,14 +4318,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Minst 6 plantor inom ca 1 m2 yta.</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4369,7 +4349,27 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4387,38 +4387,47 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125716595</v>
+        <v>125711207</v>
       </c>
       <c r="B35" t="n">
-        <v>57651</v>
+        <v>98360</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4428,14 +4437,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>450481</v>
+        <v>450852</v>
       </c>
       <c r="R35" t="n">
-        <v>7054352</v>
+        <v>7054681</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4465,24 +4474,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
+          <t>Minst 17 plantor inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4497,26 +4496,6 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4534,10 +4513,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125724603</v>
+        <v>125724627</v>
       </c>
       <c r="B36" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4545,21 +4524,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4569,10 +4548,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>450339</v>
+        <v>450528</v>
       </c>
       <c r="R36" t="n">
-        <v>7054827</v>
+        <v>7054102</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4605,11 +4584,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4636,7 +4610,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125724613</v>
+        <v>125716595</v>
       </c>
       <c r="B37" t="n">
         <v>57651</v>
@@ -4665,16 +4639,26 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>450714</v>
+        <v>450481</v>
       </c>
       <c r="R37" t="n">
-        <v>7055072</v>
+        <v>7054352</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4704,14 +4688,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4722,26 +4716,51 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125724627</v>
+        <v>125724603</v>
       </c>
       <c r="B38" t="n">
-        <v>80075</v>
+        <v>57651</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4749,21 +4768,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4773,10 +4792,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450528</v>
+        <v>450339</v>
       </c>
       <c r="R38" t="n">
-        <v>7054102</v>
+        <v>7054827</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4809,6 +4828,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4835,64 +4859,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125711207</v>
+        <v>125724613</v>
       </c>
       <c r="B39" t="n">
-        <v>98360</v>
+        <v>57651</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>450852</v>
+        <v>450714</v>
       </c>
       <c r="R39" t="n">
-        <v>7054681</v>
+        <v>7055072</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4929,7 +4934,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Minst 17 plantor inom ca 2 m2 yta.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4940,28 +4945,23 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125708223</v>
+        <v>125710168</v>
       </c>
       <c r="B40" t="n">
         <v>78972</v>
@@ -4996,10 +4996,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>451292</v>
+        <v>451182</v>
       </c>
       <c r="R40" t="n">
-        <v>7055142</v>
+        <v>7055004</v>
       </c>
       <c r="S40" t="n">
         <v>8</v>
@@ -5029,19 +5029,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>09:34</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5052,31 +5047,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5093,10 +5063,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125715396</v>
+        <v>125724631</v>
       </c>
       <c r="B41" t="n">
-        <v>78972</v>
+        <v>91250</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5104,37 +5074,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>450394</v>
+        <v>450196</v>
       </c>
       <c r="R41" t="n">
-        <v>7054235</v>
+        <v>7054664</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5178,19 +5148,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125710168</v>
+        <v>125708223</v>
       </c>
       <c r="B42" t="n">
         <v>78972</v>
@@ -5225,10 +5195,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>451182</v>
+        <v>451292</v>
       </c>
       <c r="R42" t="n">
-        <v>7055004</v>
+        <v>7055142</v>
       </c>
       <c r="S42" t="n">
         <v>8</v>
@@ -5258,14 +5228,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5276,6 +5251,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5292,10 +5292,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125724631</v>
+        <v>125715396</v>
       </c>
       <c r="B43" t="n">
-        <v>91250</v>
+        <v>78972</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5303,37 +5303,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>450196</v>
+        <v>450394</v>
       </c>
       <c r="R43" t="n">
-        <v>7054664</v>
+        <v>7054235</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5377,12 +5377,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5491,7 +5491,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125724556</v>
+        <v>125724594</v>
       </c>
       <c r="B45" t="n">
         <v>57651</v>
@@ -5526,10 +5526,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>450878</v>
+        <v>450285</v>
       </c>
       <c r="R45" t="n">
-        <v>7054550</v>
+        <v>7054794</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5593,7 +5593,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125724594</v>
+        <v>125724556</v>
       </c>
       <c r="B46" t="n">
         <v>57651</v>
@@ -5628,10 +5628,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>450285</v>
+        <v>450878</v>
       </c>
       <c r="R46" t="n">
-        <v>7054794</v>
+        <v>7054550</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6742,48 +6742,62 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125724606</v>
+        <v>125709578</v>
       </c>
       <c r="B56" t="n">
-        <v>57651</v>
+        <v>98360</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>450436</v>
+        <v>451288</v>
       </c>
       <c r="R56" t="n">
-        <v>7054836</v>
+        <v>7055288</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6817,7 +6831,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 10 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6828,26 +6842,31 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125724554</v>
+        <v>125710504</v>
       </c>
       <c r="B57" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6855,37 +6874,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>450796</v>
+        <v>451089</v>
       </c>
       <c r="R57" t="n">
-        <v>7054404</v>
+        <v>7054989</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6919,7 +6938,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6930,23 +6949,48 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125709678</v>
+        <v>125711291</v>
       </c>
       <c r="B58" t="n">
         <v>78972</v>
@@ -6981,13 +7025,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451218</v>
+        <v>450795</v>
       </c>
       <c r="R58" t="n">
-        <v>7055148</v>
+        <v>7054803</v>
       </c>
       <c r="S58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7019,6 +7063,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flertalet granar.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7030,7 +7079,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
@@ -7068,10 +7117,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125710504</v>
+        <v>125724606</v>
       </c>
       <c r="B59" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7079,37 +7128,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451089</v>
+        <v>450436</v>
       </c>
       <c r="R59" t="n">
-        <v>7054989</v>
+        <v>7054836</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7143,7 +7192,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7154,51 +7203,26 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125711291</v>
+        <v>125724554</v>
       </c>
       <c r="B60" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7206,37 +7230,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>450795</v>
+        <v>450796</v>
       </c>
       <c r="R60" t="n">
-        <v>7054803</v>
+        <v>7054404</v>
       </c>
       <c r="S60" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7270,7 +7294,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7281,103 +7305,64 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125709578</v>
+        <v>125709678</v>
       </c>
       <c r="B61" t="n">
-        <v>98360</v>
+        <v>78972</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>451288</v>
+        <v>451218</v>
       </c>
       <c r="R61" t="n">
-        <v>7055288</v>
+        <v>7055148</v>
       </c>
       <c r="S61" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7409,11 +7394,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7426,6 +7406,26 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7443,62 +7443,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125716316</v>
+        <v>125714547</v>
       </c>
       <c r="B62" t="n">
-        <v>98360</v>
+        <v>78972</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>450483</v>
+        <v>450361</v>
       </c>
       <c r="R62" t="n">
-        <v>7054352</v>
+        <v>7054101</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7527,7 +7513,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7537,7 +7523,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7552,6 +7538,26 @@
       <c r="AH62" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7569,48 +7575,62 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125714547</v>
+        <v>125716316</v>
       </c>
       <c r="B63" t="n">
-        <v>78972</v>
+        <v>98360</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>450361</v>
+        <v>450483</v>
       </c>
       <c r="R63" t="n">
-        <v>7054101</v>
+        <v>7054352</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7639,7 +7659,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7649,7 +7669,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7664,26 +7684,6 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8411,10 +8411,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125716115</v>
+        <v>125724544</v>
       </c>
       <c r="B70" t="n">
-        <v>78972</v>
+        <v>91232</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8422,37 +8422,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>450545</v>
+        <v>450929</v>
       </c>
       <c r="R70" t="n">
-        <v>7054277</v>
+        <v>7054588</v>
       </c>
       <c r="S70" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8479,19 +8479,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8506,22 +8496,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125724544</v>
+        <v>125716115</v>
       </c>
       <c r="B71" t="n">
-        <v>91232</v>
+        <v>78972</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8529,37 +8519,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>450929</v>
+        <v>450545</v>
       </c>
       <c r="R71" t="n">
-        <v>7054588</v>
+        <v>7054277</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8586,9 +8576,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8603,12 +8603,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -9113,67 +9113,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125718167</v>
+        <v>125724545</v>
       </c>
       <c r="B76" t="n">
-        <v>98360</v>
+        <v>91232</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>451146</v>
+        <v>450771</v>
       </c>
       <c r="R76" t="n">
-        <v>7054932</v>
+        <v>7055042</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9200,26 +9181,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Minst 14 plantor inom ca 1 m2.</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9228,31 +9194,26 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125724545</v>
+        <v>125715929</v>
       </c>
       <c r="B77" t="n">
-        <v>91232</v>
+        <v>78972</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9260,37 +9221,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>450771</v>
+        <v>450435</v>
       </c>
       <c r="R77" t="n">
-        <v>7055042</v>
+        <v>7054165</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9317,9 +9278,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9334,22 +9305,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125715929</v>
+        <v>125724584</v>
       </c>
       <c r="B78" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9357,37 +9328,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>450435</v>
+        <v>450230</v>
       </c>
       <c r="R78" t="n">
-        <v>7054165</v>
+        <v>7054621</v>
       </c>
       <c r="S78" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9414,19 +9385,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>15:26</t>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9441,19 +9407,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125724584</v>
+        <v>125724550</v>
       </c>
       <c r="B79" t="n">
         <v>57651</v>
@@ -9488,10 +9454,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>450230</v>
+        <v>450437</v>
       </c>
       <c r="R79" t="n">
-        <v>7054621</v>
+        <v>7054480</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9555,7 +9521,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125724550</v>
+        <v>125724578</v>
       </c>
       <c r="B80" t="n">
         <v>57651</v>
@@ -9590,10 +9556,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>450437</v>
+        <v>450228</v>
       </c>
       <c r="R80" t="n">
-        <v>7054480</v>
+        <v>7054435</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9657,48 +9623,67 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125724578</v>
+        <v>125718167</v>
       </c>
       <c r="B81" t="n">
-        <v>57651</v>
+        <v>98360</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>450228</v>
+        <v>451146</v>
       </c>
       <c r="R81" t="n">
-        <v>7054435</v>
+        <v>7054932</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9725,14 +9710,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Minst 14 plantor inom ca 1 m2.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9743,16 +9738,21 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -10162,10 +10162,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125710745</v>
+        <v>125724605</v>
       </c>
       <c r="B86" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10173,37 +10173,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>451035</v>
+        <v>450357</v>
       </c>
       <c r="R86" t="n">
-        <v>7054940</v>
+        <v>7054800</v>
       </c>
       <c r="S86" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10248,48 +10248,23 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125724605</v>
+        <v>125715345</v>
       </c>
       <c r="B87" t="n">
         <v>57651</v>
@@ -10318,16 +10293,26 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>450357</v>
+        <v>450372</v>
       </c>
       <c r="R87" t="n">
-        <v>7054800</v>
+        <v>7054250</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10357,14 +10342,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en död liggande gran precis öster om vägen.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10375,23 +10370,48 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125715345</v>
+        <v>125724587</v>
       </c>
       <c r="B88" t="n">
         <v>57651</v>
@@ -10420,26 +10440,16 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>450372</v>
+        <v>450279</v>
       </c>
       <c r="R88" t="n">
-        <v>7054250</v>
+        <v>7054606</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10469,24 +10479,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en död liggande gran precis öster om vägen.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10497,48 +10497,23 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125724587</v>
+        <v>125715883</v>
       </c>
       <c r="B89" t="n">
         <v>57651</v>
@@ -10567,19 +10542,29 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>450279</v>
+        <v>450371</v>
       </c>
       <c r="R89" t="n">
-        <v>7054606</v>
+        <v>7054182</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10606,14 +10591,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en något smalare gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10624,74 +10619,103 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125715883</v>
+        <v>125708960</v>
       </c>
       <c r="B90" t="n">
-        <v>57651</v>
+        <v>98360</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>450371</v>
+        <v>451445</v>
       </c>
       <c r="R90" t="n">
-        <v>7054182</v>
+        <v>7055383</v>
       </c>
       <c r="S90" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10718,24 +10742,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en något smalare gran.</t>
+          <t>Minst 29 plantor inom ca 2 m2.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10750,26 +10764,6 @@
       <c r="AH90" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10787,62 +10781,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125708960</v>
+        <v>125710745</v>
       </c>
       <c r="B91" t="n">
-        <v>98360</v>
+        <v>78972</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>451445</v>
+        <v>451035</v>
       </c>
       <c r="R91" t="n">
-        <v>7055383</v>
+        <v>7054940</v>
       </c>
       <c r="S91" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10876,7 +10856,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Minst 29 plantor inom ca 2 m2.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10891,6 +10871,26 @@
       <c r="AH91" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11496,62 +11496,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125712767</v>
+        <v>125709922</v>
       </c>
       <c r="B97" t="n">
-        <v>98360</v>
+        <v>78972</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>450391</v>
+        <v>451225</v>
       </c>
       <c r="R97" t="n">
-        <v>7054281</v>
+        <v>7055093</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11578,24 +11564,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Minst 20 plantor inom ca 2 m2 yta.</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11627,7 +11603,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125709922</v>
+        <v>125718221</v>
       </c>
       <c r="B98" t="n">
         <v>78972</v>
@@ -11662,13 +11638,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>451225</v>
+        <v>451172</v>
       </c>
       <c r="R98" t="n">
-        <v>7055093</v>
+        <v>7054946</v>
       </c>
       <c r="S98" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11695,14 +11671,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11713,11 +11694,6 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -11734,10 +11710,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125718221</v>
+        <v>125715109</v>
       </c>
       <c r="B99" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11745,37 +11721,42 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>451172</v>
+        <v>450365</v>
       </c>
       <c r="R99" t="n">
-        <v>7054946</v>
+        <v>7054197</v>
       </c>
       <c r="S99" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11804,7 +11785,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11814,7 +11795,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11825,6 +11811,31 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -11841,10 +11852,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125715109</v>
+        <v>125724609</v>
       </c>
       <c r="B100" t="n">
-        <v>80076</v>
+        <v>57651</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11852,39 +11863,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>450365</v>
+        <v>450581</v>
       </c>
       <c r="R100" t="n">
-        <v>7054197</v>
+        <v>7055012</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11914,24 +11920,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11942,48 +11938,23 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125724609</v>
+        <v>125724546</v>
       </c>
       <c r="B101" t="n">
         <v>57651</v>
@@ -12018,10 +11989,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>450581</v>
+        <v>451102</v>
       </c>
       <c r="R101" t="n">
-        <v>7055012</v>
+        <v>7054896</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12085,7 +12056,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125724546</v>
+        <v>125724566</v>
       </c>
       <c r="B102" t="n">
         <v>57651</v>
@@ -12120,10 +12091,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>451102</v>
+        <v>450600</v>
       </c>
       <c r="R102" t="n">
-        <v>7054896</v>
+        <v>7054142</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12187,7 +12158,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125724566</v>
+        <v>125724551</v>
       </c>
       <c r="B103" t="n">
         <v>57651</v>
@@ -12222,10 +12193,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>450600</v>
+        <v>450486</v>
       </c>
       <c r="R103" t="n">
-        <v>7054142</v>
+        <v>7054445</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12289,7 +12260,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125724551</v>
+        <v>125724621</v>
       </c>
       <c r="B104" t="n">
         <v>57651</v>
@@ -12324,10 +12295,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>450486</v>
+        <v>450933</v>
       </c>
       <c r="R104" t="n">
-        <v>7054445</v>
+        <v>7054883</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12364,7 +12335,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12391,7 +12362,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125724621</v>
+        <v>125715238</v>
       </c>
       <c r="B105" t="n">
         <v>57651</v>
@@ -12420,16 +12391,26 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>450933</v>
+        <v>450342</v>
       </c>
       <c r="R105" t="n">
-        <v>7054883</v>
+        <v>7054212</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12459,14 +12440,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran  precis öster om vägen.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12477,23 +12468,48 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125715238</v>
+        <v>125724618</v>
       </c>
       <c r="B106" t="n">
         <v>57651</v>
@@ -12522,26 +12538,16 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>450342</v>
+        <v>450905</v>
       </c>
       <c r="R106" t="n">
-        <v>7054212</v>
+        <v>7054898</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12571,24 +12577,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  precis öster om vägen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12599,48 +12595,23 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125724618</v>
+        <v>125724577</v>
       </c>
       <c r="B107" t="n">
         <v>57651</v>
@@ -12675,10 +12646,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>450905</v>
+        <v>450259</v>
       </c>
       <c r="R107" t="n">
-        <v>7054898</v>
+        <v>7054380</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12742,45 +12713,59 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125724577</v>
+        <v>125712767</v>
       </c>
       <c r="B108" t="n">
-        <v>57651</v>
+        <v>98360</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>450259</v>
+        <v>450391</v>
       </c>
       <c r="R108" t="n">
-        <v>7054380</v>
+        <v>7054281</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12810,14 +12795,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 20 plantor inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12828,16 +12823,21 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -15613,7 +15613,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125724582</v>
+        <v>125724620</v>
       </c>
       <c r="B134" t="n">
         <v>57651</v>
@@ -15648,10 +15648,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>450120</v>
+        <v>450942</v>
       </c>
       <c r="R134" t="n">
-        <v>7054703</v>
+        <v>7054894</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15715,48 +15715,58 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125724620</v>
+        <v>125712965</v>
       </c>
       <c r="B135" t="n">
-        <v>57651</v>
+        <v>56843</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>450942</v>
+        <v>450279</v>
       </c>
       <c r="R135" t="n">
-        <v>7054894</v>
+        <v>7054063</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15783,14 +15793,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15801,74 +15816,69 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125712965</v>
+        <v>125724582</v>
       </c>
       <c r="B136" t="n">
-        <v>56843</v>
+        <v>57651</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>450279</v>
+        <v>450120</v>
       </c>
       <c r="R136" t="n">
-        <v>7054063</v>
+        <v>7054703</v>
       </c>
       <c r="S136" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15895,19 +15905,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>13:00</t>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15918,21 +15923,16 @@
       </c>
       <c r="AG136" t="b">
         <v>0</v>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -17445,10 +17445,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126056428</v>
+        <v>126056434</v>
       </c>
       <c r="B150" t="n">
-        <v>57651</v>
+        <v>91250</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17456,21 +17456,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17480,10 +17480,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>450230</v>
+        <v>450397</v>
       </c>
       <c r="R150" t="n">
-        <v>7054413</v>
+        <v>7054085</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17516,11 +17516,6 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17547,10 +17542,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126056434</v>
+        <v>126056428</v>
       </c>
       <c r="B151" t="n">
-        <v>91250</v>
+        <v>57651</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17558,21 +17553,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17582,10 +17577,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>450397</v>
+        <v>450230</v>
       </c>
       <c r="R151" t="n">
-        <v>7054085</v>
+        <v>7054413</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17618,6 +17613,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD151" t="b">

--- a/artfynd/A 22902-2025 artfynd.xlsx
+++ b/artfynd/A 22902-2025 artfynd.xlsx
@@ -4387,64 +4387,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125711207</v>
+        <v>125724627</v>
       </c>
       <c r="B35" t="n">
-        <v>98362</v>
+        <v>80076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>450852</v>
+        <v>450528</v>
       </c>
       <c r="R35" t="n">
-        <v>7054681</v>
+        <v>7054102</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4479,11 +4460,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Minst 17 plantor inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4492,66 +4468,80 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125724627</v>
+        <v>125711207</v>
       </c>
       <c r="B36" t="n">
-        <v>80076</v>
+        <v>98362</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>450528</v>
+        <v>450852</v>
       </c>
       <c r="R36" t="n">
-        <v>7054102</v>
+        <v>7054681</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4586,6 +4576,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Minst 17 plantor inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4594,16 +4589,21 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4961,10 +4961,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125724594</v>
+        <v>125710168</v>
       </c>
       <c r="B40" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4972,37 +4972,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>450285</v>
+        <v>451182</v>
       </c>
       <c r="R40" t="n">
-        <v>7054794</v>
+        <v>7055004</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5051,22 +5051,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125724580</v>
+        <v>125708223</v>
       </c>
       <c r="B41" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5074,37 +5074,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>450072</v>
+        <v>451292</v>
       </c>
       <c r="R41" t="n">
-        <v>7054712</v>
+        <v>7055142</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5131,14 +5131,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5149,23 +5154,48 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125710168</v>
+        <v>125715396</v>
       </c>
       <c r="B42" t="n">
         <v>78973</v>
@@ -5196,17 +5226,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>451182</v>
+        <v>450394</v>
       </c>
       <c r="R42" t="n">
-        <v>7055004</v>
+        <v>7054235</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5236,11 +5266,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5267,10 +5292,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125708223</v>
+        <v>125724594</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5278,37 +5303,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>451292</v>
+        <v>450285</v>
       </c>
       <c r="R43" t="n">
-        <v>7055142</v>
+        <v>7054794</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5335,19 +5360,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>09:34</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5358,51 +5378,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125715396</v>
+        <v>125724556</v>
       </c>
       <c r="B44" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5410,37 +5405,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>450394</v>
+        <v>450878</v>
       </c>
       <c r="R44" t="n">
-        <v>7054235</v>
+        <v>7054550</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5470,6 +5465,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5484,22 +5484,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125724556</v>
+        <v>125724631</v>
       </c>
       <c r="B45" t="n">
-        <v>57652</v>
+        <v>91252</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5507,21 +5507,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5531,10 +5531,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>450878</v>
+        <v>450196</v>
       </c>
       <c r="R45" t="n">
-        <v>7054550</v>
+        <v>7054664</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5567,11 +5567,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5598,10 +5593,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125724631</v>
+        <v>125724580</v>
       </c>
       <c r="B46" t="n">
-        <v>91252</v>
+        <v>57652</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5609,21 +5604,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5633,10 +5628,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>450196</v>
+        <v>450072</v>
       </c>
       <c r="R46" t="n">
-        <v>7054664</v>
+        <v>7054712</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5669,6 +5664,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6742,10 +6742,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125724606</v>
+        <v>125710504</v>
       </c>
       <c r="B56" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6753,37 +6753,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>450436</v>
+        <v>451089</v>
       </c>
       <c r="R56" t="n">
-        <v>7054836</v>
+        <v>7054989</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6828,26 +6828,51 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125724554</v>
+        <v>125711291</v>
       </c>
       <c r="B57" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6855,37 +6880,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>450796</v>
+        <v>450795</v>
       </c>
       <c r="R57" t="n">
-        <v>7054404</v>
+        <v>7054803</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6919,7 +6944,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6930,23 +6955,48 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125710504</v>
+        <v>125709678</v>
       </c>
       <c r="B58" t="n">
         <v>78973</v>
@@ -6981,13 +7031,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451089</v>
+        <v>451218</v>
       </c>
       <c r="R58" t="n">
-        <v>7054989</v>
+        <v>7055148</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7019,11 +7069,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flertalet granar.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7035,7 +7080,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
@@ -7073,10 +7118,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125711291</v>
+        <v>125724606</v>
       </c>
       <c r="B59" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7084,37 +7129,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>450795</v>
+        <v>450436</v>
       </c>
       <c r="R59" t="n">
-        <v>7054803</v>
+        <v>7054836</v>
       </c>
       <c r="S59" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7148,7 +7193,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7159,51 +7204,26 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125709678</v>
+        <v>125724554</v>
       </c>
       <c r="B60" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7211,37 +7231,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>451218</v>
+        <v>450796</v>
       </c>
       <c r="R60" t="n">
-        <v>7055148</v>
+        <v>7054404</v>
       </c>
       <c r="S60" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7273,6 +7293,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7281,41 +7306,16 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7930,10 +7930,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125724626</v>
+        <v>125717826</v>
       </c>
       <c r="B66" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7941,37 +7941,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>450584</v>
+        <v>451046</v>
       </c>
       <c r="R66" t="n">
-        <v>7054245</v>
+        <v>7054820</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7998,11 +7998,26 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Långväxta bålar i god mängd.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8011,26 +8026,51 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125717826</v>
+        <v>125724626</v>
       </c>
       <c r="B67" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8038,37 +8078,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>451046</v>
+        <v>450584</v>
       </c>
       <c r="R67" t="n">
-        <v>7054820</v>
+        <v>7054245</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8095,26 +8135,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Långväxta bålar i god mängd.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8123,41 +8148,16 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8290,48 +8290,62 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125724544</v>
+        <v>125708839</v>
       </c>
       <c r="B69" t="n">
-        <v>91234</v>
+        <v>98362</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>450929</v>
+        <v>451394</v>
       </c>
       <c r="R69" t="n">
-        <v>7054588</v>
+        <v>7055346</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8363,6 +8377,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor inom ca 2 m2.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8371,26 +8390,31 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125716115</v>
+        <v>125724544</v>
       </c>
       <c r="B70" t="n">
-        <v>78973</v>
+        <v>91234</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8398,37 +8422,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>450545</v>
+        <v>450929</v>
       </c>
       <c r="R70" t="n">
-        <v>7054277</v>
+        <v>7054588</v>
       </c>
       <c r="S70" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8455,19 +8479,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8482,22 +8496,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125715668</v>
+        <v>125716115</v>
       </c>
       <c r="B71" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8505,47 +8519,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>450399</v>
+        <v>450545</v>
       </c>
       <c r="R71" t="n">
-        <v>7054150</v>
+        <v>7054277</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8574,7 +8578,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8584,12 +8588,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8600,31 +8599,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8641,7 +8615,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125724596</v>
+        <v>125715668</v>
       </c>
       <c r="B72" t="n">
         <v>57652</v>
@@ -8670,16 +8644,26 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>450286</v>
+        <v>450399</v>
       </c>
       <c r="R72" t="n">
-        <v>7054789</v>
+        <v>7054150</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8709,14 +8693,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8727,23 +8721,48 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125712863</v>
+        <v>125724596</v>
       </c>
       <c r="B73" t="n">
         <v>57652</v>
@@ -8772,29 +8791,19 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>450351</v>
+        <v>450286</v>
       </c>
       <c r="R73" t="n">
-        <v>7054230</v>
+        <v>7054789</v>
       </c>
       <c r="S73" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8821,24 +8830,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran nära vägen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8849,48 +8848,23 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125724576</v>
+        <v>125712863</v>
       </c>
       <c r="B74" t="n">
         <v>57652</v>
@@ -8919,19 +8893,29 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>450258</v>
+        <v>450351</v>
       </c>
       <c r="R74" t="n">
-        <v>7054372</v>
+        <v>7054230</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8958,14 +8942,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gran nära vägen.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8976,78 +8970,89 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125708839</v>
+        <v>125724576</v>
       </c>
       <c r="B75" t="n">
-        <v>98362</v>
+        <v>57652</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>451394</v>
+        <v>450258</v>
       </c>
       <c r="R75" t="n">
-        <v>7055346</v>
+        <v>7054372</v>
       </c>
       <c r="S75" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9081,7 +9086,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Minst 25 plantor inom ca 2 m2.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9092,21 +9097,16 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9759,10 +9759,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125709469</v>
+        <v>125724569</v>
       </c>
       <c r="B82" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9770,34 +9770,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>451269</v>
+        <v>450437</v>
       </c>
       <c r="R82" t="n">
-        <v>7055329</v>
+        <v>7054064</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9832,6 +9832,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9844,19 +9849,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125724569</v>
+        <v>125724588</v>
       </c>
       <c r="B83" t="n">
         <v>57652</v>
@@ -9891,10 +9896,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>450437</v>
+        <v>450275</v>
       </c>
       <c r="R83" t="n">
-        <v>7054064</v>
+        <v>7054607</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9931,7 +9936,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9958,7 +9963,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125724588</v>
+        <v>125724568</v>
       </c>
       <c r="B84" t="n">
         <v>57652</v>
@@ -9993,10 +9998,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>450275</v>
+        <v>450530</v>
       </c>
       <c r="R84" t="n">
-        <v>7054607</v>
+        <v>7054095</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10033,7 +10038,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10060,10 +10065,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125724568</v>
+        <v>125709469</v>
       </c>
       <c r="B85" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10071,34 +10076,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>450530</v>
+        <v>451269</v>
       </c>
       <c r="R85" t="n">
-        <v>7054095</v>
+        <v>7055329</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10133,11 +10138,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10150,70 +10150,74 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125715883</v>
+        <v>125708960</v>
       </c>
       <c r="B86" t="n">
-        <v>57652</v>
+        <v>98362</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>450371</v>
+        <v>451445</v>
       </c>
       <c r="R86" t="n">
-        <v>7054182</v>
+        <v>7055383</v>
       </c>
       <c r="S86" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10240,24 +10244,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en något smalare gran.</t>
+          <t>Minst 29 plantor inom ca 2 m2.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10272,26 +10266,6 @@
       <c r="AH86" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10309,62 +10283,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125708960</v>
+        <v>125710745</v>
       </c>
       <c r="B87" t="n">
-        <v>98362</v>
+        <v>78973</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>451445</v>
+        <v>451035</v>
       </c>
       <c r="R87" t="n">
-        <v>7055383</v>
+        <v>7054940</v>
       </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10398,7 +10358,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Minst 29 plantor inom ca 2 m2.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10413,6 +10373,26 @@
       <c r="AH87" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10430,10 +10410,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125710745</v>
+        <v>125724605</v>
       </c>
       <c r="B88" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10441,37 +10421,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>451035</v>
+        <v>450357</v>
       </c>
       <c r="R88" t="n">
-        <v>7054940</v>
+        <v>7054800</v>
       </c>
       <c r="S88" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10505,7 +10485,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10516,48 +10496,23 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125724605</v>
+        <v>125715345</v>
       </c>
       <c r="B89" t="n">
         <v>57652</v>
@@ -10586,16 +10541,26 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>450357</v>
+        <v>450372</v>
       </c>
       <c r="R89" t="n">
-        <v>7054800</v>
+        <v>7054250</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10625,14 +10590,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en död liggande gran precis öster om vägen.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10643,23 +10618,48 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125715345</v>
+        <v>125724587</v>
       </c>
       <c r="B90" t="n">
         <v>57652</v>
@@ -10688,26 +10688,16 @@
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>450372</v>
+        <v>450279</v>
       </c>
       <c r="R90" t="n">
-        <v>7054250</v>
+        <v>7054606</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10737,24 +10727,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en död liggande gran precis öster om vägen.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10765,48 +10745,23 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125724587</v>
+        <v>125715883</v>
       </c>
       <c r="B91" t="n">
         <v>57652</v>
@@ -10835,19 +10790,29 @@
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>450279</v>
+        <v>450371</v>
       </c>
       <c r="R91" t="n">
-        <v>7054606</v>
+        <v>7054182</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10874,14 +10839,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en något smalare gran.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10892,78 +10867,89 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125708590</v>
+        <v>125724543</v>
       </c>
       <c r="B92" t="n">
-        <v>98362</v>
+        <v>91592</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221952</v>
+        <v>2062</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>451359</v>
+        <v>450931</v>
       </c>
       <c r="R92" t="n">
-        <v>7055225</v>
+        <v>7054587</v>
       </c>
       <c r="S92" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10990,94 +10976,94 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 3 m2.</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125724543</v>
+        <v>125710515</v>
       </c>
       <c r="B93" t="n">
-        <v>91592</v>
+        <v>58021</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2062</v>
+        <v>103015</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>450931</v>
+        <v>451089</v>
       </c>
       <c r="R93" t="n">
-        <v>7054587</v>
+        <v>7054975</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11107,30 +11093,44 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -11239,32 +11239,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125710515</v>
+        <v>125714169</v>
       </c>
       <c r="B95" t="n">
-        <v>58021</v>
+        <v>57812</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -11272,14 +11272,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -11289,17 +11284,17 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>451089</v>
+        <v>450226</v>
       </c>
       <c r="R95" t="n">
-        <v>7054975</v>
+        <v>7054095</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11328,7 +11323,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11338,7 +11333,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11352,7 +11347,7 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11370,62 +11365,62 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125714169</v>
+        <v>125708590</v>
       </c>
       <c r="B96" t="n">
-        <v>57812</v>
+        <v>98362</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>450226</v>
+        <v>451359</v>
       </c>
       <c r="R96" t="n">
-        <v>7054095</v>
+        <v>7055225</v>
       </c>
       <c r="S96" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11454,7 +11449,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11464,7 +11459,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 3 m2.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12844,10 +12844,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125724549</v>
+        <v>125712294</v>
       </c>
       <c r="B109" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12855,37 +12855,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storholmen, Storholmen, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>450547</v>
+        <v>450461</v>
       </c>
       <c r="R109" t="n">
-        <v>7054823</v>
+        <v>7054536</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12912,14 +12912,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12930,23 +12940,48 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125724586</v>
+        <v>125724552</v>
       </c>
       <c r="B110" t="n">
         <v>57652</v>
@@ -12981,10 +13016,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>450292</v>
+        <v>450545</v>
       </c>
       <c r="R110" t="n">
-        <v>7054587</v>
+        <v>7054416</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13021,7 +13056,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13048,10 +13083,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125724558</v>
+        <v>125712133</v>
       </c>
       <c r="B111" t="n">
-        <v>57652</v>
+        <v>58131</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13059,37 +13094,56 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>103018</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>450702</v>
+        <v>450497</v>
       </c>
       <c r="R111" t="n">
-        <v>7054428</v>
+        <v>7054617</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13116,14 +13170,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>En sjungande hane i ett stråk med en del asp.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13134,26 +13198,31 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125712294</v>
+        <v>125724549</v>
       </c>
       <c r="B112" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13161,37 +13230,37 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Storholmen, Storholmen, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>450461</v>
+        <v>450547</v>
       </c>
       <c r="R112" t="n">
-        <v>7054536</v>
+        <v>7054823</v>
       </c>
       <c r="S112" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13218,24 +13287,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13246,48 +13305,23 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125724552</v>
+        <v>125724586</v>
       </c>
       <c r="B113" t="n">
         <v>57652</v>
@@ -13322,10 +13356,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>450545</v>
+        <v>450292</v>
       </c>
       <c r="R113" t="n">
-        <v>7054416</v>
+        <v>7054587</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13362,7 +13396,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13389,10 +13423,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125712133</v>
+        <v>125724558</v>
       </c>
       <c r="B114" t="n">
-        <v>58131</v>
+        <v>57652</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13400,56 +13434,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103018</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>450497</v>
+        <v>450702</v>
       </c>
       <c r="R114" t="n">
-        <v>7054617</v>
+        <v>7054428</v>
       </c>
       <c r="S114" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13476,24 +13491,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>En sjungande hane i ett stråk med en del asp.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13504,21 +13509,16 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>

--- a/artfynd/A 22902-2025 artfynd.xlsx
+++ b/artfynd/A 22902-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125711912</v>
+        <v>125708514</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,47 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450518</v>
+        <v>451330</v>
       </c>
       <c r="R2" t="n">
-        <v>7054696</v>
+        <v>7055192</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,26 +743,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -781,11 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -802,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125724579</v>
+        <v>125724629</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>91254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450145</v>
+        <v>450502</v>
       </c>
       <c r="R3" t="n">
-        <v>7054502</v>
+        <v>7054507</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125724597</v>
+        <v>125724628</v>
       </c>
       <c r="B4" t="n">
-        <v>57652</v>
+        <v>91254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450287</v>
+        <v>451229</v>
       </c>
       <c r="R4" t="n">
-        <v>7054787</v>
+        <v>7055028</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125724610</v>
+        <v>125711912</v>
       </c>
       <c r="B5" t="n">
         <v>57652</v>
@@ -1035,19 +995,29 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450597</v>
+        <v>450518</v>
       </c>
       <c r="R5" t="n">
-        <v>7055031</v>
+        <v>7054696</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,14 +1044,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,26 +1072,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125708514</v>
+        <v>125724579</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,37 +1104,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451330</v>
+        <v>450145</v>
       </c>
       <c r="R6" t="n">
-        <v>7055192</v>
+        <v>7054502</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1179,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125724629</v>
+        <v>125714988</v>
       </c>
       <c r="B7" t="n">
-        <v>91252</v>
+        <v>57652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,34 +1206,44 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>450502</v>
+        <v>450413</v>
       </c>
       <c r="R7" t="n">
-        <v>7054507</v>
+        <v>7054149</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,11 +1273,26 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1286,26 +1301,51 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125724628</v>
+        <v>125724597</v>
       </c>
       <c r="B8" t="n">
-        <v>91252</v>
+        <v>57652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,21 +1353,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451229</v>
+        <v>450287</v>
       </c>
       <c r="R8" t="n">
-        <v>7055028</v>
+        <v>7054787</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,6 +1413,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,7 +1444,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125714988</v>
+        <v>125724591</v>
       </c>
       <c r="B9" t="n">
         <v>57652</v>
@@ -1428,26 +1473,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>450413</v>
+        <v>450270</v>
       </c>
       <c r="R9" t="n">
-        <v>7054149</v>
+        <v>7054720</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1477,24 +1512,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,48 +1530,23 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125724591</v>
+        <v>125724610</v>
       </c>
       <c r="B10" t="n">
         <v>57652</v>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450270</v>
+        <v>450597</v>
       </c>
       <c r="R10" t="n">
-        <v>7054720</v>
+        <v>7055031</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1775,7 +1775,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125724599</v>
+        <v>125724585</v>
       </c>
       <c r="B12" t="n">
         <v>57652</v>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450306</v>
+        <v>450232</v>
       </c>
       <c r="R12" t="n">
-        <v>7054865</v>
+        <v>7054602</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125724619</v>
+        <v>125724599</v>
       </c>
       <c r="B13" t="n">
         <v>57652</v>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450958</v>
+        <v>450306</v>
       </c>
       <c r="R13" t="n">
-        <v>7054933</v>
+        <v>7054865</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,7 +1979,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125724585</v>
+        <v>125724592</v>
       </c>
       <c r="B14" t="n">
         <v>57652</v>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450232</v>
+        <v>450278</v>
       </c>
       <c r="R14" t="n">
-        <v>7054602</v>
+        <v>7054719</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125724592</v>
+        <v>125724619</v>
       </c>
       <c r="B15" t="n">
         <v>57652</v>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450278</v>
+        <v>450958</v>
       </c>
       <c r="R15" t="n">
-        <v>7054719</v>
+        <v>7054933</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2864,10 +2864,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125714526</v>
+        <v>125708478</v>
       </c>
       <c r="B22" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2904,22 +2904,22 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>450368</v>
+        <v>451306</v>
       </c>
       <c r="R22" t="n">
-        <v>7054102</v>
+        <v>7055204</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minst 11 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 6 plantor inom ca 4 m2 yta.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2995,10 +2995,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125708478</v>
+        <v>125714526</v>
       </c>
       <c r="B23" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3035,22 +3035,22 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451306</v>
+        <v>450368</v>
       </c>
       <c r="R23" t="n">
-        <v>7055204</v>
+        <v>7054102</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 6 plantor inom ca 4 m2 yta.</t>
+          <t>Minst 11 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3126,62 +3126,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125709103</v>
+        <v>125717532</v>
       </c>
       <c r="B24" t="n">
-        <v>98362</v>
+        <v>78973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Slättbrännorna, Slättbrännorna, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451383</v>
+        <v>450948</v>
       </c>
       <c r="R24" t="n">
-        <v>7055475</v>
+        <v>7054739</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3208,14 +3194,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Minst 6 plantor inom ca 1 m2 yta.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3230,6 +3226,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3247,7 +3263,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125724565</v>
+        <v>125724573</v>
       </c>
       <c r="B25" t="n">
         <v>57652</v>
@@ -3282,10 +3298,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450606</v>
+        <v>450391</v>
       </c>
       <c r="R25" t="n">
-        <v>7054211</v>
+        <v>7054076</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3322,7 +3338,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3349,7 +3365,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125724593</v>
+        <v>125724572</v>
       </c>
       <c r="B26" t="n">
         <v>57652</v>
@@ -3384,10 +3400,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450274</v>
+        <v>450406</v>
       </c>
       <c r="R26" t="n">
-        <v>7054720</v>
+        <v>7054072</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3424,7 +3440,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3451,48 +3467,62 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125724564</v>
+        <v>125709103</v>
       </c>
       <c r="B27" t="n">
-        <v>57652</v>
+        <v>98364</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Slättbrännorna, Slättbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>450638</v>
+        <v>451383</v>
       </c>
       <c r="R27" t="n">
-        <v>7054244</v>
+        <v>7055475</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3526,7 +3556,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 6 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3537,64 +3567,74 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125724574</v>
+        <v>125715130</v>
       </c>
       <c r="B28" t="n">
-        <v>57652</v>
+        <v>80112</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>450390</v>
+        <v>450363</v>
       </c>
       <c r="R28" t="n">
-        <v>7054071</v>
+        <v>7054211</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3621,14 +3661,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3639,23 +3689,48 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125724608</v>
+        <v>125724565</v>
       </c>
       <c r="B29" t="n">
         <v>57652</v>
@@ -3690,10 +3765,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>450441</v>
+        <v>450606</v>
       </c>
       <c r="R29" t="n">
-        <v>7054842</v>
+        <v>7054211</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3757,7 +3832,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125724573</v>
+        <v>125712711</v>
       </c>
       <c r="B30" t="n">
         <v>57652</v>
@@ -3786,19 +3861,29 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>450391</v>
+        <v>450410</v>
       </c>
       <c r="R30" t="n">
-        <v>7054076</v>
+        <v>7054290</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3825,14 +3910,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran  nära en stor myrstack.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3843,69 +3938,89 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125715130</v>
+        <v>125724593</v>
       </c>
       <c r="B31" t="n">
-        <v>80112</v>
+        <v>57652</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>450363</v>
+        <v>450274</v>
       </c>
       <c r="R31" t="n">
-        <v>7054211</v>
+        <v>7054720</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3932,24 +4047,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3960,51 +4065,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125717532</v>
+        <v>125724564</v>
       </c>
       <c r="B32" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4012,34 +4092,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>450948</v>
+        <v>450638</v>
       </c>
       <c r="R32" t="n">
-        <v>7054739</v>
+        <v>7054244</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4069,24 +4149,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4097,48 +4167,23 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125712711</v>
+        <v>125724574</v>
       </c>
       <c r="B33" t="n">
         <v>57652</v>
@@ -4167,29 +4212,19 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450410</v>
+        <v>450390</v>
       </c>
       <c r="R33" t="n">
-        <v>7054290</v>
+        <v>7054071</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4216,24 +4251,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  nära en stor myrstack.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4244,48 +4269,23 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125724572</v>
+        <v>125724608</v>
       </c>
       <c r="B34" t="n">
         <v>57652</v>
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>450406</v>
+        <v>450441</v>
       </c>
       <c r="R34" t="n">
-        <v>7054072</v>
+        <v>7054842</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4387,45 +4387,64 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125724627</v>
+        <v>125711207</v>
       </c>
       <c r="B35" t="n">
-        <v>80076</v>
+        <v>98364</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>450528</v>
+        <v>450852</v>
       </c>
       <c r="R35" t="n">
-        <v>7054102</v>
+        <v>7054681</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4460,6 +4479,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Minst 17 plantor inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4468,80 +4492,66 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125711207</v>
+        <v>125724627</v>
       </c>
       <c r="B36" t="n">
-        <v>98362</v>
+        <v>80076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>450852</v>
+        <v>450528</v>
       </c>
       <c r="R36" t="n">
-        <v>7054681</v>
+        <v>7054102</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4576,11 +4586,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Minst 17 plantor inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4589,21 +4594,16 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5063,10 +5063,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125708223</v>
+        <v>125724631</v>
       </c>
       <c r="B41" t="n">
-        <v>78973</v>
+        <v>91254</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5074,37 +5074,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>451292</v>
+        <v>450196</v>
       </c>
       <c r="R41" t="n">
-        <v>7055142</v>
+        <v>7054664</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5131,21 +5131,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5154,48 +5144,23 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125715396</v>
+        <v>125708223</v>
       </c>
       <c r="B42" t="n">
         <v>78973</v>
@@ -5226,17 +5191,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>450394</v>
+        <v>451292</v>
       </c>
       <c r="R42" t="n">
-        <v>7054235</v>
+        <v>7055142</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5263,11 +5228,21 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5276,6 +5251,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5292,10 +5292,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125724594</v>
+        <v>125715396</v>
       </c>
       <c r="B43" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5303,37 +5303,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>450285</v>
+        <v>450394</v>
       </c>
       <c r="R43" t="n">
-        <v>7054794</v>
+        <v>7054235</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5363,11 +5363,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5382,19 +5377,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125724556</v>
+        <v>125724580</v>
       </c>
       <c r="B44" t="n">
         <v>57652</v>
@@ -5429,10 +5424,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>450878</v>
+        <v>450072</v>
       </c>
       <c r="R44" t="n">
-        <v>7054550</v>
+        <v>7054712</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5496,10 +5491,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125724631</v>
+        <v>125724594</v>
       </c>
       <c r="B45" t="n">
-        <v>91252</v>
+        <v>57652</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5507,21 +5502,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5531,10 +5526,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>450196</v>
+        <v>450285</v>
       </c>
       <c r="R45" t="n">
-        <v>7054664</v>
+        <v>7054794</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5567,6 +5562,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5593,7 +5593,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125724580</v>
+        <v>125724556</v>
       </c>
       <c r="B46" t="n">
         <v>57652</v>
@@ -5628,10 +5628,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>450072</v>
+        <v>450878</v>
       </c>
       <c r="R46" t="n">
-        <v>7054712</v>
+        <v>7054550</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5822,62 +5822,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125709295</v>
+        <v>125724630</v>
       </c>
       <c r="B48" t="n">
-        <v>98362</v>
+        <v>91254</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>451312</v>
+        <v>450577</v>
       </c>
       <c r="R48" t="n">
-        <v>7055388</v>
+        <v>7054440</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5909,11 +5895,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5922,21 +5903,16 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6441,7 +6417,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125724614</v>
+        <v>125724553</v>
       </c>
       <c r="B53" t="n">
         <v>57652</v>
@@ -6476,10 +6452,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>450762</v>
+        <v>450713</v>
       </c>
       <c r="R53" t="n">
-        <v>7055029</v>
+        <v>7054346</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6516,7 +6492,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6543,10 +6519,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125724630</v>
+        <v>125724614</v>
       </c>
       <c r="B54" t="n">
-        <v>91252</v>
+        <v>57652</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6554,21 +6530,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6578,10 +6554,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>450577</v>
+        <v>450762</v>
       </c>
       <c r="R54" t="n">
-        <v>7054440</v>
+        <v>7055029</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6614,6 +6590,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6640,48 +6621,62 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125724553</v>
+        <v>125709295</v>
       </c>
       <c r="B55" t="n">
-        <v>57652</v>
+        <v>98364</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>450713</v>
+        <v>451312</v>
       </c>
       <c r="R55" t="n">
-        <v>7054346</v>
+        <v>7055388</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6715,7 +6710,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6726,16 +6721,21 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6869,7 +6869,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125711291</v>
+        <v>125709678</v>
       </c>
       <c r="B57" t="n">
         <v>78973</v>
@@ -6904,13 +6904,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>450795</v>
+        <v>451218</v>
       </c>
       <c r="R57" t="n">
-        <v>7054803</v>
+        <v>7055148</v>
       </c>
       <c r="S57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6942,11 +6942,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flertalet granar.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6958,7 +6953,7 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -6996,7 +6991,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125709678</v>
+        <v>125711291</v>
       </c>
       <c r="B58" t="n">
         <v>78973</v>
@@ -7031,13 +7026,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451218</v>
+        <v>450795</v>
       </c>
       <c r="R58" t="n">
-        <v>7055148</v>
+        <v>7054803</v>
       </c>
       <c r="S58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7069,6 +7064,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flertalet granar.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7080,7 +7080,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
@@ -7325,7 +7325,7 @@
         <v>125709578</v>
       </c>
       <c r="B61" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7443,10 +7443,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125714547</v>
+        <v>125711118</v>
       </c>
       <c r="B62" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7454,34 +7454,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>450361</v>
+        <v>450865</v>
       </c>
       <c r="R62" t="n">
-        <v>7054101</v>
+        <v>7054734</v>
       </c>
       <c r="S62" t="n">
         <v>8</v>
@@ -7511,19 +7516,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>14:12</t>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På nedfallen död gren av sälg.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7537,27 +7537,27 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7575,10 +7575,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125711118</v>
+        <v>125714547</v>
       </c>
       <c r="B63" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7586,39 +7586,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>450865</v>
+        <v>450361</v>
       </c>
       <c r="R63" t="n">
-        <v>7054734</v>
+        <v>7054101</v>
       </c>
       <c r="S63" t="n">
         <v>8</v>
@@ -7648,14 +7643,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>På nedfallen död gren av sälg.</t>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7669,27 +7669,27 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7710,7 +7710,7 @@
         <v>125724634</v>
       </c>
       <c r="B64" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>125716316</v>
       </c>
       <c r="B65" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8290,62 +8290,58 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125708839</v>
+        <v>125715668</v>
       </c>
       <c r="B69" t="n">
-        <v>98362</v>
+        <v>57652</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>451394</v>
+        <v>450399</v>
       </c>
       <c r="R69" t="n">
-        <v>7055346</v>
+        <v>7054150</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8372,14 +8368,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 25 plantor inom ca 2 m2.</t>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8393,7 +8399,27 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8411,10 +8437,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125724544</v>
+        <v>125724596</v>
       </c>
       <c r="B70" t="n">
-        <v>91234</v>
+        <v>57652</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8422,21 +8448,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8446,10 +8472,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>450929</v>
+        <v>450286</v>
       </c>
       <c r="R70" t="n">
-        <v>7054588</v>
+        <v>7054789</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8482,6 +8508,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8508,10 +8539,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125716115</v>
+        <v>125712863</v>
       </c>
       <c r="B71" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8519,37 +8550,47 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>450545</v>
+        <v>450351</v>
       </c>
       <c r="R71" t="n">
-        <v>7054277</v>
+        <v>7054230</v>
       </c>
       <c r="S71" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8578,7 +8619,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8588,7 +8629,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran nära vägen.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8599,6 +8645,31 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8615,7 +8686,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125715668</v>
+        <v>125724576</v>
       </c>
       <c r="B72" t="n">
         <v>57652</v>
@@ -8644,26 +8715,16 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>450399</v>
+        <v>450258</v>
       </c>
       <c r="R72" t="n">
-        <v>7054150</v>
+        <v>7054372</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8693,24 +8754,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8721,51 +8772,26 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125724596</v>
+        <v>125724544</v>
       </c>
       <c r="B73" t="n">
-        <v>57652</v>
+        <v>91236</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8773,21 +8799,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8797,10 +8823,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>450286</v>
+        <v>450929</v>
       </c>
       <c r="R73" t="n">
-        <v>7054789</v>
+        <v>7054588</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8833,11 +8859,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8864,10 +8885,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125712863</v>
+        <v>125716115</v>
       </c>
       <c r="B74" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8875,47 +8896,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>450351</v>
+        <v>450545</v>
       </c>
       <c r="R74" t="n">
-        <v>7054230</v>
+        <v>7054277</v>
       </c>
       <c r="S74" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8944,7 +8955,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8954,12 +8965,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran nära vägen.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8970,31 +8976,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9011,48 +8992,62 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125724576</v>
+        <v>125708839</v>
       </c>
       <c r="B75" t="n">
-        <v>57652</v>
+        <v>98364</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>450258</v>
+        <v>451394</v>
       </c>
       <c r="R75" t="n">
-        <v>7054372</v>
+        <v>7055346</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9086,7 +9081,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 25 plantor inom ca 2 m2.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9097,26 +9092,31 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125715929</v>
+        <v>125724545</v>
       </c>
       <c r="B76" t="n">
-        <v>78973</v>
+        <v>91236</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9124,37 +9124,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>450435</v>
+        <v>450771</v>
       </c>
       <c r="R76" t="n">
-        <v>7054165</v>
+        <v>7055042</v>
       </c>
       <c r="S76" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9181,19 +9181,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>15:26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9208,22 +9198,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125724584</v>
+        <v>125715929</v>
       </c>
       <c r="B77" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9231,37 +9221,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>450230</v>
+        <v>450435</v>
       </c>
       <c r="R77" t="n">
-        <v>7054621</v>
+        <v>7054165</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9288,14 +9278,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9310,19 +9305,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125724550</v>
+        <v>125724584</v>
       </c>
       <c r="B78" t="n">
         <v>57652</v>
@@ -9357,10 +9352,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>450437</v>
+        <v>450230</v>
       </c>
       <c r="R78" t="n">
-        <v>7054480</v>
+        <v>7054621</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9424,7 +9419,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125724578</v>
+        <v>125724550</v>
       </c>
       <c r="B79" t="n">
         <v>57652</v>
@@ -9459,10 +9454,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>450228</v>
+        <v>450437</v>
       </c>
       <c r="R79" t="n">
-        <v>7054435</v>
+        <v>7054480</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9526,67 +9521,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125718167</v>
+        <v>125724578</v>
       </c>
       <c r="B80" t="n">
-        <v>98362</v>
+        <v>57652</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>451146</v>
+        <v>450228</v>
       </c>
       <c r="R80" t="n">
-        <v>7054932</v>
+        <v>7054435</v>
       </c>
       <c r="S80" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9613,24 +9589,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Minst 14 plantor inom ca 1 m2.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9641,69 +9607,83 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125724545</v>
+        <v>125718167</v>
       </c>
       <c r="B81" t="n">
-        <v>91234</v>
+        <v>98364</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>450771</v>
+        <v>451146</v>
       </c>
       <c r="R81" t="n">
-        <v>7055042</v>
+        <v>7054932</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9730,11 +9710,26 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Minst 14 plantor inom ca 1 m2.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9743,26 +9738,31 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125724569</v>
+        <v>125709469</v>
       </c>
       <c r="B82" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9770,34 +9770,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>450437</v>
+        <v>451269</v>
       </c>
       <c r="R82" t="n">
-        <v>7054064</v>
+        <v>7055329</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9832,11 +9832,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9849,19 +9844,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125724588</v>
+        <v>125724569</v>
       </c>
       <c r="B83" t="n">
         <v>57652</v>
@@ -9896,10 +9891,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>450275</v>
+        <v>450437</v>
       </c>
       <c r="R83" t="n">
-        <v>7054607</v>
+        <v>7054064</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9936,7 +9931,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9963,7 +9958,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125724568</v>
+        <v>125724588</v>
       </c>
       <c r="B84" t="n">
         <v>57652</v>
@@ -9998,10 +9993,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>450530</v>
+        <v>450275</v>
       </c>
       <c r="R84" t="n">
-        <v>7054095</v>
+        <v>7054607</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10038,7 +10033,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10065,10 +10060,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125709469</v>
+        <v>125724568</v>
       </c>
       <c r="B85" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10076,34 +10071,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>451269</v>
+        <v>450530</v>
       </c>
       <c r="R85" t="n">
-        <v>7055329</v>
+        <v>7054095</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10138,6 +10133,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10150,74 +10150,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125708960</v>
+        <v>125724605</v>
       </c>
       <c r="B86" t="n">
-        <v>98362</v>
+        <v>57652</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>451445</v>
+        <v>450357</v>
       </c>
       <c r="R86" t="n">
-        <v>7055383</v>
+        <v>7054800</v>
       </c>
       <c r="S86" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10251,7 +10237,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Minst 29 plantor inom ca 2 m2.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10262,31 +10248,26 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125710745</v>
+        <v>125715345</v>
       </c>
       <c r="B87" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10294,37 +10275,47 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>451035</v>
+        <v>450372</v>
       </c>
       <c r="R87" t="n">
-        <v>7054940</v>
+        <v>7054250</v>
       </c>
       <c r="S87" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10351,14 +10342,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack, äldre, på en död liggande gran precis öster om vägen.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10387,12 +10388,12 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10410,7 +10411,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125724605</v>
+        <v>125724587</v>
       </c>
       <c r="B88" t="n">
         <v>57652</v>
@@ -10445,10 +10446,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>450357</v>
+        <v>450279</v>
       </c>
       <c r="R88" t="n">
-        <v>7054800</v>
+        <v>7054606</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10512,7 +10513,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125715345</v>
+        <v>125715883</v>
       </c>
       <c r="B89" t="n">
         <v>57652</v>
@@ -10557,13 +10558,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>450372</v>
+        <v>450371</v>
       </c>
       <c r="R89" t="n">
-        <v>7054250</v>
+        <v>7054182</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10592,7 +10593,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10602,12 +10603,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en död liggande gran precis öster om vägen.</t>
+          <t>Ringhack, äldre, på stambasen av en något smalare gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10636,12 +10637,12 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10659,10 +10660,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125724587</v>
+        <v>125710745</v>
       </c>
       <c r="B90" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10670,37 +10671,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>450279</v>
+        <v>451035</v>
       </c>
       <c r="R90" t="n">
-        <v>7054606</v>
+        <v>7054940</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10734,7 +10735,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10745,74 +10746,103 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125715883</v>
+        <v>125708960</v>
       </c>
       <c r="B91" t="n">
-        <v>57652</v>
+        <v>98364</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>450371</v>
+        <v>451445</v>
       </c>
       <c r="R91" t="n">
-        <v>7054182</v>
+        <v>7055383</v>
       </c>
       <c r="S91" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10839,24 +10869,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en något smalare gran.</t>
+          <t>Minst 29 plantor inom ca 2 m2.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10871,26 +10891,6 @@
       <c r="AH91" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10911,7 +10911,7 @@
         <v>125724543</v>
       </c>
       <c r="B92" t="n">
-        <v>91592</v>
+        <v>91594</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11006,27 +11006,27 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125710515</v>
+        <v>125724622</v>
       </c>
       <c r="B93" t="n">
-        <v>58021</v>
+        <v>57652</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -11034,36 +11034,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>451089</v>
+        <v>450935</v>
       </c>
       <c r="R93" t="n">
-        <v>7054975</v>
+        <v>7055227</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11093,19 +11074,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>10:58</t>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11116,48 +11092,43 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125724622</v>
+        <v>125710515</v>
       </c>
       <c r="B94" t="n">
-        <v>57652</v>
+        <v>58021</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -11165,17 +11136,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>450935</v>
+        <v>451089</v>
       </c>
       <c r="R94" t="n">
-        <v>7055227</v>
+        <v>7054975</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11205,14 +11195,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11223,16 +11218,21 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11368,7 +11368,7 @@
         <v>125708590</v>
       </c>
       <c r="B96" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11496,59 +11496,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125712767</v>
+        <v>125724609</v>
       </c>
       <c r="B97" t="n">
-        <v>98362</v>
+        <v>57652</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>450391</v>
+        <v>450581</v>
       </c>
       <c r="R97" t="n">
-        <v>7054281</v>
+        <v>7055012</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11578,24 +11564,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Minst 20 plantor inom ca 2 m2 yta.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11606,28 +11582,23 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125724609</v>
+        <v>125724546</v>
       </c>
       <c r="B98" t="n">
         <v>57652</v>
@@ -11662,10 +11633,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>450581</v>
+        <v>451102</v>
       </c>
       <c r="R98" t="n">
-        <v>7055012</v>
+        <v>7054896</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11729,10 +11700,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125709922</v>
+        <v>125724566</v>
       </c>
       <c r="B99" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11740,37 +11711,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>451225</v>
+        <v>450600</v>
       </c>
       <c r="R99" t="n">
-        <v>7055093</v>
+        <v>7054142</v>
       </c>
       <c r="S99" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11804,7 +11775,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11815,31 +11786,26 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125718221</v>
+        <v>125724551</v>
       </c>
       <c r="B100" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11847,37 +11813,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>451172</v>
+        <v>450486</v>
       </c>
       <c r="R100" t="n">
-        <v>7054946</v>
+        <v>7054445</v>
       </c>
       <c r="S100" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11904,19 +11870,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>17:06</t>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11931,19 +11892,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125724566</v>
+        <v>125724621</v>
       </c>
       <c r="B101" t="n">
         <v>57652</v>
@@ -11978,10 +11939,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>450600</v>
+        <v>450933</v>
       </c>
       <c r="R101" t="n">
-        <v>7054142</v>
+        <v>7054883</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12018,7 +11979,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12045,7 +12006,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125724621</v>
+        <v>125715238</v>
       </c>
       <c r="B102" t="n">
         <v>57652</v>
@@ -12074,16 +12035,26 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>450933</v>
+        <v>450342</v>
       </c>
       <c r="R102" t="n">
-        <v>7054883</v>
+        <v>7054212</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12113,14 +12084,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran  precis öster om vägen.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12131,23 +12112,48 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125715238</v>
+        <v>125724618</v>
       </c>
       <c r="B103" t="n">
         <v>57652</v>
@@ -12176,26 +12182,16 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>450342</v>
+        <v>450905</v>
       </c>
       <c r="R103" t="n">
-        <v>7054212</v>
+        <v>7054898</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12225,24 +12221,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  precis öster om vägen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12253,48 +12239,23 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125724618</v>
+        <v>125724577</v>
       </c>
       <c r="B104" t="n">
         <v>57652</v>
@@ -12329,10 +12290,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>450905</v>
+        <v>450259</v>
       </c>
       <c r="R104" t="n">
-        <v>7054898</v>
+        <v>7054380</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12396,38 +12357,47 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125715109</v>
+        <v>125712767</v>
       </c>
       <c r="B105" t="n">
-        <v>80077</v>
+        <v>98364</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -12436,10 +12406,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>450365</v>
+        <v>450391</v>
       </c>
       <c r="R105" t="n">
-        <v>7054197</v>
+        <v>7054281</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12471,7 +12441,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12481,12 +12451,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Minst 20 plantor inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12501,26 +12471,6 @@
       <c r="AH105" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12538,10 +12488,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125724546</v>
+        <v>125709922</v>
       </c>
       <c r="B106" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12549,37 +12499,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>451102</v>
+        <v>451225</v>
       </c>
       <c r="R106" t="n">
-        <v>7054896</v>
+        <v>7055093</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12613,7 +12563,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12624,26 +12574,31 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125724551</v>
+        <v>125715109</v>
       </c>
       <c r="B107" t="n">
-        <v>57652</v>
+        <v>80077</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12651,34 +12606,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>450486</v>
+        <v>450365</v>
       </c>
       <c r="R107" t="n">
-        <v>7054445</v>
+        <v>7054197</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12708,14 +12668,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12726,26 +12696,51 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125724577</v>
+        <v>125718221</v>
       </c>
       <c r="B108" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12753,37 +12748,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>450259</v>
+        <v>451172</v>
       </c>
       <c r="R108" t="n">
-        <v>7054380</v>
+        <v>7054946</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12810,14 +12805,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12832,22 +12832,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125712294</v>
+        <v>125724549</v>
       </c>
       <c r="B109" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12855,37 +12855,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Storholmen, Storholmen, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>450461</v>
+        <v>450547</v>
       </c>
       <c r="R109" t="n">
-        <v>7054536</v>
+        <v>7054823</v>
       </c>
       <c r="S109" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12912,24 +12912,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12940,48 +12930,23 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125724552</v>
+        <v>125724586</v>
       </c>
       <c r="B110" t="n">
         <v>57652</v>
@@ -13016,10 +12981,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>450545</v>
+        <v>450292</v>
       </c>
       <c r="R110" t="n">
-        <v>7054416</v>
+        <v>7054587</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13056,7 +13021,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13083,10 +13048,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125712133</v>
+        <v>125724558</v>
       </c>
       <c r="B111" t="n">
-        <v>58131</v>
+        <v>57652</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13094,56 +13059,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103018</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>450497</v>
+        <v>450702</v>
       </c>
       <c r="R111" t="n">
-        <v>7054617</v>
+        <v>7054428</v>
       </c>
       <c r="S111" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13170,24 +13116,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>En sjungande hane i ett stråk med en del asp.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13198,28 +13134,23 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125724549</v>
+        <v>125724552</v>
       </c>
       <c r="B112" t="n">
         <v>57652</v>
@@ -13254,10 +13185,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>450547</v>
+        <v>450545</v>
       </c>
       <c r="R112" t="n">
-        <v>7054823</v>
+        <v>7054416</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13321,10 +13252,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125724586</v>
+        <v>125712294</v>
       </c>
       <c r="B113" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13332,37 +13263,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storholmen, Storholmen, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>450292</v>
+        <v>450461</v>
       </c>
       <c r="R113" t="n">
-        <v>7054587</v>
+        <v>7054536</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13389,14 +13320,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13407,26 +13348,51 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125724558</v>
+        <v>125712133</v>
       </c>
       <c r="B114" t="n">
-        <v>57652</v>
+        <v>58131</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13434,37 +13400,56 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>103018</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>450702</v>
+        <v>450497</v>
       </c>
       <c r="R114" t="n">
-        <v>7054428</v>
+        <v>7054617</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13491,14 +13476,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>En sjungande hane i ett stråk med en del asp.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13509,26 +13504,31 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125724625</v>
+        <v>125709665</v>
       </c>
       <c r="B115" t="n">
-        <v>98362</v>
+        <v>80104</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13536,37 +13536,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>451414</v>
+        <v>451229</v>
       </c>
       <c r="R115" t="n">
-        <v>7055348</v>
+        <v>7055183</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13596,6 +13596,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13610,60 +13615,65 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125709665</v>
+        <v>125712605</v>
       </c>
       <c r="B116" t="n">
-        <v>80104</v>
+        <v>78973</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>451229</v>
+        <v>450406</v>
       </c>
       <c r="R116" t="n">
-        <v>7055183</v>
+        <v>7054312</v>
       </c>
       <c r="S116" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13690,14 +13700,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13708,6 +13728,31 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
@@ -13724,10 +13769,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125712605</v>
+        <v>125724559</v>
       </c>
       <c r="B117" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13735,42 +13780,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>450406</v>
+        <v>450487</v>
       </c>
       <c r="R117" t="n">
-        <v>7054312</v>
+        <v>7054409</v>
       </c>
       <c r="S117" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13797,24 +13837,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar med apothecier.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13825,48 +13855,23 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125724559</v>
+        <v>125712655</v>
       </c>
       <c r="B118" t="n">
         <v>57652</v>
@@ -13895,19 +13900,29 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>450487</v>
+        <v>450387</v>
       </c>
       <c r="R118" t="n">
-        <v>7054409</v>
+        <v>7054295</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13934,14 +13949,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gran intill en stor myrstack.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13952,23 +13977,48 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125712655</v>
+        <v>125715638</v>
       </c>
       <c r="B119" t="n">
         <v>57652</v>
@@ -14013,13 +14063,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>450387</v>
+        <v>450416</v>
       </c>
       <c r="R119" t="n">
-        <v>7054295</v>
+        <v>7054156</v>
       </c>
       <c r="S119" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14048,7 +14098,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14058,12 +14108,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran intill en stor myrstack.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14115,7 +14165,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125715638</v>
+        <v>125724557</v>
       </c>
       <c r="B120" t="n">
         <v>57652</v>
@@ -14144,26 +14194,16 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>450416</v>
+        <v>450772</v>
       </c>
       <c r="R120" t="n">
-        <v>7054156</v>
+        <v>7054621</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14193,24 +14233,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14221,73 +14251,48 @@
       </c>
       <c r="AG120" t="b">
         <v>0</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125724557</v>
+        <v>125724625</v>
       </c>
       <c r="B121" t="n">
-        <v>57652</v>
+        <v>98364</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14297,10 +14302,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>450772</v>
+        <v>451414</v>
       </c>
       <c r="R121" t="n">
-        <v>7054621</v>
+        <v>7055348</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14333,11 +14338,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15108,10 +15108,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125724633</v>
+        <v>125724623</v>
       </c>
       <c r="B129" t="n">
-        <v>91252</v>
+        <v>57652</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15119,21 +15119,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15143,10 +15143,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>450636</v>
+        <v>451200</v>
       </c>
       <c r="R129" t="n">
-        <v>7054969</v>
+        <v>7055401</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15179,6 +15179,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15205,10 +15210,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125724623</v>
+        <v>125724633</v>
       </c>
       <c r="B130" t="n">
-        <v>57652</v>
+        <v>91254</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15216,21 +15221,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15240,10 +15245,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>451200</v>
+        <v>450636</v>
       </c>
       <c r="R130" t="n">
-        <v>7055401</v>
+        <v>7054969</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15276,11 +15281,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15307,7 +15307,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125724582</v>
+        <v>125724601</v>
       </c>
       <c r="B131" t="n">
         <v>57652</v>
@@ -15342,10 +15342,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>450120</v>
+        <v>450317</v>
       </c>
       <c r="R131" t="n">
-        <v>7054703</v>
+        <v>7054857</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15382,7 +15382,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15409,7 +15409,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125724601</v>
+        <v>125724561</v>
       </c>
       <c r="B132" t="n">
         <v>57652</v>
@@ -15444,10 +15444,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>450317</v>
+        <v>450605</v>
       </c>
       <c r="R132" t="n">
-        <v>7054857</v>
+        <v>7054337</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15511,7 +15511,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125724561</v>
+        <v>125724611</v>
       </c>
       <c r="B133" t="n">
         <v>57652</v>
@@ -15546,10 +15546,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>450605</v>
+        <v>450631</v>
       </c>
       <c r="R133" t="n">
-        <v>7054337</v>
+        <v>7054989</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15586,7 +15586,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15613,48 +15613,58 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125724611</v>
+        <v>125712965</v>
       </c>
       <c r="B134" t="n">
-        <v>57652</v>
+        <v>56844</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>450631</v>
+        <v>450279</v>
       </c>
       <c r="R134" t="n">
-        <v>7054989</v>
+        <v>7054063</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15681,14 +15691,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15699,23 +15714,28 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125724620</v>
+        <v>125724582</v>
       </c>
       <c r="B135" t="n">
         <v>57652</v>
@@ -15750,10 +15770,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>450942</v>
+        <v>450120</v>
       </c>
       <c r="R135" t="n">
-        <v>7054894</v>
+        <v>7054703</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15817,58 +15837,48 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125712965</v>
+        <v>125724620</v>
       </c>
       <c r="B136" t="n">
-        <v>56844</v>
+        <v>57652</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>450279</v>
+        <v>450942</v>
       </c>
       <c r="R136" t="n">
-        <v>7054063</v>
+        <v>7054894</v>
       </c>
       <c r="S136" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15895,19 +15905,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>13:00</t>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15918,21 +15923,16 @@
       </c>
       <c r="AG136" t="b">
         <v>0</v>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -15942,7 +15942,7 @@
         <v>125710733</v>
       </c>
       <c r="B137" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16639,10 +16639,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126056424</v>
+        <v>126056436</v>
       </c>
       <c r="B142" t="n">
-        <v>57652</v>
+        <v>91254</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16650,21 +16650,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16674,10 +16674,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>450341</v>
+        <v>450342</v>
       </c>
       <c r="R142" t="n">
-        <v>7054692</v>
+        <v>7054358</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16710,11 +16710,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16741,7 +16736,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126056423</v>
+        <v>126056424</v>
       </c>
       <c r="B143" t="n">
         <v>57652</v>
@@ -16776,10 +16771,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>450419</v>
+        <v>450341</v>
       </c>
       <c r="R143" t="n">
-        <v>7054568</v>
+        <v>7054692</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16816,7 +16811,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16843,10 +16838,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126056436</v>
+        <v>126056423</v>
       </c>
       <c r="B144" t="n">
-        <v>91252</v>
+        <v>57652</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16854,21 +16849,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16878,10 +16873,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>450342</v>
+        <v>450419</v>
       </c>
       <c r="R144" t="n">
-        <v>7054358</v>
+        <v>7054568</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16914,6 +16909,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17351,7 +17351,7 @@
         <v>126056432</v>
       </c>
       <c r="B149" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>126056434</v>
       </c>
       <c r="B150" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>126056435</v>
       </c>
       <c r="B152" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>126056433</v>
       </c>
       <c r="B155" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>126056431</v>
       </c>
       <c r="B160" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 22902-2025 artfynd.xlsx
+++ b/artfynd/A 22902-2025 artfynd.xlsx
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125711912</v>
+        <v>125714988</v>
       </c>
       <c r="B5" t="n">
         <v>57652</v>
@@ -1007,17 +1007,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450518</v>
+        <v>450413</v>
       </c>
       <c r="R5" t="n">
-        <v>7054696</v>
+        <v>7054149</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1076,6 +1076,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1093,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125724579</v>
+        <v>125724597</v>
       </c>
       <c r="B6" t="n">
         <v>57652</v>
@@ -1128,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450145</v>
+        <v>450287</v>
       </c>
       <c r="R6" t="n">
-        <v>7054502</v>
+        <v>7054787</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125714988</v>
+        <v>125724591</v>
       </c>
       <c r="B7" t="n">
         <v>57652</v>
@@ -1224,26 +1244,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>450413</v>
+        <v>450270</v>
       </c>
       <c r="R7" t="n">
-        <v>7054149</v>
+        <v>7054720</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,24 +1283,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,48 +1301,23 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125724597</v>
+        <v>125724610</v>
       </c>
       <c r="B8" t="n">
         <v>57652</v>
@@ -1377,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>450287</v>
+        <v>450597</v>
       </c>
       <c r="R8" t="n">
-        <v>7054787</v>
+        <v>7055031</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125724591</v>
+        <v>125711912</v>
       </c>
       <c r="B9" t="n">
         <v>57652</v>
@@ -1473,19 +1448,29 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>450270</v>
+        <v>450518</v>
       </c>
       <c r="R9" t="n">
-        <v>7054720</v>
+        <v>7054696</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,14 +1497,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1530,23 +1525,28 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125724610</v>
+        <v>125724579</v>
       </c>
       <c r="B10" t="n">
         <v>57652</v>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450597</v>
+        <v>450145</v>
       </c>
       <c r="R10" t="n">
-        <v>7055031</v>
+        <v>7054502</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -4387,64 +4387,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125711207</v>
+        <v>125724627</v>
       </c>
       <c r="B35" t="n">
-        <v>98364</v>
+        <v>80076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>450852</v>
+        <v>450528</v>
       </c>
       <c r="R35" t="n">
-        <v>7054681</v>
+        <v>7054102</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4479,11 +4460,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Minst 17 plantor inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4492,31 +4468,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125724627</v>
+        <v>125716595</v>
       </c>
       <c r="B36" t="n">
-        <v>80076</v>
+        <v>57652</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4524,34 +4495,44 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>450528</v>
+        <v>450481</v>
       </c>
       <c r="R36" t="n">
-        <v>7054102</v>
+        <v>7054352</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4581,11 +4562,26 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4594,23 +4590,48 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125716595</v>
+        <v>125724603</v>
       </c>
       <c r="B37" t="n">
         <v>57652</v>
@@ -4639,26 +4660,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>450481</v>
+        <v>450339</v>
       </c>
       <c r="R37" t="n">
-        <v>7054352</v>
+        <v>7054827</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4688,24 +4699,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs ett par meter på en granstam.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4716,48 +4717,23 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125724603</v>
+        <v>125724613</v>
       </c>
       <c r="B38" t="n">
         <v>57652</v>
@@ -4792,10 +4768,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450339</v>
+        <v>450714</v>
       </c>
       <c r="R38" t="n">
-        <v>7054827</v>
+        <v>7055072</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4832,7 +4808,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4859,45 +4835,64 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125724613</v>
+        <v>125711207</v>
       </c>
       <c r="B39" t="n">
-        <v>57652</v>
+        <v>98364</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>450714</v>
+        <v>450852</v>
       </c>
       <c r="R39" t="n">
-        <v>7055072</v>
+        <v>7054681</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4934,7 +4929,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Minst 17 plantor inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4945,16 +4940,21 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -10908,32 +10908,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125724543</v>
+        <v>125724622</v>
       </c>
       <c r="B92" t="n">
-        <v>91594</v>
+        <v>57652</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10943,10 +10943,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>450931</v>
+        <v>450935</v>
       </c>
       <c r="R92" t="n">
-        <v>7054587</v>
+        <v>7055227</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10981,13 +10981,17 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -11006,27 +11010,27 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125724622</v>
+        <v>125710515</v>
       </c>
       <c r="B93" t="n">
-        <v>57652</v>
+        <v>58021</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -11034,17 +11038,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>450935</v>
+        <v>451089</v>
       </c>
       <c r="R93" t="n">
-        <v>7055227</v>
+        <v>7054975</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11074,14 +11097,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11092,48 +11120,53 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125710515</v>
+        <v>125714169</v>
       </c>
       <c r="B94" t="n">
-        <v>58021</v>
+        <v>57812</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -11141,14 +11174,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -11158,17 +11186,17 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>451089</v>
+        <v>450226</v>
       </c>
       <c r="R94" t="n">
-        <v>7054975</v>
+        <v>7054095</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11197,7 +11225,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11207,7 +11235,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11221,7 +11249,7 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11239,62 +11267,62 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125714169</v>
+        <v>125708590</v>
       </c>
       <c r="B95" t="n">
-        <v>57812</v>
+        <v>98364</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>450226</v>
+        <v>451359</v>
       </c>
       <c r="R95" t="n">
-        <v>7054095</v>
+        <v>7055225</v>
       </c>
       <c r="S95" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11323,7 +11351,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11333,7 +11361,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 3 m2.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11347,7 +11380,7 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11365,62 +11398,48 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125708590</v>
+        <v>125724543</v>
       </c>
       <c r="B96" t="n">
-        <v>98364</v>
+        <v>91594</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221952</v>
+        <v>2062</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>451359</v>
+        <v>450931</v>
       </c>
       <c r="R96" t="n">
-        <v>7055225</v>
+        <v>7054587</v>
       </c>
       <c r="S96" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11447,49 +11466,30 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 3 m2.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -13525,48 +13525,48 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125709665</v>
+        <v>125724559</v>
       </c>
       <c r="B115" t="n">
-        <v>80104</v>
+        <v>57652</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>451229</v>
+        <v>450487</v>
       </c>
       <c r="R115" t="n">
-        <v>7055183</v>
+        <v>7054409</v>
       </c>
       <c r="S115" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13615,22 +13615,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125712605</v>
+        <v>125712655</v>
       </c>
       <c r="B116" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13638,27 +13638,32 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -13667,13 +13672,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>450406</v>
+        <v>450387</v>
       </c>
       <c r="R116" t="n">
-        <v>7054312</v>
+        <v>7054295</v>
       </c>
       <c r="S116" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13702,7 +13707,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13712,12 +13717,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar med apothecier.</t>
+          <t>Ringhack, äldre, på en gran intill en stor myrstack.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13746,12 +13751,12 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -13769,7 +13774,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125724559</v>
+        <v>125715638</v>
       </c>
       <c r="B117" t="n">
         <v>57652</v>
@@ -13798,16 +13803,26 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>450487</v>
+        <v>450416</v>
       </c>
       <c r="R117" t="n">
-        <v>7054409</v>
+        <v>7054156</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13837,14 +13852,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13855,23 +13880,48 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125712655</v>
+        <v>125724557</v>
       </c>
       <c r="B118" t="n">
         <v>57652</v>
@@ -13900,29 +13950,19 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>450387</v>
+        <v>450772</v>
       </c>
       <c r="R118" t="n">
-        <v>7054295</v>
+        <v>7054621</v>
       </c>
       <c r="S118" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13949,24 +13989,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran intill en stor myrstack.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13977,99 +14007,64 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125715638</v>
+        <v>125709665</v>
       </c>
       <c r="B119" t="n">
-        <v>57652</v>
+        <v>80104</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>450416</v>
+        <v>451229</v>
       </c>
       <c r="R119" t="n">
-        <v>7054156</v>
+        <v>7055183</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14096,24 +14091,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14124,31 +14109,6 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
@@ -14165,10 +14125,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125724557</v>
+        <v>125712605</v>
       </c>
       <c r="B120" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14176,37 +14136,42 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>450772</v>
+        <v>450406</v>
       </c>
       <c r="R120" t="n">
-        <v>7054621</v>
+        <v>7054312</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14233,14 +14198,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14251,16 +14226,41 @@
       </c>
       <c r="AG120" t="b">
         <v>0</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>

--- a/artfynd/A 22902-2025 artfynd.xlsx
+++ b/artfynd/A 22902-2025 artfynd.xlsx
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125724599</v>
+        <v>125711059</v>
       </c>
       <c r="B11" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,34 +1659,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450306</v>
+        <v>450886</v>
       </c>
       <c r="R11" t="n">
-        <v>7054865</v>
+        <v>7054749</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,23 +1734,48 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125724619</v>
+        <v>125724599</v>
       </c>
       <c r="B12" t="n">
         <v>57652</v>
@@ -1785,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450958</v>
+        <v>450306</v>
       </c>
       <c r="R12" t="n">
-        <v>7054933</v>
+        <v>7054865</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,7 +1877,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125724585</v>
+        <v>125724619</v>
       </c>
       <c r="B13" t="n">
         <v>57652</v>
@@ -1887,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450232</v>
+        <v>450958</v>
       </c>
       <c r="R13" t="n">
-        <v>7054602</v>
+        <v>7054933</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,7 +1979,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125724592</v>
+        <v>125724585</v>
       </c>
       <c r="B14" t="n">
         <v>57652</v>
@@ -1989,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450278</v>
+        <v>450232</v>
       </c>
       <c r="R14" t="n">
-        <v>7054719</v>
+        <v>7054602</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2054,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125712265</v>
+        <v>125724592</v>
       </c>
       <c r="B15" t="n">
-        <v>57812</v>
+        <v>57652</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2067,51 +2092,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storholmen, Storholmen, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450456</v>
+        <v>450278</v>
       </c>
       <c r="R15" t="n">
-        <v>7054618</v>
+        <v>7054719</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2138,24 +2149,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Locklätet av en talltita observerades i lämplig häckmiljö.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2166,31 +2167,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125711059</v>
+        <v>125712265</v>
       </c>
       <c r="B16" t="n">
-        <v>78973</v>
+        <v>57812</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,37 +2194,51 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Storholmen, Storholmen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>450886</v>
+        <v>450456</v>
       </c>
       <c r="R16" t="n">
-        <v>7054749</v>
+        <v>7054618</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2255,14 +2265,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Locklätet av en talltita observerades i lämplig häckmiljö.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2277,26 +2297,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -5695,43 +5695,47 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125711989</v>
+        <v>125709295</v>
       </c>
       <c r="B47" t="n">
-        <v>57652</v>
+        <v>98366</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5740,13 +5744,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>450536</v>
+        <v>451312</v>
       </c>
       <c r="R47" t="n">
-        <v>7054699</v>
+        <v>7055388</v>
       </c>
       <c r="S47" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5773,24 +5777,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5805,26 +5799,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5842,10 +5816,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125724615</v>
+        <v>125724630</v>
       </c>
       <c r="B48" t="n">
-        <v>57652</v>
+        <v>91256</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5853,21 +5827,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5877,10 +5851,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>450856</v>
+        <v>450577</v>
       </c>
       <c r="R48" t="n">
-        <v>7054955</v>
+        <v>7054440</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5913,11 +5887,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5944,10 +5913,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125724555</v>
+        <v>125710364</v>
       </c>
       <c r="B49" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5955,37 +5924,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>450816</v>
+        <v>451107</v>
       </c>
       <c r="R49" t="n">
-        <v>7054432</v>
+        <v>7055032</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6019,7 +5988,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Gott om långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6030,23 +5999,48 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125712552</v>
+        <v>125711989</v>
       </c>
       <c r="B50" t="n">
         <v>57652</v>
@@ -6087,17 +6081,17 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>450417</v>
+        <v>450536</v>
       </c>
       <c r="R50" t="n">
-        <v>7054319</v>
+        <v>7054699</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6126,7 +6120,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6136,7 +6130,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -6193,7 +6187,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125724553</v>
+        <v>125724615</v>
       </c>
       <c r="B51" t="n">
         <v>57652</v>
@@ -6228,10 +6222,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>450713</v>
+        <v>450856</v>
       </c>
       <c r="R51" t="n">
-        <v>7054346</v>
+        <v>7054955</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6295,7 +6289,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125724614</v>
+        <v>125724555</v>
       </c>
       <c r="B52" t="n">
         <v>57652</v>
@@ -6330,10 +6324,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>450762</v>
+        <v>450816</v>
       </c>
       <c r="R52" t="n">
-        <v>7055029</v>
+        <v>7054432</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6370,7 +6364,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6397,59 +6391,55 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125709295</v>
+        <v>125712552</v>
       </c>
       <c r="B53" t="n">
-        <v>98366</v>
+        <v>57652</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>451312</v>
+        <v>450417</v>
       </c>
       <c r="R53" t="n">
-        <v>7055388</v>
+        <v>7054319</v>
       </c>
       <c r="S53" t="n">
         <v>8</v>
@@ -6479,14 +6469,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6501,6 +6501,26 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6518,10 +6538,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125724630</v>
+        <v>125724553</v>
       </c>
       <c r="B54" t="n">
-        <v>91256</v>
+        <v>57652</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6529,21 +6549,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6553,10 +6573,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>450577</v>
+        <v>450713</v>
       </c>
       <c r="R54" t="n">
-        <v>7054440</v>
+        <v>7054346</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6589,6 +6609,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6615,10 +6640,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125710364</v>
+        <v>125724614</v>
       </c>
       <c r="B55" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6626,37 +6651,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>451107</v>
+        <v>450762</v>
       </c>
       <c r="R55" t="n">
-        <v>7055032</v>
+        <v>7055029</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6690,7 +6715,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Gott om långväxta bålar på en gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6701,89 +6726,78 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125724606</v>
+        <v>125709578</v>
       </c>
       <c r="B56" t="n">
-        <v>57652</v>
+        <v>98366</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>450436</v>
+        <v>451288</v>
       </c>
       <c r="R56" t="n">
-        <v>7054836</v>
+        <v>7055288</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6817,7 +6831,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 10 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6828,26 +6842,31 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125724554</v>
+        <v>125709678</v>
       </c>
       <c r="B57" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6855,37 +6874,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>450796</v>
+        <v>451218</v>
       </c>
       <c r="R57" t="n">
-        <v>7054404</v>
+        <v>7055148</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6917,11 +6936,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6930,78 +6944,89 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125709578</v>
+        <v>125724606</v>
       </c>
       <c r="B58" t="n">
-        <v>98366</v>
+        <v>57652</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451288</v>
+        <v>450436</v>
       </c>
       <c r="R58" t="n">
-        <v>7055288</v>
+        <v>7054836</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7035,7 +7060,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 10 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7046,31 +7071,26 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125709678</v>
+        <v>125724554</v>
       </c>
       <c r="B59" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7078,37 +7098,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451218</v>
+        <v>450796</v>
       </c>
       <c r="R59" t="n">
-        <v>7055148</v>
+        <v>7054404</v>
       </c>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7140,6 +7160,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7148,41 +7173,16 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7930,10 +7930,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125714185</v>
+        <v>125717826</v>
       </c>
       <c r="B66" t="n">
-        <v>57070</v>
+        <v>78973</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7941,56 +7941,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>102961</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>450224</v>
+        <v>451046</v>
       </c>
       <c r="R66" t="n">
-        <v>7054100</v>
+        <v>7054820</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8019,7 +8000,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8029,7 +8010,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Långväxta bålar i god mängd.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8040,6 +8026,31 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8056,10 +8067,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125717826</v>
+        <v>125724626</v>
       </c>
       <c r="B67" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8067,37 +8078,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>451046</v>
+        <v>450584</v>
       </c>
       <c r="R67" t="n">
-        <v>7054820</v>
+        <v>7054245</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8124,26 +8135,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Långväxta bålar i god mängd.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8152,51 +8148,26 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125724626</v>
+        <v>125714185</v>
       </c>
       <c r="B68" t="n">
-        <v>80076</v>
+        <v>57070</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8204,37 +8175,56 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>102961</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>450584</v>
+        <v>450224</v>
       </c>
       <c r="R68" t="n">
-        <v>7054245</v>
+        <v>7054100</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8261,9 +8251,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8278,12 +8278,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -10162,48 +10162,62 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125710745</v>
+        <v>125708960</v>
       </c>
       <c r="B86" t="n">
-        <v>78973</v>
+        <v>98366</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>451035</v>
+        <v>451445</v>
       </c>
       <c r="R86" t="n">
-        <v>7054940</v>
+        <v>7055383</v>
       </c>
       <c r="S86" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10237,7 +10251,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 29 plantor inom ca 2 m2.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10252,26 +10266,6 @@
       <c r="AH86" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10289,10 +10283,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125715345</v>
+        <v>125710745</v>
       </c>
       <c r="B87" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10300,47 +10294,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>450372</v>
+        <v>451035</v>
       </c>
       <c r="R87" t="n">
-        <v>7054250</v>
+        <v>7054940</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10367,24 +10351,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en död liggande gran precis öster om vägen.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10413,12 +10387,12 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10436,7 +10410,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125724605</v>
+        <v>125715345</v>
       </c>
       <c r="B88" t="n">
         <v>57652</v>
@@ -10465,16 +10439,26 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>450357</v>
+        <v>450372</v>
       </c>
       <c r="R88" t="n">
-        <v>7054800</v>
+        <v>7054250</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10504,14 +10488,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en död liggande gran precis öster om vägen.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10522,23 +10516,48 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125724587</v>
+        <v>125724605</v>
       </c>
       <c r="B89" t="n">
         <v>57652</v>
@@ -10573,10 +10592,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>450279</v>
+        <v>450357</v>
       </c>
       <c r="R89" t="n">
-        <v>7054606</v>
+        <v>7054800</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10640,7 +10659,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125715883</v>
+        <v>125724587</v>
       </c>
       <c r="B90" t="n">
         <v>57652</v>
@@ -10669,29 +10688,19 @@
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>450371</v>
+        <v>450279</v>
       </c>
       <c r="R90" t="n">
-        <v>7054182</v>
+        <v>7054606</v>
       </c>
       <c r="S90" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10718,24 +10727,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en något smalare gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10746,103 +10745,74 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125708960</v>
+        <v>125715883</v>
       </c>
       <c r="B91" t="n">
-        <v>98366</v>
+        <v>57652</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>451445</v>
+        <v>450371</v>
       </c>
       <c r="R91" t="n">
-        <v>7055383</v>
+        <v>7054182</v>
       </c>
       <c r="S91" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10869,14 +10839,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Minst 29 plantor inom ca 2 m2.</t>
+          <t>Ringhack, äldre, på stambasen av en något smalare gran.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10891,6 +10871,26 @@
       <c r="AH91" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10908,32 +10908,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125724622</v>
+        <v>125724543</v>
       </c>
       <c r="B92" t="n">
-        <v>57652</v>
+        <v>91596</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10943,10 +10943,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>450935</v>
+        <v>450931</v>
       </c>
       <c r="R92" t="n">
-        <v>7055227</v>
+        <v>7054587</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10981,17 +10981,13 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -11010,32 +11006,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125714169</v>
+        <v>125710515</v>
       </c>
       <c r="B93" t="n">
-        <v>57812</v>
+        <v>58021</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -11043,9 +11039,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -11055,17 +11056,17 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>450226</v>
+        <v>451089</v>
       </c>
       <c r="R93" t="n">
-        <v>7054095</v>
+        <v>7054975</v>
       </c>
       <c r="S93" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11094,7 +11095,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11104,7 +11105,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11118,7 +11119,7 @@
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11136,48 +11137,62 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125724543</v>
+        <v>125708590</v>
       </c>
       <c r="B94" t="n">
-        <v>91596</v>
+        <v>98366</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2062</v>
+        <v>221952</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>450931</v>
+        <v>451359</v>
       </c>
       <c r="R94" t="n">
-        <v>7054587</v>
+        <v>7055225</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11204,57 +11219,76 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 3 m2.</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125710515</v>
+        <v>125724622</v>
       </c>
       <c r="B95" t="n">
-        <v>58021</v>
+        <v>57652</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -11262,36 +11296,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>451089</v>
+        <v>450935</v>
       </c>
       <c r="R95" t="n">
-        <v>7054975</v>
+        <v>7055227</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11321,19 +11336,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>10:58</t>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11344,83 +11354,78 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125708590</v>
+        <v>125714169</v>
       </c>
       <c r="B96" t="n">
-        <v>98366</v>
+        <v>57812</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>451359</v>
+        <v>450226</v>
       </c>
       <c r="R96" t="n">
-        <v>7055225</v>
+        <v>7054095</v>
       </c>
       <c r="S96" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11449,7 +11454,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11459,12 +11464,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 3 m2.</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -13525,48 +13525,53 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125709665</v>
+        <v>125712605</v>
       </c>
       <c r="B115" t="n">
-        <v>80104</v>
+        <v>78973</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>451229</v>
+        <v>450406</v>
       </c>
       <c r="R115" t="n">
-        <v>7055183</v>
+        <v>7054312</v>
       </c>
       <c r="S115" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13593,14 +13598,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13611,6 +13626,31 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
@@ -14023,32 +14063,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125724557</v>
+        <v>125724625</v>
       </c>
       <c r="B119" t="n">
-        <v>57652</v>
+        <v>98366</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14058,10 +14098,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>450772</v>
+        <v>451414</v>
       </c>
       <c r="R119" t="n">
-        <v>7054621</v>
+        <v>7055348</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14094,11 +14134,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14125,10 +14160,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125724625</v>
+        <v>125709665</v>
       </c>
       <c r="B120" t="n">
-        <v>98366</v>
+        <v>80104</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14136,37 +14171,37 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>451414</v>
+        <v>451229</v>
       </c>
       <c r="R120" t="n">
-        <v>7055348</v>
+        <v>7055183</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14196,6 +14231,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14210,22 +14250,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125712605</v>
+        <v>125724557</v>
       </c>
       <c r="B121" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14233,42 +14273,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>450406</v>
+        <v>450772</v>
       </c>
       <c r="R121" t="n">
-        <v>7054312</v>
+        <v>7054621</v>
       </c>
       <c r="S121" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14295,24 +14330,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar med apothecier.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14323,41 +14348,16 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -14461,10 +14461,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125715696</v>
+        <v>125724612</v>
       </c>
       <c r="B123" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14472,37 +14472,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>450391</v>
+        <v>450636</v>
       </c>
       <c r="R123" t="n">
-        <v>7054170</v>
+        <v>7054958</v>
       </c>
       <c r="S123" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14529,19 +14529,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>15:13</t>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14552,48 +14547,23 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125724612</v>
+        <v>125724602</v>
       </c>
       <c r="B124" t="n">
         <v>57652</v>
@@ -14628,10 +14598,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>450636</v>
+        <v>450307</v>
       </c>
       <c r="R124" t="n">
-        <v>7054958</v>
+        <v>7054854</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14668,7 +14638,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14695,7 +14665,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125724602</v>
+        <v>125724548</v>
       </c>
       <c r="B125" t="n">
         <v>57652</v>
@@ -14730,10 +14700,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>450307</v>
+        <v>450973</v>
       </c>
       <c r="R125" t="n">
-        <v>7054854</v>
+        <v>7054710</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14770,7 +14740,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14797,7 +14767,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125724548</v>
+        <v>125724571</v>
       </c>
       <c r="B126" t="n">
         <v>57652</v>
@@ -14832,10 +14802,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>450973</v>
+        <v>450408</v>
       </c>
       <c r="R126" t="n">
-        <v>7054710</v>
+        <v>7054064</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14899,7 +14869,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125724571</v>
+        <v>125724616</v>
       </c>
       <c r="B127" t="n">
         <v>57652</v>
@@ -14934,10 +14904,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>450408</v>
+        <v>450858</v>
       </c>
       <c r="R127" t="n">
-        <v>7054064</v>
+        <v>7054949</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14974,7 +14944,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15001,7 +14971,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125724616</v>
+        <v>125724617</v>
       </c>
       <c r="B128" t="n">
         <v>57652</v>
@@ -15036,10 +15006,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>450858</v>
+        <v>450851</v>
       </c>
       <c r="R128" t="n">
-        <v>7054949</v>
+        <v>7054937</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15076,7 +15046,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15103,7 +15073,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125724617</v>
+        <v>125724623</v>
       </c>
       <c r="B129" t="n">
         <v>57652</v>
@@ -15138,10 +15108,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>450851</v>
+        <v>451200</v>
       </c>
       <c r="R129" t="n">
-        <v>7054937</v>
+        <v>7055401</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15205,10 +15175,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125724623</v>
+        <v>125715696</v>
       </c>
       <c r="B130" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15216,37 +15186,37 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>451200</v>
+        <v>450391</v>
       </c>
       <c r="R130" t="n">
-        <v>7055401</v>
+        <v>7054170</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15273,14 +15243,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15291,16 +15266,41 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>

--- a/artfynd/A 22902-2025 artfynd.xlsx
+++ b/artfynd/A 22902-2025 artfynd.xlsx
@@ -1648,7 +1648,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125724585</v>
+        <v>125724592</v>
       </c>
       <c r="B11" t="n">
         <v>57656</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450232</v>
+        <v>450278</v>
       </c>
       <c r="R11" t="n">
-        <v>7054602</v>
+        <v>7054719</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,7 +1750,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125724599</v>
+        <v>125724619</v>
       </c>
       <c r="B12" t="n">
         <v>57656</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450306</v>
+        <v>450958</v>
       </c>
       <c r="R12" t="n">
-        <v>7054865</v>
+        <v>7054933</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125724592</v>
+        <v>125711059</v>
       </c>
       <c r="B13" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,34 +1863,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450278</v>
+        <v>450886</v>
       </c>
       <c r="R13" t="n">
-        <v>7054719</v>
+        <v>7054749</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1938,23 +1938,48 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125724619</v>
+        <v>125724585</v>
       </c>
       <c r="B14" t="n">
         <v>57656</v>
@@ -1989,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450958</v>
+        <v>450232</v>
       </c>
       <c r="R14" t="n">
-        <v>7054933</v>
+        <v>7054602</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125711059</v>
+        <v>125724599</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2067,34 +2092,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450886</v>
+        <v>450306</v>
       </c>
       <c r="R15" t="n">
-        <v>7054749</v>
+        <v>7054865</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,7 +2156,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2142,41 +2167,16 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -4387,64 +4387,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125711207</v>
+        <v>125724627</v>
       </c>
       <c r="B35" t="n">
-        <v>98370</v>
+        <v>80080</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>450852</v>
+        <v>450528</v>
       </c>
       <c r="R35" t="n">
-        <v>7054681</v>
+        <v>7054102</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4479,11 +4460,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Minst 17 plantor inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4492,66 +4468,80 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125724627</v>
+        <v>125711207</v>
       </c>
       <c r="B36" t="n">
-        <v>80080</v>
+        <v>98370</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>450528</v>
+        <v>450852</v>
       </c>
       <c r="R36" t="n">
-        <v>7054102</v>
+        <v>7054681</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4586,6 +4576,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Minst 17 plantor inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4594,16 +4589,21 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -6742,10 +6742,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125709678</v>
+        <v>125724606</v>
       </c>
       <c r="B56" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6753,37 +6753,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451218</v>
+        <v>450436</v>
       </c>
       <c r="R56" t="n">
-        <v>7055148</v>
+        <v>7054836</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6815,6 +6815,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6823,51 +6828,26 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125710504</v>
+        <v>125724554</v>
       </c>
       <c r="B57" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6875,37 +6855,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451089</v>
+        <v>450796</v>
       </c>
       <c r="R57" t="n">
-        <v>7054989</v>
+        <v>7054404</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6939,7 +6919,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6950,48 +6930,23 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125711291</v>
+        <v>125709678</v>
       </c>
       <c r="B58" t="n">
         <v>78977</v>
@@ -7026,13 +6981,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>450795</v>
+        <v>451218</v>
       </c>
       <c r="R58" t="n">
-        <v>7054803</v>
+        <v>7055148</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7064,11 +7019,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flertalet granar.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7080,7 +7030,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
@@ -7118,10 +7068,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125724606</v>
+        <v>125710504</v>
       </c>
       <c r="B59" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7129,37 +7079,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>450436</v>
+        <v>451089</v>
       </c>
       <c r="R59" t="n">
-        <v>7054836</v>
+        <v>7054989</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7193,7 +7143,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7204,26 +7154,51 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125724554</v>
+        <v>125711291</v>
       </c>
       <c r="B60" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7231,37 +7206,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>450796</v>
+        <v>450795</v>
       </c>
       <c r="R60" t="n">
-        <v>7054404</v>
+        <v>7054803</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7295,7 +7270,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7306,16 +7281,41 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7443,10 +7443,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125714547</v>
+        <v>125711118</v>
       </c>
       <c r="B62" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7454,34 +7454,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>450361</v>
+        <v>450865</v>
       </c>
       <c r="R62" t="n">
-        <v>7054101</v>
+        <v>7054734</v>
       </c>
       <c r="S62" t="n">
         <v>8</v>
@@ -7511,19 +7516,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>14:12</t>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På nedfallen död gren av sälg.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7537,27 +7537,27 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7575,45 +7575,59 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125724634</v>
+        <v>125716316</v>
       </c>
       <c r="B63" t="n">
-        <v>91260</v>
+        <v>98370</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>451148</v>
+        <v>450483</v>
       </c>
       <c r="R63" t="n">
-        <v>7055327</v>
+        <v>7054352</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7643,11 +7657,21 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7656,26 +7680,31 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125711118</v>
+        <v>125714547</v>
       </c>
       <c r="B64" t="n">
-        <v>80081</v>
+        <v>78977</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7683,39 +7712,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>450865</v>
+        <v>450361</v>
       </c>
       <c r="R64" t="n">
-        <v>7054734</v>
+        <v>7054101</v>
       </c>
       <c r="S64" t="n">
         <v>8</v>
@@ -7745,14 +7769,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På nedfallen död gren av sälg.</t>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7766,27 +7795,27 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7804,59 +7833,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125716316</v>
+        <v>125724634</v>
       </c>
       <c r="B65" t="n">
-        <v>98370</v>
+        <v>91260</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>450483</v>
+        <v>451148</v>
       </c>
       <c r="R65" t="n">
-        <v>7054352</v>
+        <v>7055327</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7886,21 +7901,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7909,31 +7914,26 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125724626</v>
+        <v>125717826</v>
       </c>
       <c r="B66" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7941,37 +7941,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>450584</v>
+        <v>451046</v>
       </c>
       <c r="R66" t="n">
-        <v>7054245</v>
+        <v>7054820</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7998,11 +7998,26 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Långväxta bålar i god mängd.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8011,26 +8026,51 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125717826</v>
+        <v>125724626</v>
       </c>
       <c r="B67" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8038,37 +8078,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>451046</v>
+        <v>450584</v>
       </c>
       <c r="R67" t="n">
-        <v>7054820</v>
+        <v>7054245</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8095,26 +8135,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Långväxta bålar i god mängd.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8123,41 +8148,16 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -9113,10 +9113,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125715929</v>
+        <v>125724584</v>
       </c>
       <c r="B76" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9124,37 +9124,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>450435</v>
+        <v>450230</v>
       </c>
       <c r="R76" t="n">
-        <v>7054165</v>
+        <v>7054621</v>
       </c>
       <c r="S76" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9181,19 +9181,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>15:26</t>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9208,19 +9203,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125724584</v>
+        <v>125724550</v>
       </c>
       <c r="B77" t="n">
         <v>57656</v>
@@ -9255,10 +9250,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>450230</v>
+        <v>450437</v>
       </c>
       <c r="R77" t="n">
-        <v>7054621</v>
+        <v>7054480</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9322,7 +9317,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125724550</v>
+        <v>125724578</v>
       </c>
       <c r="B78" t="n">
         <v>57656</v>
@@ -9357,10 +9352,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>450437</v>
+        <v>450228</v>
       </c>
       <c r="R78" t="n">
-        <v>7054480</v>
+        <v>7054435</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9424,48 +9419,67 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125724578</v>
+        <v>125718167</v>
       </c>
       <c r="B79" t="n">
-        <v>57656</v>
+        <v>98370</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>450228</v>
+        <v>451146</v>
       </c>
       <c r="R79" t="n">
-        <v>7054435</v>
+        <v>7054932</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9492,14 +9506,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Minst 14 plantor inom ca 1 m2.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9510,16 +9534,21 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9623,67 +9652,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125718167</v>
+        <v>125715929</v>
       </c>
       <c r="B81" t="n">
-        <v>98370</v>
+        <v>78977</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>451146</v>
+        <v>450435</v>
       </c>
       <c r="R81" t="n">
-        <v>7054932</v>
+        <v>7054165</v>
       </c>
       <c r="S81" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9712,7 +9722,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9722,12 +9732,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:03</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Minst 14 plantor inom ca 1 m2.</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9738,11 +9743,6 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">

--- a/artfynd/A 22902-2025 artfynd.xlsx
+++ b/artfynd/A 22902-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125724579</v>
+        <v>125711912</v>
       </c>
       <c r="B2" t="n">
         <v>57656</v>
@@ -704,19 +704,29 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450145</v>
+        <v>450518</v>
       </c>
       <c r="R2" t="n">
-        <v>7054502</v>
+        <v>7054696</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,14 +753,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,23 +781,28 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125724597</v>
+        <v>125724579</v>
       </c>
       <c r="B3" t="n">
         <v>57656</v>
@@ -812,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450287</v>
+        <v>450145</v>
       </c>
       <c r="R3" t="n">
-        <v>7054787</v>
+        <v>7054502</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125724591</v>
+        <v>125714988</v>
       </c>
       <c r="B4" t="n">
         <v>57656</v>
@@ -908,16 +933,26 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450270</v>
+        <v>450413</v>
       </c>
       <c r="R4" t="n">
-        <v>7054720</v>
+        <v>7054149</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,14 +982,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -965,23 +1010,48 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125724610</v>
+        <v>125724597</v>
       </c>
       <c r="B5" t="n">
         <v>57656</v>
@@ -1016,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450597</v>
+        <v>450287</v>
       </c>
       <c r="R5" t="n">
-        <v>7055031</v>
+        <v>7054787</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125708514</v>
+        <v>125724591</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,37 +1164,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451330</v>
+        <v>450270</v>
       </c>
       <c r="R6" t="n">
-        <v>7055192</v>
+        <v>7054720</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1154,6 +1224,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1168,22 +1243,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125724629</v>
+        <v>125724610</v>
       </c>
       <c r="B7" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>450502</v>
+        <v>450597</v>
       </c>
       <c r="R7" t="n">
-        <v>7054507</v>
+        <v>7055031</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,6 +1326,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,7 +1357,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125724628</v>
+        <v>125724629</v>
       </c>
       <c r="B8" t="n">
         <v>91260</v>
@@ -1312,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451229</v>
+        <v>450502</v>
       </c>
       <c r="R8" t="n">
-        <v>7055028</v>
+        <v>7054507</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125711912</v>
+        <v>125724628</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>91260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,47 +1465,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>450518</v>
+        <v>451229</v>
       </c>
       <c r="R9" t="n">
-        <v>7054696</v>
+        <v>7055028</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1452,26 +1522,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1480,31 +1535,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125714988</v>
+        <v>125708514</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1512,47 +1562,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450413</v>
+        <v>451330</v>
       </c>
       <c r="R10" t="n">
-        <v>7054149</v>
+        <v>7055192</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1579,26 +1619,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1607,31 +1632,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1648,7 +1648,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125724592</v>
+        <v>125724585</v>
       </c>
       <c r="B11" t="n">
         <v>57656</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450278</v>
+        <v>450232</v>
       </c>
       <c r="R11" t="n">
-        <v>7054719</v>
+        <v>7054602</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,7 +1750,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125724619</v>
+        <v>125724599</v>
       </c>
       <c r="B12" t="n">
         <v>57656</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450958</v>
+        <v>450306</v>
       </c>
       <c r="R12" t="n">
-        <v>7054933</v>
+        <v>7054865</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125711059</v>
+        <v>125724592</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,34 +1863,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450886</v>
+        <v>450278</v>
       </c>
       <c r="R13" t="n">
-        <v>7054749</v>
+        <v>7054719</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1938,48 +1938,23 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125724585</v>
+        <v>125724619</v>
       </c>
       <c r="B14" t="n">
         <v>57656</v>
@@ -2014,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450232</v>
+        <v>450958</v>
       </c>
       <c r="R14" t="n">
-        <v>7054602</v>
+        <v>7054933</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2081,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125724599</v>
+        <v>125711059</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,34 +2067,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450306</v>
+        <v>450886</v>
       </c>
       <c r="R15" t="n">
-        <v>7054865</v>
+        <v>7054749</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2131,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2167,16 +2142,41 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2411,48 +2411,62 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125724598</v>
+        <v>125708478</v>
       </c>
       <c r="B18" t="n">
-        <v>57656</v>
+        <v>98373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>450292</v>
+        <v>451306</v>
       </c>
       <c r="R18" t="n">
-        <v>7054851</v>
+        <v>7055204</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2479,14 +2493,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 6 plantor inom ca 4 m2 yta.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,61 +2521,80 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125724560</v>
+        <v>125714526</v>
       </c>
       <c r="B19" t="n">
-        <v>57656</v>
+        <v>98373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>450673</v>
+        <v>450368</v>
       </c>
       <c r="R19" t="n">
-        <v>7054359</v>
+        <v>7054102</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2581,14 +2624,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 11 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,23 +2652,28 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125724547</v>
+        <v>125718101</v>
       </c>
       <c r="B20" t="n">
         <v>57656</v>
@@ -2644,19 +2702,29 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451006</v>
+        <v>451151</v>
       </c>
       <c r="R20" t="n">
-        <v>7054764</v>
+        <v>7054937</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2683,14 +2751,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre och rejäla, längs ca 2 meter på en granstam.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2701,23 +2779,48 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125718101</v>
+        <v>125724598</v>
       </c>
       <c r="B21" t="n">
         <v>57656</v>
@@ -2746,29 +2849,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451151</v>
+        <v>450292</v>
       </c>
       <c r="R21" t="n">
-        <v>7054937</v>
+        <v>7054851</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2795,24 +2888,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, äldre och rejäla, längs ca 2 meter på en granstam.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2823,103 +2906,64 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125708478</v>
+        <v>125724560</v>
       </c>
       <c r="B22" t="n">
-        <v>98370</v>
+        <v>57656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451306</v>
+        <v>450673</v>
       </c>
       <c r="R22" t="n">
-        <v>7055204</v>
+        <v>7054359</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2946,24 +2990,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minst 6 plantor inom ca 4 m2 yta.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2974,80 +3008,61 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125714526</v>
+        <v>125724547</v>
       </c>
       <c r="B23" t="n">
-        <v>98370</v>
+        <v>57656</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>450368</v>
+        <v>451006</v>
       </c>
       <c r="R23" t="n">
-        <v>7054102</v>
+        <v>7054764</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3077,24 +3092,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 11 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3105,74 +3110,64 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125715130</v>
+        <v>125717532</v>
       </c>
       <c r="B24" t="n">
-        <v>80116</v>
+        <v>78977</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>450363</v>
+        <v>450948</v>
       </c>
       <c r="R24" t="n">
-        <v>7054211</v>
+        <v>7054739</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3201,7 +3196,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3211,12 +3206,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3230,27 +3225,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3268,43 +3263,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125712711</v>
+        <v>125715130</v>
       </c>
       <c r="B25" t="n">
-        <v>57656</v>
+        <v>80116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3313,10 +3303,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450410</v>
+        <v>450363</v>
       </c>
       <c r="R25" t="n">
-        <v>7054290</v>
+        <v>7054211</v>
       </c>
       <c r="S25" t="n">
         <v>11</v>
@@ -3348,7 +3338,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3358,12 +3348,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  nära en stor myrstack.</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3382,22 +3372,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3415,10 +3405,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125717532</v>
+        <v>125724565</v>
       </c>
       <c r="B26" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3426,34 +3416,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450948</v>
+        <v>450606</v>
       </c>
       <c r="R26" t="n">
-        <v>7054739</v>
+        <v>7054211</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3483,24 +3473,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:43</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3511,48 +3491,23 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125724565</v>
+        <v>125712711</v>
       </c>
       <c r="B27" t="n">
         <v>57656</v>
@@ -3581,19 +3536,29 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>450606</v>
+        <v>450410</v>
       </c>
       <c r="R27" t="n">
-        <v>7054211</v>
+        <v>7054290</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3620,14 +3585,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran  nära en stor myrstack.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3638,16 +3613,41 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4269,7 +4269,7 @@
         <v>125709103</v>
       </c>
       <c r="B34" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4387,45 +4387,64 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125724627</v>
+        <v>125711207</v>
       </c>
       <c r="B35" t="n">
-        <v>80080</v>
+        <v>98373</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>450528</v>
+        <v>450852</v>
       </c>
       <c r="R35" t="n">
-        <v>7054102</v>
+        <v>7054681</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4460,6 +4479,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Minst 17 plantor inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4468,80 +4492,66 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125711207</v>
+        <v>125724627</v>
       </c>
       <c r="B36" t="n">
-        <v>98370</v>
+        <v>80080</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>450852</v>
+        <v>450528</v>
       </c>
       <c r="R36" t="n">
-        <v>7054681</v>
+        <v>7054102</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4576,11 +4586,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Minst 17 plantor inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4589,21 +4594,16 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4961,10 +4961,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125708223</v>
+        <v>125724631</v>
       </c>
       <c r="B40" t="n">
-        <v>78977</v>
+        <v>91260</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4972,37 +4972,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>451292</v>
+        <v>450196</v>
       </c>
       <c r="R40" t="n">
-        <v>7055142</v>
+        <v>7054664</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5029,21 +5029,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5052,48 +5042,23 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125715396</v>
+        <v>125708223</v>
       </c>
       <c r="B41" t="n">
         <v>78977</v>
@@ -5124,17 +5089,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>450394</v>
+        <v>451292</v>
       </c>
       <c r="R41" t="n">
-        <v>7054235</v>
+        <v>7055142</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5161,11 +5126,21 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5174,6 +5149,31 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5190,7 +5190,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125710168</v>
+        <v>125715396</v>
       </c>
       <c r="B42" t="n">
         <v>78977</v>
@@ -5221,17 +5221,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>451182</v>
+        <v>450394</v>
       </c>
       <c r="R42" t="n">
-        <v>7055004</v>
+        <v>7054235</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5261,11 +5261,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5292,10 +5287,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125724631</v>
+        <v>125710168</v>
       </c>
       <c r="B43" t="n">
-        <v>91260</v>
+        <v>78977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5303,37 +5298,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>450196</v>
+        <v>451182</v>
       </c>
       <c r="R43" t="n">
-        <v>7054664</v>
+        <v>7055004</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5363,6 +5358,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5377,12 +5377,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5695,10 +5695,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125711989</v>
+        <v>125724630</v>
       </c>
       <c r="B47" t="n">
-        <v>57656</v>
+        <v>91260</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5706,47 +5706,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>450536</v>
+        <v>450577</v>
       </c>
       <c r="R47" t="n">
-        <v>7054699</v>
+        <v>7054440</v>
       </c>
       <c r="S47" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5773,26 +5763,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5801,51 +5776,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125712552</v>
+        <v>125710364</v>
       </c>
       <c r="B48" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5853,47 +5803,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>450417</v>
+        <v>451107</v>
       </c>
       <c r="R48" t="n">
-        <v>7054319</v>
+        <v>7055032</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5920,24 +5860,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Gott om långväxta bålar på en gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5951,7 +5881,7 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -5966,12 +5896,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5989,10 +5919,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125710364</v>
+        <v>125711989</v>
       </c>
       <c r="B49" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6000,37 +5930,47 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>451107</v>
+        <v>450536</v>
       </c>
       <c r="R49" t="n">
-        <v>7055032</v>
+        <v>7054699</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6057,14 +5997,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Gott om långväxta bålar på en gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6078,7 +6028,7 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -6093,12 +6043,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6116,10 +6066,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125724630</v>
+        <v>125724615</v>
       </c>
       <c r="B50" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6127,21 +6077,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6151,10 +6101,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>450577</v>
+        <v>450856</v>
       </c>
       <c r="R50" t="n">
-        <v>7054440</v>
+        <v>7054955</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6187,6 +6137,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6213,7 +6168,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125724615</v>
+        <v>125724555</v>
       </c>
       <c r="B51" t="n">
         <v>57656</v>
@@ -6248,10 +6203,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>450856</v>
+        <v>450816</v>
       </c>
       <c r="R51" t="n">
-        <v>7054955</v>
+        <v>7054432</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6315,7 +6270,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125724555</v>
+        <v>125712552</v>
       </c>
       <c r="B52" t="n">
         <v>57656</v>
@@ -6344,19 +6299,29 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>450816</v>
+        <v>450417</v>
       </c>
       <c r="R52" t="n">
-        <v>7054432</v>
+        <v>7054319</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6383,14 +6348,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6401,16 +6376,41 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6624,7 +6624,7 @@
         <v>125709295</v>
       </c>
       <c r="B55" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6742,10 +6742,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125724606</v>
+        <v>125709678</v>
       </c>
       <c r="B56" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6753,37 +6753,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>450436</v>
+        <v>451218</v>
       </c>
       <c r="R56" t="n">
-        <v>7054836</v>
+        <v>7055148</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6815,11 +6815,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6828,26 +6823,51 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125724554</v>
+        <v>125710504</v>
       </c>
       <c r="B57" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6855,37 +6875,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>450796</v>
+        <v>451089</v>
       </c>
       <c r="R57" t="n">
-        <v>7054404</v>
+        <v>7054989</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6919,7 +6939,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6930,23 +6950,48 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125709678</v>
+        <v>125711291</v>
       </c>
       <c r="B58" t="n">
         <v>78977</v>
@@ -6981,13 +7026,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451218</v>
+        <v>450795</v>
       </c>
       <c r="R58" t="n">
-        <v>7055148</v>
+        <v>7054803</v>
       </c>
       <c r="S58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7019,6 +7064,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flertalet granar.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7030,7 +7080,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
@@ -7068,10 +7118,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125710504</v>
+        <v>125724606</v>
       </c>
       <c r="B59" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7079,37 +7129,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451089</v>
+        <v>450436</v>
       </c>
       <c r="R59" t="n">
-        <v>7054989</v>
+        <v>7054836</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7143,7 +7193,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7154,51 +7204,26 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125711291</v>
+        <v>125724554</v>
       </c>
       <c r="B60" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7206,37 +7231,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>450795</v>
+        <v>450796</v>
       </c>
       <c r="R60" t="n">
-        <v>7054803</v>
+        <v>7054404</v>
       </c>
       <c r="S60" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7270,7 +7295,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7281,41 +7306,16 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7325,7 +7325,7 @@
         <v>125709578</v>
       </c>
       <c r="B61" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7575,59 +7575,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125716316</v>
+        <v>125724634</v>
       </c>
       <c r="B63" t="n">
-        <v>98370</v>
+        <v>91260</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>450483</v>
+        <v>451148</v>
       </c>
       <c r="R63" t="n">
-        <v>7054352</v>
+        <v>7055327</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7657,21 +7643,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7680,21 +7656,16 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7833,45 +7804,59 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125724634</v>
+        <v>125716316</v>
       </c>
       <c r="B65" t="n">
-        <v>91260</v>
+        <v>98373</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>451148</v>
+        <v>450483</v>
       </c>
       <c r="R65" t="n">
-        <v>7055327</v>
+        <v>7054352</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7901,11 +7886,21 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7914,26 +7909,31 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125717826</v>
+        <v>125724626</v>
       </c>
       <c r="B66" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7941,37 +7941,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>451046</v>
+        <v>450584</v>
       </c>
       <c r="R66" t="n">
-        <v>7054820</v>
+        <v>7054245</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7998,26 +7998,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Långväxta bålar i god mängd.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8026,51 +8011,26 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125724626</v>
+        <v>125717826</v>
       </c>
       <c r="B67" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8078,37 +8038,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>450584</v>
+        <v>451046</v>
       </c>
       <c r="R67" t="n">
-        <v>7054245</v>
+        <v>7054820</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8135,11 +8095,26 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Långväxta bålar i god mängd.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8148,16 +8123,41 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8290,10 +8290,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125724596</v>
+        <v>125716115</v>
       </c>
       <c r="B69" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8301,37 +8301,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>450286</v>
+        <v>450545</v>
       </c>
       <c r="R69" t="n">
-        <v>7054789</v>
+        <v>7054277</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8358,14 +8358,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8380,19 +8385,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125712863</v>
+        <v>125715668</v>
       </c>
       <c r="B70" t="n">
         <v>57656</v>
@@ -8437,13 +8442,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>450351</v>
+        <v>450399</v>
       </c>
       <c r="R70" t="n">
-        <v>7054230</v>
+        <v>7054150</v>
       </c>
       <c r="S70" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8472,7 +8477,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8482,12 +8487,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran nära vägen.</t>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8539,7 +8544,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125724576</v>
+        <v>125724596</v>
       </c>
       <c r="B71" t="n">
         <v>57656</v>
@@ -8574,10 +8579,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>450258</v>
+        <v>450286</v>
       </c>
       <c r="R71" t="n">
-        <v>7054372</v>
+        <v>7054789</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8614,7 +8619,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8641,7 +8646,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125715668</v>
+        <v>125712863</v>
       </c>
       <c r="B72" t="n">
         <v>57656</v>
@@ -8686,13 +8691,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>450399</v>
+        <v>450351</v>
       </c>
       <c r="R72" t="n">
-        <v>7054150</v>
+        <v>7054230</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8721,7 +8726,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8731,12 +8736,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
+          <t>Ringhack, äldre, på en gran nära vägen.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8788,62 +8793,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125708839</v>
+        <v>125724576</v>
       </c>
       <c r="B73" t="n">
-        <v>98370</v>
+        <v>57656</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>451394</v>
+        <v>450258</v>
       </c>
       <c r="R73" t="n">
-        <v>7055346</v>
+        <v>7054372</v>
       </c>
       <c r="S73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8877,7 +8868,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Minst 25 plantor inom ca 2 m2.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8888,69 +8879,78 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125724544</v>
+        <v>125708839</v>
       </c>
       <c r="B74" t="n">
-        <v>91242</v>
+        <v>98373</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>450929</v>
+        <v>451394</v>
       </c>
       <c r="R74" t="n">
-        <v>7054588</v>
+        <v>7055346</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8982,6 +8982,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor inom ca 2 m2.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8990,26 +8995,31 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125716115</v>
+        <v>125724544</v>
       </c>
       <c r="B75" t="n">
-        <v>78977</v>
+        <v>91242</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9017,37 +9027,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>450545</v>
+        <v>450929</v>
       </c>
       <c r="R75" t="n">
-        <v>7054277</v>
+        <v>7054588</v>
       </c>
       <c r="S75" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9074,19 +9084,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9101,22 +9101,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125724584</v>
+        <v>125724545</v>
       </c>
       <c r="B76" t="n">
-        <v>57656</v>
+        <v>91242</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9124,21 +9124,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9148,10 +9148,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>450230</v>
+        <v>450771</v>
       </c>
       <c r="R76" t="n">
-        <v>7054621</v>
+        <v>7055042</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9184,11 +9184,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9215,10 +9210,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125724550</v>
+        <v>125715929</v>
       </c>
       <c r="B77" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9226,37 +9221,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>450437</v>
+        <v>450435</v>
       </c>
       <c r="R77" t="n">
-        <v>7054480</v>
+        <v>7054165</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9283,14 +9278,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9305,19 +9305,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125724578</v>
+        <v>125724584</v>
       </c>
       <c r="B78" t="n">
         <v>57656</v>
@@ -9352,10 +9352,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>450228</v>
+        <v>450230</v>
       </c>
       <c r="R78" t="n">
-        <v>7054435</v>
+        <v>7054621</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9419,67 +9419,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125718167</v>
+        <v>125724550</v>
       </c>
       <c r="B79" t="n">
-        <v>98370</v>
+        <v>57656</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>451146</v>
+        <v>450437</v>
       </c>
       <c r="R79" t="n">
-        <v>7054932</v>
+        <v>7054480</v>
       </c>
       <c r="S79" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9506,24 +9487,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Minst 14 plantor inom ca 1 m2.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9534,31 +9505,26 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125724545</v>
+        <v>125724578</v>
       </c>
       <c r="B80" t="n">
-        <v>91242</v>
+        <v>57656</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9566,21 +9532,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9590,10 +9556,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>450771</v>
+        <v>450228</v>
       </c>
       <c r="R80" t="n">
-        <v>7055042</v>
+        <v>7054435</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9626,6 +9592,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9652,48 +9623,67 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125715929</v>
+        <v>125718167</v>
       </c>
       <c r="B81" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>450435</v>
+        <v>451146</v>
       </c>
       <c r="R81" t="n">
-        <v>7054165</v>
+        <v>7054932</v>
       </c>
       <c r="S81" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9722,7 +9712,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9732,7 +9722,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Minst 14 plantor inom ca 1 m2.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9743,6 +9738,11 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9759,10 +9759,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125724568</v>
+        <v>125709469</v>
       </c>
       <c r="B82" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9770,34 +9770,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>450530</v>
+        <v>451269</v>
       </c>
       <c r="R82" t="n">
-        <v>7054095</v>
+        <v>7055329</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9832,11 +9832,6 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9849,22 +9844,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125709469</v>
+        <v>125724569</v>
       </c>
       <c r="B83" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9872,34 +9867,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>451269</v>
+        <v>450437</v>
       </c>
       <c r="R83" t="n">
-        <v>7055329</v>
+        <v>7054064</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9934,6 +9929,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9946,19 +9946,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125724569</v>
+        <v>125724588</v>
       </c>
       <c r="B84" t="n">
         <v>57656</v>
@@ -9993,10 +9993,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>450437</v>
+        <v>450275</v>
       </c>
       <c r="R84" t="n">
-        <v>7054064</v>
+        <v>7054607</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10060,7 +10060,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125724588</v>
+        <v>125724568</v>
       </c>
       <c r="B85" t="n">
         <v>57656</v>
@@ -10095,10 +10095,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>450275</v>
+        <v>450530</v>
       </c>
       <c r="R85" t="n">
-        <v>7054607</v>
+        <v>7054095</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10289,48 +10289,62 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125724605</v>
+        <v>125708960</v>
       </c>
       <c r="B87" t="n">
-        <v>57656</v>
+        <v>98373</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>450357</v>
+        <v>451445</v>
       </c>
       <c r="R87" t="n">
-        <v>7054800</v>
+        <v>7055383</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10364,7 +10378,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Minst 29 plantor inom ca 2 m2.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10375,23 +10389,28 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125724587</v>
+        <v>125724605</v>
       </c>
       <c r="B88" t="n">
         <v>57656</v>
@@ -10426,10 +10445,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>450279</v>
+        <v>450357</v>
       </c>
       <c r="R88" t="n">
-        <v>7054606</v>
+        <v>7054800</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10640,7 +10659,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125715883</v>
+        <v>125724587</v>
       </c>
       <c r="B90" t="n">
         <v>57656</v>
@@ -10669,29 +10688,19 @@
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>450371</v>
+        <v>450279</v>
       </c>
       <c r="R90" t="n">
-        <v>7054182</v>
+        <v>7054606</v>
       </c>
       <c r="S90" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10718,24 +10727,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en något smalare gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10746,103 +10745,74 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125708960</v>
+        <v>125715883</v>
       </c>
       <c r="B91" t="n">
-        <v>98370</v>
+        <v>57656</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>451445</v>
+        <v>450371</v>
       </c>
       <c r="R91" t="n">
-        <v>7055383</v>
+        <v>7054182</v>
       </c>
       <c r="S91" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10869,14 +10839,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Minst 29 plantor inom ca 2 m2.</t>
+          <t>Ringhack, äldre, på stambasen av en något smalare gran.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10891,6 +10871,26 @@
       <c r="AH91" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11006,27 +11006,27 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125724622</v>
+        <v>125710515</v>
       </c>
       <c r="B93" t="n">
-        <v>57656</v>
+        <v>58025</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -11034,17 +11034,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>450935</v>
+        <v>451089</v>
       </c>
       <c r="R93" t="n">
-        <v>7055227</v>
+        <v>7054975</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11074,14 +11093,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11092,48 +11116,53 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125710515</v>
+        <v>125714169</v>
       </c>
       <c r="B94" t="n">
-        <v>58025</v>
+        <v>57816</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -11141,14 +11170,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -11158,17 +11182,17 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>451089</v>
+        <v>450226</v>
       </c>
       <c r="R94" t="n">
-        <v>7054975</v>
+        <v>7054095</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11197,7 +11221,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11207,7 +11231,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11221,7 +11245,7 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11239,10 +11263,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125714169</v>
+        <v>125724622</v>
       </c>
       <c r="B95" t="n">
-        <v>57816</v>
+        <v>57656</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11250,51 +11274,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>450226</v>
+        <v>450935</v>
       </c>
       <c r="R95" t="n">
-        <v>7054095</v>
+        <v>7055227</v>
       </c>
       <c r="S95" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11321,19 +11331,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>13:35</t>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11344,21 +11349,16 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -11368,7 +11368,7 @@
         <v>125708590</v>
       </c>
       <c r="B96" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11496,38 +11496,47 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125715109</v>
+        <v>125712767</v>
       </c>
       <c r="B97" t="n">
-        <v>80081</v>
+        <v>98373</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -11536,10 +11545,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>450365</v>
+        <v>450391</v>
       </c>
       <c r="R97" t="n">
-        <v>7054197</v>
+        <v>7054281</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11571,7 +11580,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11581,12 +11590,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Minst 20 plantor inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11601,26 +11610,6 @@
       <c r="AH97" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11638,10 +11627,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125709922</v>
+        <v>125724609</v>
       </c>
       <c r="B98" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11649,37 +11638,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>451225</v>
+        <v>450581</v>
       </c>
       <c r="R98" t="n">
-        <v>7055093</v>
+        <v>7055012</v>
       </c>
       <c r="S98" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11713,7 +11702,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11724,31 +11713,26 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125718221</v>
+        <v>125724546</v>
       </c>
       <c r="B99" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11756,37 +11740,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>451172</v>
+        <v>451102</v>
       </c>
       <c r="R99" t="n">
-        <v>7054946</v>
+        <v>7054896</v>
       </c>
       <c r="S99" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11813,19 +11797,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>17:06</t>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11840,19 +11819,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125724609</v>
+        <v>125724566</v>
       </c>
       <c r="B100" t="n">
         <v>57656</v>
@@ -11887,10 +11866,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>450581</v>
+        <v>450600</v>
       </c>
       <c r="R100" t="n">
-        <v>7055012</v>
+        <v>7054142</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11954,7 +11933,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125724546</v>
+        <v>125724551</v>
       </c>
       <c r="B101" t="n">
         <v>57656</v>
@@ -11989,10 +11968,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>451102</v>
+        <v>450486</v>
       </c>
       <c r="R101" t="n">
-        <v>7054896</v>
+        <v>7054445</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12056,7 +12035,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125724566</v>
+        <v>125724621</v>
       </c>
       <c r="B102" t="n">
         <v>57656</v>
@@ -12091,10 +12070,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>450600</v>
+        <v>450933</v>
       </c>
       <c r="R102" t="n">
-        <v>7054142</v>
+        <v>7054883</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12131,7 +12110,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12158,7 +12137,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125724551</v>
+        <v>125715238</v>
       </c>
       <c r="B103" t="n">
         <v>57656</v>
@@ -12187,16 +12166,26 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>450486</v>
+        <v>450342</v>
       </c>
       <c r="R103" t="n">
-        <v>7054445</v>
+        <v>7054212</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12226,14 +12215,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran  precis öster om vägen.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12244,23 +12243,48 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125724621</v>
+        <v>125724618</v>
       </c>
       <c r="B104" t="n">
         <v>57656</v>
@@ -12295,10 +12319,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>450933</v>
+        <v>450905</v>
       </c>
       <c r="R104" t="n">
-        <v>7054883</v>
+        <v>7054898</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12335,7 +12359,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12362,7 +12386,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125724618</v>
+        <v>125724577</v>
       </c>
       <c r="B105" t="n">
         <v>57656</v>
@@ -12397,10 +12421,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>450905</v>
+        <v>450259</v>
       </c>
       <c r="R105" t="n">
-        <v>7054898</v>
+        <v>7054380</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12464,10 +12488,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125724577</v>
+        <v>125715109</v>
       </c>
       <c r="B106" t="n">
-        <v>57656</v>
+        <v>80081</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12475,34 +12499,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>450259</v>
+        <v>450365</v>
       </c>
       <c r="R106" t="n">
-        <v>7054380</v>
+        <v>7054197</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12532,14 +12561,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12550,26 +12589,51 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125715238</v>
+        <v>125709922</v>
       </c>
       <c r="B107" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12577,47 +12641,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>450342</v>
+        <v>451225</v>
       </c>
       <c r="R107" t="n">
-        <v>7054212</v>
+        <v>7055093</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12644,24 +12698,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran  precis öster om vägen.</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12676,26 +12720,6 @@
       <c r="AH107" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12713,62 +12737,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125712767</v>
+        <v>125718221</v>
       </c>
       <c r="B108" t="n">
-        <v>98370</v>
+        <v>78977</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>450391</v>
+        <v>451172</v>
       </c>
       <c r="R108" t="n">
-        <v>7054281</v>
+        <v>7054946</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12797,7 +12807,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12807,12 +12817,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:47</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Minst 20 plantor inom ca 2 m2 yta.</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12823,11 +12828,6 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -12981,10 +12981,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125712133</v>
+        <v>125724549</v>
       </c>
       <c r="B110" t="n">
-        <v>58135</v>
+        <v>57656</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12992,56 +12992,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103018</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>450497</v>
+        <v>450547</v>
       </c>
       <c r="R110" t="n">
-        <v>7054617</v>
+        <v>7054823</v>
       </c>
       <c r="S110" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13068,24 +13049,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>En sjungande hane i ett stråk med en del asp.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13096,28 +13067,23 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125724549</v>
+        <v>125724586</v>
       </c>
       <c r="B111" t="n">
         <v>57656</v>
@@ -13152,10 +13118,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>450547</v>
+        <v>450292</v>
       </c>
       <c r="R111" t="n">
-        <v>7054823</v>
+        <v>7054587</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13192,7 +13158,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13219,7 +13185,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125724586</v>
+        <v>125724558</v>
       </c>
       <c r="B112" t="n">
         <v>57656</v>
@@ -13254,10 +13220,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>450292</v>
+        <v>450702</v>
       </c>
       <c r="R112" t="n">
-        <v>7054587</v>
+        <v>7054428</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13294,7 +13260,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13321,7 +13287,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125724558</v>
+        <v>125724552</v>
       </c>
       <c r="B113" t="n">
         <v>57656</v>
@@ -13356,10 +13322,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>450702</v>
+        <v>450545</v>
       </c>
       <c r="R113" t="n">
-        <v>7054428</v>
+        <v>7054416</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13423,10 +13389,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125724552</v>
+        <v>125712133</v>
       </c>
       <c r="B114" t="n">
-        <v>57656</v>
+        <v>58135</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13434,37 +13400,56 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>103018</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>450545</v>
+        <v>450497</v>
       </c>
       <c r="R114" t="n">
-        <v>7054416</v>
+        <v>7054617</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13491,14 +13476,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>En sjungande hane i ett stråk med en del asp.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13509,64 +13504,74 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125709665</v>
+        <v>125712605</v>
       </c>
       <c r="B115" t="n">
-        <v>80108</v>
+        <v>78977</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>451229</v>
+        <v>450406</v>
       </c>
       <c r="R115" t="n">
-        <v>7055183</v>
+        <v>7054312</v>
       </c>
       <c r="S115" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13593,14 +13598,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13611,6 +13626,31 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
@@ -13627,10 +13667,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125724625</v>
+        <v>125709665</v>
       </c>
       <c r="B116" t="n">
-        <v>98370</v>
+        <v>80108</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13638,37 +13678,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>451414</v>
+        <v>451229</v>
       </c>
       <c r="R116" t="n">
-        <v>7055348</v>
+        <v>7055183</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13698,6 +13738,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13712,22 +13757,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125712605</v>
+        <v>125724559</v>
       </c>
       <c r="B117" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13735,42 +13780,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>450406</v>
+        <v>450487</v>
       </c>
       <c r="R117" t="n">
-        <v>7054312</v>
+        <v>7054409</v>
       </c>
       <c r="S117" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13797,24 +13837,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar med apothecier.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13825,48 +13855,23 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125724559</v>
+        <v>125712655</v>
       </c>
       <c r="B118" t="n">
         <v>57656</v>
@@ -13895,19 +13900,29 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>450487</v>
+        <v>450387</v>
       </c>
       <c r="R118" t="n">
-        <v>7054409</v>
+        <v>7054295</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13934,14 +13949,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gran intill en stor myrstack.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13952,16 +13977,41 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -14217,58 +14267,48 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125712655</v>
+        <v>125724625</v>
       </c>
       <c r="B121" t="n">
-        <v>57656</v>
+        <v>98373</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>450387</v>
+        <v>451414</v>
       </c>
       <c r="R121" t="n">
-        <v>7054295</v>
+        <v>7055348</v>
       </c>
       <c r="S121" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14295,26 +14335,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran intill en stor myrstack.</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -14323,51 +14348,26 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125724633</v>
+        <v>125724571</v>
       </c>
       <c r="B122" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14375,21 +14375,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14399,10 +14399,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>450636</v>
+        <v>450408</v>
       </c>
       <c r="R122" t="n">
-        <v>7054969</v>
+        <v>7054064</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14435,6 +14435,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14461,10 +14466,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125715696</v>
+        <v>125724616</v>
       </c>
       <c r="B123" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14472,37 +14477,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>450391</v>
+        <v>450858</v>
       </c>
       <c r="R123" t="n">
-        <v>7054170</v>
+        <v>7054949</v>
       </c>
       <c r="S123" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14529,19 +14534,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>15:13</t>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14552,48 +14552,23 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125724571</v>
+        <v>125724612</v>
       </c>
       <c r="B124" t="n">
         <v>57656</v>
@@ -14628,10 +14603,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>450408</v>
+        <v>450636</v>
       </c>
       <c r="R124" t="n">
-        <v>7054064</v>
+        <v>7054958</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14695,7 +14670,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125724616</v>
+        <v>125724602</v>
       </c>
       <c r="B125" t="n">
         <v>57656</v>
@@ -14730,10 +14705,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>450858</v>
+        <v>450307</v>
       </c>
       <c r="R125" t="n">
-        <v>7054949</v>
+        <v>7054854</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14797,7 +14772,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125724612</v>
+        <v>125724548</v>
       </c>
       <c r="B126" t="n">
         <v>57656</v>
@@ -14832,10 +14807,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>450636</v>
+        <v>450973</v>
       </c>
       <c r="R126" t="n">
-        <v>7054958</v>
+        <v>7054710</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14899,7 +14874,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125724602</v>
+        <v>125724617</v>
       </c>
       <c r="B127" t="n">
         <v>57656</v>
@@ -14934,10 +14909,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>450307</v>
+        <v>450851</v>
       </c>
       <c r="R127" t="n">
-        <v>7054854</v>
+        <v>7054937</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14974,7 +14949,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15001,7 +14976,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125724548</v>
+        <v>125724623</v>
       </c>
       <c r="B128" t="n">
         <v>57656</v>
@@ -15036,10 +15011,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>450973</v>
+        <v>451200</v>
       </c>
       <c r="R128" t="n">
-        <v>7054710</v>
+        <v>7055401</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15103,10 +15078,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125724617</v>
+        <v>125724633</v>
       </c>
       <c r="B129" t="n">
-        <v>57656</v>
+        <v>91260</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15114,21 +15089,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15138,10 +15113,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>450851</v>
+        <v>450636</v>
       </c>
       <c r="R129" t="n">
-        <v>7054937</v>
+        <v>7054969</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15174,11 +15149,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15205,10 +15175,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125724623</v>
+        <v>125715696</v>
       </c>
       <c r="B130" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15216,37 +15186,37 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>451200</v>
+        <v>450391</v>
       </c>
       <c r="R130" t="n">
-        <v>7055401</v>
+        <v>7054170</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15273,14 +15243,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15291,69 +15266,89 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125710733</v>
+        <v>125724601</v>
       </c>
       <c r="B131" t="n">
-        <v>98370</v>
+        <v>57656</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>451046</v>
+        <v>450317</v>
       </c>
       <c r="R131" t="n">
-        <v>7054942</v>
+        <v>7054857</v>
       </c>
       <c r="S131" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15387,7 +15382,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15398,79 +15393,64 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125712965</v>
+        <v>125724561</v>
       </c>
       <c r="B132" t="n">
-        <v>56848</v>
+        <v>57656</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>450279</v>
+        <v>450605</v>
       </c>
       <c r="R132" t="n">
-        <v>7054063</v>
+        <v>7054337</v>
       </c>
       <c r="S132" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15497,19 +15477,14 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>13:00</t>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15520,28 +15495,23 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125724601</v>
+        <v>125724611</v>
       </c>
       <c r="B133" t="n">
         <v>57656</v>
@@ -15576,10 +15546,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>450317</v>
+        <v>450631</v>
       </c>
       <c r="R133" t="n">
-        <v>7054857</v>
+        <v>7054989</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15616,7 +15586,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15643,7 +15613,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125724561</v>
+        <v>125724582</v>
       </c>
       <c r="B134" t="n">
         <v>57656</v>
@@ -15678,10 +15648,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>450605</v>
+        <v>450120</v>
       </c>
       <c r="R134" t="n">
-        <v>7054337</v>
+        <v>7054703</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15718,7 +15688,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15745,7 +15715,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125724611</v>
+        <v>125724620</v>
       </c>
       <c r="B135" t="n">
         <v>57656</v>
@@ -15780,10 +15750,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>450631</v>
+        <v>450942</v>
       </c>
       <c r="R135" t="n">
-        <v>7054989</v>
+        <v>7054894</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15847,48 +15817,58 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125724582</v>
+        <v>125712965</v>
       </c>
       <c r="B136" t="n">
-        <v>57656</v>
+        <v>56848</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>450120</v>
+        <v>450279</v>
       </c>
       <c r="R136" t="n">
-        <v>7054703</v>
+        <v>7054063</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15915,14 +15895,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15933,64 +15918,74 @@
       </c>
       <c r="AG136" t="b">
         <v>0</v>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125724620</v>
+        <v>125710733</v>
       </c>
       <c r="B137" t="n">
-        <v>57656</v>
+        <v>98373</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>450942</v>
+        <v>451046</v>
       </c>
       <c r="R137" t="n">
-        <v>7054894</v>
+        <v>7054942</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16024,7 +16019,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Minst 30 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16035,16 +16030,21 @@
       </c>
       <c r="AG137" t="b">
         <v>0</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -16639,10 +16639,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126056424</v>
+        <v>126056436</v>
       </c>
       <c r="B142" t="n">
-        <v>57656</v>
+        <v>91260</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16650,21 +16650,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16674,10 +16674,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>450341</v>
+        <v>450342</v>
       </c>
       <c r="R142" t="n">
-        <v>7054692</v>
+        <v>7054358</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16710,11 +16710,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16741,7 +16736,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126056423</v>
+        <v>126056424</v>
       </c>
       <c r="B143" t="n">
         <v>57656</v>
@@ -16776,10 +16771,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>450419</v>
+        <v>450341</v>
       </c>
       <c r="R143" t="n">
-        <v>7054568</v>
+        <v>7054692</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16816,7 +16811,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16843,10 +16838,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126056436</v>
+        <v>126056423</v>
       </c>
       <c r="B144" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16854,21 +16849,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16878,10 +16873,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>450342</v>
+        <v>450419</v>
       </c>
       <c r="R144" t="n">
-        <v>7054358</v>
+        <v>7054568</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16914,6 +16909,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD144" t="b">

--- a/artfynd/A 22902-2025 artfynd.xlsx
+++ b/artfynd/A 22902-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125711912</v>
+        <v>125724629</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>91260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,47 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storloken, Storloken, Jmt</t>
+          <t>Enarsvedjan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450518</v>
+        <v>450502</v>
       </c>
       <c r="R2" t="n">
-        <v>7054696</v>
+        <v>7054507</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,26 +743,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -781,31 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125724579</v>
+        <v>125724628</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>91260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450145</v>
+        <v>451229</v>
       </c>
       <c r="R3" t="n">
-        <v>7054502</v>
+        <v>7055028</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125714988</v>
+        <v>125708514</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,47 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Simamyren, Simamyren, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450413</v>
+        <v>451330</v>
       </c>
       <c r="R4" t="n">
-        <v>7054149</v>
+        <v>7055192</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,26 +937,11 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1010,31 +950,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1051,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125724597</v>
+        <v>125711912</v>
       </c>
       <c r="B5" t="n">
         <v>57656</v>
@@ -1080,19 +995,29 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Storloken, Storloken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450287</v>
+        <v>450518</v>
       </c>
       <c r="R5" t="n">
-        <v>7054787</v>
+        <v>7054696</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,14 +1044,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,23 +1072,28 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125724591</v>
+        <v>125724579</v>
       </c>
       <c r="B6" t="n">
         <v>57656</v>
@@ -1188,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450270</v>
+        <v>450145</v>
       </c>
       <c r="R6" t="n">
-        <v>7054720</v>
+        <v>7054502</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1168,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125724610</v>
+        <v>125714988</v>
       </c>
       <c r="B7" t="n">
         <v>57656</v>
@@ -1284,16 +1224,26 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Enarsvedjan, Jmt</t>
+          <t>Simamyren, Simamyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>450597</v>
+        <v>450413</v>
       </c>
       <c r="R7" t="n">
-        <v>7055031</v>
+        <v>7054149</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,14 +1273,24 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,26 +1301,51 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125724629</v>
+        <v>125724597</v>
       </c>
       <c r="B8" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,21 +1353,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>450502</v>
+        <v>450287</v>
       </c>
       <c r="R8" t="n">
-        <v>7054507</v>
+        <v>7054787</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,6 +1413,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125724628</v>
+        <v>125724591</v>
       </c>
       <c r="B9" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,21 +1455,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1489,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451229</v>
+        <v>450270</v>
       </c>
       <c r="R9" t="n">
-        <v>7055028</v>
+        <v>7054720</v>
       </c>
       <